--- a/shatrov_bootstraps_res.xlsx
+++ b/shatrov_bootstraps_res.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Игорь\Desktop\sem_8\diplom\bootstrap\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FDE16143-B3AB-4C4B-914D-FD490C70D644}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6A2C1159-C390-4DE7-A083-33748DBB997A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Информация про ряды" sheetId="1" r:id="rId1"/>
@@ -29,7 +29,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="51" uniqueCount="18">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="86" uniqueCount="23">
   <si>
     <t>Номер</t>
   </si>
@@ -83,6 +83,21 @@
   </si>
   <si>
     <t>SARIMA</t>
+  </si>
+  <si>
+    <t>Monthly Mean Temperature</t>
+  </si>
+  <si>
+    <t>https://raw.githubusercontent.com/jbrownlee/Datasets/master/monthly-mean-temp.csv</t>
+  </si>
+  <si>
+    <t>Примечания</t>
+  </si>
+  <si>
+    <t>-</t>
+  </si>
+  <si>
+    <t>Отсутствует тренд</t>
   </si>
 </sst>
 </file>
@@ -90,7 +105,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <numFmts count="1">
-    <numFmt numFmtId="168" formatCode="0.000"/>
+    <numFmt numFmtId="164" formatCode="0.000"/>
   </numFmts>
   <fonts count="3" x14ac:knownFonts="1">
     <font>
@@ -115,7 +130,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="3">
+  <fills count="4">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -125,6 +140,12 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor theme="6"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFF0000"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -141,12 +162,12 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="6">
+  <cellXfs count="8">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="168" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -156,6 +177,8 @@
     <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Обычный" xfId="0" builtinId="0"/>
@@ -436,10 +459,13 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="D4:F5"/>
+  <dimension ref="D4:G16"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="6" max="6" width="8.88671875" customWidth="1"/>
+  </cols>
   <sheetData>
-    <row r="4" spans="4:6" x14ac:dyDescent="0.3">
+    <row r="4" spans="4:7" x14ac:dyDescent="0.3">
       <c r="D4" t="s">
         <v>0</v>
       </c>
@@ -449,8 +475,11 @@
       <c r="F4" t="s">
         <v>2</v>
       </c>
-    </row>
-    <row r="5" spans="4:6" x14ac:dyDescent="0.3">
+      <c r="G4" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="5" spans="4:7" x14ac:dyDescent="0.3">
       <c r="D5">
         <v>1</v>
       </c>
@@ -460,6 +489,53 @@
       <c r="F5" s="1" t="s">
         <v>3</v>
       </c>
+      <c r="G5" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="6" spans="4:7" x14ac:dyDescent="0.3">
+      <c r="D6">
+        <v>2</v>
+      </c>
+      <c r="E6" t="s">
+        <v>18</v>
+      </c>
+      <c r="F6" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="G6" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="7" spans="4:7" x14ac:dyDescent="0.3">
+      <c r="F7" s="6"/>
+    </row>
+    <row r="8" spans="4:7" x14ac:dyDescent="0.3">
+      <c r="F8" s="6"/>
+    </row>
+    <row r="9" spans="4:7" x14ac:dyDescent="0.3">
+      <c r="F9" s="6"/>
+    </row>
+    <row r="10" spans="4:7" x14ac:dyDescent="0.3">
+      <c r="F10" s="6"/>
+    </row>
+    <row r="11" spans="4:7" x14ac:dyDescent="0.3">
+      <c r="F11" s="6"/>
+    </row>
+    <row r="12" spans="4:7" x14ac:dyDescent="0.3">
+      <c r="F12" s="6"/>
+    </row>
+    <row r="13" spans="4:7" x14ac:dyDescent="0.3">
+      <c r="F13" s="6"/>
+    </row>
+    <row r="14" spans="4:7" x14ac:dyDescent="0.3">
+      <c r="F14" s="6"/>
+    </row>
+    <row r="15" spans="4:7" x14ac:dyDescent="0.3">
+      <c r="F15" s="6"/>
+    </row>
+    <row r="16" spans="4:7" x14ac:dyDescent="0.3">
+      <c r="F16" s="6"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -468,7 +544,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5432242B-BB45-4574-A5B4-2CF25C9CDCFF}">
-  <dimension ref="D4:G13"/>
+  <dimension ref="D4:G22"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="4" max="4" width="13.21875" customWidth="1"/>
@@ -593,10 +669,116 @@
       <c r="F13" s="4"/>
       <c r="G13" s="4"/>
     </row>
+    <row r="14" spans="4:7" x14ac:dyDescent="0.3">
+      <c r="D14" s="3">
+        <v>2</v>
+      </c>
+      <c r="E14" t="s">
+        <v>9</v>
+      </c>
+      <c r="F14">
+        <v>1</v>
+      </c>
+      <c r="G14">
+        <v>10.445423</v>
+      </c>
+    </row>
+    <row r="15" spans="4:7" x14ac:dyDescent="0.3">
+      <c r="D15" s="3"/>
+      <c r="E15" t="s">
+        <v>16</v>
+      </c>
+      <c r="F15">
+        <v>1</v>
+      </c>
+      <c r="G15">
+        <v>10.442648</v>
+      </c>
+    </row>
+    <row r="16" spans="4:7" x14ac:dyDescent="0.3">
+      <c r="D16" s="3"/>
+      <c r="E16" t="s">
+        <v>10</v>
+      </c>
+      <c r="F16">
+        <v>1</v>
+      </c>
+      <c r="G16">
+        <v>10.353051000000001</v>
+      </c>
+    </row>
+    <row r="17" spans="4:7" x14ac:dyDescent="0.3">
+      <c r="D17" s="3"/>
+      <c r="E17" t="s">
+        <v>11</v>
+      </c>
+      <c r="F17">
+        <v>1</v>
+      </c>
+      <c r="G17">
+        <v>10.348001</v>
+      </c>
+    </row>
+    <row r="18" spans="4:7" x14ac:dyDescent="0.3">
+      <c r="D18" s="3"/>
+      <c r="E18" t="s">
+        <v>12</v>
+      </c>
+      <c r="F18">
+        <v>1</v>
+      </c>
+      <c r="G18">
+        <v>10.370028</v>
+      </c>
+    </row>
+    <row r="19" spans="4:7" x14ac:dyDescent="0.3">
+      <c r="D19" s="3"/>
+      <c r="E19" t="s">
+        <v>13</v>
+      </c>
+      <c r="F19">
+        <v>1</v>
+      </c>
+      <c r="G19">
+        <v>10.634069999999999</v>
+      </c>
+    </row>
+    <row r="20" spans="4:7" x14ac:dyDescent="0.3">
+      <c r="D20" s="3"/>
+      <c r="E20" t="s">
+        <v>14</v>
+      </c>
+      <c r="F20">
+        <v>1</v>
+      </c>
+      <c r="G20">
+        <v>10.265594999999999</v>
+      </c>
+    </row>
+    <row r="21" spans="4:7" x14ac:dyDescent="0.3">
+      <c r="D21" s="3"/>
+      <c r="E21" t="s">
+        <v>15</v>
+      </c>
+      <c r="F21">
+        <v>1</v>
+      </c>
+      <c r="G21">
+        <v>10.528846</v>
+      </c>
+    </row>
+    <row r="22" spans="4:7" x14ac:dyDescent="0.3">
+      <c r="D22" s="4"/>
+      <c r="E22" s="4"/>
+      <c r="F22" s="4"/>
+      <c r="G22" s="4"/>
+    </row>
   </sheetData>
-  <mergeCells count="2">
+  <mergeCells count="4">
     <mergeCell ref="D5:D12"/>
     <mergeCell ref="D13:G13"/>
+    <mergeCell ref="D14:D21"/>
+    <mergeCell ref="D22:G22"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -604,7 +786,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D9F3D6F7-9B83-4803-A2A9-5F6E3F05FBE9}">
-  <dimension ref="D4:G13"/>
+  <dimension ref="D4:G22"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="4" max="4" width="13.21875" customWidth="1"/>
@@ -729,10 +911,116 @@
       <c r="F13" s="4"/>
       <c r="G13" s="4"/>
     </row>
+    <row r="14" spans="4:7" x14ac:dyDescent="0.3">
+      <c r="D14" s="3">
+        <v>2</v>
+      </c>
+      <c r="E14" t="s">
+        <v>17</v>
+      </c>
+      <c r="F14">
+        <v>1</v>
+      </c>
+      <c r="G14">
+        <v>9.9484739999999992</v>
+      </c>
+    </row>
+    <row r="15" spans="4:7" x14ac:dyDescent="0.3">
+      <c r="D15" s="3"/>
+      <c r="E15" t="s">
+        <v>16</v>
+      </c>
+      <c r="F15">
+        <v>1</v>
+      </c>
+      <c r="G15">
+        <v>9.8285889999999991</v>
+      </c>
+    </row>
+    <row r="16" spans="4:7" x14ac:dyDescent="0.3">
+      <c r="D16" s="3"/>
+      <c r="E16" t="s">
+        <v>10</v>
+      </c>
+      <c r="F16">
+        <v>1</v>
+      </c>
+      <c r="G16">
+        <v>9.9364369999999997</v>
+      </c>
+    </row>
+    <row r="17" spans="4:7" x14ac:dyDescent="0.3">
+      <c r="D17" s="3"/>
+      <c r="E17" t="s">
+        <v>11</v>
+      </c>
+      <c r="F17">
+        <v>1</v>
+      </c>
+      <c r="G17">
+        <v>9.9255580000000005</v>
+      </c>
+    </row>
+    <row r="18" spans="4:7" x14ac:dyDescent="0.3">
+      <c r="D18" s="3"/>
+      <c r="E18" t="s">
+        <v>12</v>
+      </c>
+      <c r="F18">
+        <v>1</v>
+      </c>
+      <c r="G18">
+        <v>9.8594209999999993</v>
+      </c>
+    </row>
+    <row r="19" spans="4:7" x14ac:dyDescent="0.3">
+      <c r="D19" s="3"/>
+      <c r="E19" s="7" t="s">
+        <v>13</v>
+      </c>
+      <c r="F19" s="7">
+        <v>1</v>
+      </c>
+      <c r="G19" s="7">
+        <v>62.336621000000001</v>
+      </c>
+    </row>
+    <row r="20" spans="4:7" x14ac:dyDescent="0.3">
+      <c r="D20" s="3"/>
+      <c r="E20" t="s">
+        <v>14</v>
+      </c>
+      <c r="F20">
+        <v>1</v>
+      </c>
+      <c r="G20">
+        <v>9.8234449999999995</v>
+      </c>
+    </row>
+    <row r="21" spans="4:7" x14ac:dyDescent="0.3">
+      <c r="D21" s="3"/>
+      <c r="E21" t="s">
+        <v>15</v>
+      </c>
+      <c r="F21">
+        <v>1</v>
+      </c>
+      <c r="G21">
+        <v>9.9187390000000004</v>
+      </c>
+    </row>
+    <row r="22" spans="4:7" x14ac:dyDescent="0.3">
+      <c r="D22" s="4"/>
+      <c r="E22" s="4"/>
+      <c r="F22" s="4"/>
+      <c r="G22" s="4"/>
+    </row>
   </sheetData>
-  <mergeCells count="2">
+  <mergeCells count="4">
     <mergeCell ref="D5:D12"/>
     <mergeCell ref="D13:G13"/>
+    <mergeCell ref="D14:D21"/>
+    <mergeCell ref="D22:G22"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -740,7 +1028,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D9B1F934-9143-4061-8956-2969F906ECCB}">
-  <dimension ref="D4:G12"/>
+  <dimension ref="D4:G20"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="4" max="4" width="16.33203125" customWidth="1"/>
@@ -853,10 +1141,104 @@
       <c r="F12" s="5"/>
       <c r="G12" s="5"/>
     </row>
+    <row r="13" spans="4:7" x14ac:dyDescent="0.3">
+      <c r="D13" s="3">
+        <v>2</v>
+      </c>
+      <c r="E13" t="s">
+        <v>16</v>
+      </c>
+      <c r="F13">
+        <v>0.79166700000000001</v>
+      </c>
+      <c r="G13">
+        <v>4.8847680000000002</v>
+      </c>
+    </row>
+    <row r="14" spans="4:7" x14ac:dyDescent="0.3">
+      <c r="D14" s="3"/>
+      <c r="E14" t="s">
+        <v>10</v>
+      </c>
+      <c r="F14">
+        <v>0.79166700000000001</v>
+      </c>
+      <c r="G14">
+        <v>4.2140019999999998</v>
+      </c>
+    </row>
+    <row r="15" spans="4:7" x14ac:dyDescent="0.3">
+      <c r="D15" s="3"/>
+      <c r="E15" t="s">
+        <v>11</v>
+      </c>
+      <c r="F15">
+        <v>0.45833299999999999</v>
+      </c>
+      <c r="G15">
+        <v>2.0839439999999998</v>
+      </c>
+    </row>
+    <row r="16" spans="4:7" x14ac:dyDescent="0.3">
+      <c r="D16" s="3"/>
+      <c r="E16" t="s">
+        <v>12</v>
+      </c>
+      <c r="F16">
+        <v>0.375</v>
+      </c>
+      <c r="G16">
+        <v>1.7597320000000001</v>
+      </c>
+    </row>
+    <row r="17" spans="4:7" x14ac:dyDescent="0.3">
+      <c r="D17" s="3"/>
+      <c r="E17" t="s">
+        <v>13</v>
+      </c>
+      <c r="F17">
+        <v>0.70833299999999999</v>
+      </c>
+      <c r="G17">
+        <v>4.2938049999999999</v>
+      </c>
+    </row>
+    <row r="18" spans="4:7" x14ac:dyDescent="0.3">
+      <c r="D18" s="3"/>
+      <c r="E18" t="s">
+        <v>14</v>
+      </c>
+      <c r="F18">
+        <v>0.75</v>
+      </c>
+      <c r="G18">
+        <v>4.2911840000000003</v>
+      </c>
+    </row>
+    <row r="19" spans="4:7" x14ac:dyDescent="0.3">
+      <c r="D19" s="3"/>
+      <c r="E19" t="s">
+        <v>15</v>
+      </c>
+      <c r="F19">
+        <v>0.83333299999999999</v>
+      </c>
+      <c r="G19">
+        <v>5.2630650000000001</v>
+      </c>
+    </row>
+    <row r="20" spans="4:7" x14ac:dyDescent="0.3">
+      <c r="D20" s="4"/>
+      <c r="E20" s="4"/>
+      <c r="F20" s="4"/>
+      <c r="G20" s="4"/>
+    </row>
   </sheetData>
-  <mergeCells count="2">
+  <mergeCells count="4">
     <mergeCell ref="D5:D11"/>
     <mergeCell ref="D12:G12"/>
+    <mergeCell ref="D13:D19"/>
+    <mergeCell ref="D20:G20"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -864,7 +1246,7 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{AA9C7C1F-8E69-4E9D-9311-55B2096F876D}">
-  <dimension ref="D4:G12"/>
+  <dimension ref="D4:G20"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="4" max="4" width="16.33203125" customWidth="1"/>
@@ -977,10 +1359,104 @@
       <c r="F12" s="5"/>
       <c r="G12" s="5"/>
     </row>
+    <row r="13" spans="4:7" x14ac:dyDescent="0.3">
+      <c r="D13" s="3">
+        <v>2</v>
+      </c>
+      <c r="E13" t="s">
+        <v>16</v>
+      </c>
+      <c r="F13">
+        <v>0.75</v>
+      </c>
+      <c r="G13">
+        <v>3.302511</v>
+      </c>
+    </row>
+    <row r="14" spans="4:7" x14ac:dyDescent="0.3">
+      <c r="D14" s="3"/>
+      <c r="E14" t="s">
+        <v>10</v>
+      </c>
+      <c r="F14">
+        <v>0.70833299999999999</v>
+      </c>
+      <c r="G14">
+        <v>2.826975</v>
+      </c>
+    </row>
+    <row r="15" spans="4:7" x14ac:dyDescent="0.3">
+      <c r="D15" s="3"/>
+      <c r="E15" t="s">
+        <v>11</v>
+      </c>
+      <c r="F15">
+        <v>0.45833299999999999</v>
+      </c>
+      <c r="G15">
+        <v>1.7640830000000001</v>
+      </c>
+    </row>
+    <row r="16" spans="4:7" x14ac:dyDescent="0.3">
+      <c r="D16" s="3"/>
+      <c r="E16" t="s">
+        <v>12</v>
+      </c>
+      <c r="F16">
+        <v>0.41666700000000001</v>
+      </c>
+      <c r="G16">
+        <v>1.5894790000000001</v>
+      </c>
+    </row>
+    <row r="17" spans="4:7" x14ac:dyDescent="0.3">
+      <c r="D17" s="3"/>
+      <c r="E17" t="s">
+        <v>13</v>
+      </c>
+      <c r="F17">
+        <v>0.54166700000000001</v>
+      </c>
+      <c r="G17">
+        <v>2.2582849999999999</v>
+      </c>
+    </row>
+    <row r="18" spans="4:7" x14ac:dyDescent="0.3">
+      <c r="D18" s="3"/>
+      <c r="E18" t="s">
+        <v>14</v>
+      </c>
+      <c r="F18">
+        <v>0.75</v>
+      </c>
+      <c r="G18">
+        <v>4.5597669999999999</v>
+      </c>
+    </row>
+    <row r="19" spans="4:7" x14ac:dyDescent="0.3">
+      <c r="D19" s="3"/>
+      <c r="E19" t="s">
+        <v>15</v>
+      </c>
+      <c r="F19">
+        <v>0.70833299999999999</v>
+      </c>
+      <c r="G19">
+        <v>3.3573539999999999</v>
+      </c>
+    </row>
+    <row r="20" spans="4:7" x14ac:dyDescent="0.3">
+      <c r="D20" s="4"/>
+      <c r="E20" s="4"/>
+      <c r="F20" s="4"/>
+      <c r="G20" s="4"/>
+    </row>
   </sheetData>
-  <mergeCells count="2">
+  <mergeCells count="4">
     <mergeCell ref="D5:D11"/>
     <mergeCell ref="D12:G12"/>
+    <mergeCell ref="D20:G20"/>
+    <mergeCell ref="D13:D19"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/shatrov_bootstraps_res.xlsx
+++ b/shatrov_bootstraps_res.xlsx
@@ -5,12 +5,12 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Игорь\Desktop\sem_8\diplom\bootstrap\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Игорь\Desktop\sem_8\mipt_diplom\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6A2C1159-C390-4DE7-A083-33748DBB997A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C6D47663-394C-4FCE-AA78-3825534A79C1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Информация про ряды" sheetId="1" r:id="rId1"/>
@@ -29,7 +29,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="86" uniqueCount="23">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="120" uniqueCount="27">
   <si>
     <t>Номер</t>
   </si>
@@ -98,6 +98,18 @@
   </si>
   <si>
     <t>Отсутствует тренд</t>
+  </si>
+  <si>
+    <t>Для этого ряда ARIMA напрогнозировала что-то совсем не то</t>
+  </si>
+  <si>
+    <t>https://raw.githubusercontent.com/jbrownlee/Datasets/master/monthly_champagne_sales.csv</t>
+  </si>
+  <si>
+    <t>Monthly Champagne Sales</t>
+  </si>
+  <si>
+    <t>Почему-то для этого ряда методы ML сработали лучше, чем ARIMA/SARIMA</t>
   </si>
 </sst>
 </file>
@@ -168,6 +180,7 @@
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -177,8 +190,9 @@
     <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Обычный" xfId="0" builtinId="0"/>
@@ -459,7 +473,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="D4:G16"/>
+  <dimension ref="D4:G7"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="6" max="6" width="8.88671875" customWidth="1"/>
@@ -508,34 +522,18 @@
       </c>
     </row>
     <row r="7" spans="4:7" x14ac:dyDescent="0.3">
-      <c r="F7" s="6"/>
-    </row>
-    <row r="8" spans="4:7" x14ac:dyDescent="0.3">
-      <c r="F8" s="6"/>
-    </row>
-    <row r="9" spans="4:7" x14ac:dyDescent="0.3">
-      <c r="F9" s="6"/>
-    </row>
-    <row r="10" spans="4:7" x14ac:dyDescent="0.3">
-      <c r="F10" s="6"/>
-    </row>
-    <row r="11" spans="4:7" x14ac:dyDescent="0.3">
-      <c r="F11" s="6"/>
-    </row>
-    <row r="12" spans="4:7" x14ac:dyDescent="0.3">
-      <c r="F12" s="6"/>
-    </row>
-    <row r="13" spans="4:7" x14ac:dyDescent="0.3">
-      <c r="F13" s="6"/>
-    </row>
-    <row r="14" spans="4:7" x14ac:dyDescent="0.3">
-      <c r="F14" s="6"/>
-    </row>
-    <row r="15" spans="4:7" x14ac:dyDescent="0.3">
-      <c r="F15" s="6"/>
-    </row>
-    <row r="16" spans="4:7" x14ac:dyDescent="0.3">
-      <c r="F16" s="6"/>
+      <c r="D7">
+        <v>3</v>
+      </c>
+      <c r="E7" t="s">
+        <v>25</v>
+      </c>
+      <c r="F7" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="G7" t="s">
+        <v>26</v>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -544,7 +542,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5432242B-BB45-4574-A5B4-2CF25C9CDCFF}">
-  <dimension ref="D4:G22"/>
+  <dimension ref="D4:H31"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="4" max="4" width="13.21875" customWidth="1"/>
@@ -566,7 +564,7 @@
       </c>
     </row>
     <row r="5" spans="4:7" x14ac:dyDescent="0.3">
-      <c r="D5" s="3">
+      <c r="D5" s="4">
         <v>1</v>
       </c>
       <c r="E5" t="s">
@@ -580,7 +578,7 @@
       </c>
     </row>
     <row r="6" spans="4:7" x14ac:dyDescent="0.3">
-      <c r="D6" s="3"/>
+      <c r="D6" s="4"/>
       <c r="E6" t="s">
         <v>16</v>
       </c>
@@ -592,7 +590,7 @@
       </c>
     </row>
     <row r="7" spans="4:7" x14ac:dyDescent="0.3">
-      <c r="D7" s="3"/>
+      <c r="D7" s="4"/>
       <c r="E7" t="s">
         <v>10</v>
       </c>
@@ -604,7 +602,7 @@
       </c>
     </row>
     <row r="8" spans="4:7" x14ac:dyDescent="0.3">
-      <c r="D8" s="3"/>
+      <c r="D8" s="4"/>
       <c r="E8" t="s">
         <v>11</v>
       </c>
@@ -616,7 +614,7 @@
       </c>
     </row>
     <row r="9" spans="4:7" x14ac:dyDescent="0.3">
-      <c r="D9" s="3"/>
+      <c r="D9" s="4"/>
       <c r="E9" t="s">
         <v>12</v>
       </c>
@@ -628,7 +626,7 @@
       </c>
     </row>
     <row r="10" spans="4:7" x14ac:dyDescent="0.3">
-      <c r="D10" s="3"/>
+      <c r="D10" s="4"/>
       <c r="E10" t="s">
         <v>13</v>
       </c>
@@ -640,7 +638,7 @@
       </c>
     </row>
     <row r="11" spans="4:7" x14ac:dyDescent="0.3">
-      <c r="D11" s="3"/>
+      <c r="D11" s="4"/>
       <c r="E11" t="s">
         <v>14</v>
       </c>
@@ -652,7 +650,7 @@
       </c>
     </row>
     <row r="12" spans="4:7" x14ac:dyDescent="0.3">
-      <c r="D12" s="3"/>
+      <c r="D12" s="4"/>
       <c r="E12" t="s">
         <v>15</v>
       </c>
@@ -664,13 +662,13 @@
       </c>
     </row>
     <row r="13" spans="4:7" x14ac:dyDescent="0.3">
-      <c r="D13" s="4"/>
-      <c r="E13" s="4"/>
-      <c r="F13" s="4"/>
-      <c r="G13" s="4"/>
+      <c r="D13" s="5"/>
+      <c r="E13" s="5"/>
+      <c r="F13" s="5"/>
+      <c r="G13" s="5"/>
     </row>
     <row r="14" spans="4:7" x14ac:dyDescent="0.3">
-      <c r="D14" s="3">
+      <c r="D14" s="4">
         <v>2</v>
       </c>
       <c r="E14" t="s">
@@ -684,7 +682,7 @@
       </c>
     </row>
     <row r="15" spans="4:7" x14ac:dyDescent="0.3">
-      <c r="D15" s="3"/>
+      <c r="D15" s="4"/>
       <c r="E15" t="s">
         <v>16</v>
       </c>
@@ -696,7 +694,7 @@
       </c>
     </row>
     <row r="16" spans="4:7" x14ac:dyDescent="0.3">
-      <c r="D16" s="3"/>
+      <c r="D16" s="4"/>
       <c r="E16" t="s">
         <v>10</v>
       </c>
@@ -707,8 +705,8 @@
         <v>10.353051000000001</v>
       </c>
     </row>
-    <row r="17" spans="4:7" x14ac:dyDescent="0.3">
-      <c r="D17" s="3"/>
+    <row r="17" spans="4:8" x14ac:dyDescent="0.3">
+      <c r="D17" s="4"/>
       <c r="E17" t="s">
         <v>11</v>
       </c>
@@ -719,8 +717,8 @@
         <v>10.348001</v>
       </c>
     </row>
-    <row r="18" spans="4:7" x14ac:dyDescent="0.3">
-      <c r="D18" s="3"/>
+    <row r="18" spans="4:8" x14ac:dyDescent="0.3">
+      <c r="D18" s="4"/>
       <c r="E18" t="s">
         <v>12</v>
       </c>
@@ -731,8 +729,8 @@
         <v>10.370028</v>
       </c>
     </row>
-    <row r="19" spans="4:7" x14ac:dyDescent="0.3">
-      <c r="D19" s="3"/>
+    <row r="19" spans="4:8" x14ac:dyDescent="0.3">
+      <c r="D19" s="4"/>
       <c r="E19" t="s">
         <v>13</v>
       </c>
@@ -743,8 +741,8 @@
         <v>10.634069999999999</v>
       </c>
     </row>
-    <row r="20" spans="4:7" x14ac:dyDescent="0.3">
-      <c r="D20" s="3"/>
+    <row r="20" spans="4:8" x14ac:dyDescent="0.3">
+      <c r="D20" s="4"/>
       <c r="E20" t="s">
         <v>14</v>
       </c>
@@ -755,8 +753,8 @@
         <v>10.265594999999999</v>
       </c>
     </row>
-    <row r="21" spans="4:7" x14ac:dyDescent="0.3">
-      <c r="D21" s="3"/>
+    <row r="21" spans="4:8" x14ac:dyDescent="0.3">
+      <c r="D21" s="4"/>
       <c r="E21" t="s">
         <v>15</v>
       </c>
@@ -767,18 +765,127 @@
         <v>10.528846</v>
       </c>
     </row>
-    <row r="22" spans="4:7" x14ac:dyDescent="0.3">
-      <c r="D22" s="4"/>
-      <c r="E22" s="4"/>
-      <c r="F22" s="4"/>
-      <c r="G22" s="4"/>
+    <row r="22" spans="4:8" x14ac:dyDescent="0.3">
+      <c r="D22" s="5"/>
+      <c r="E22" s="5"/>
+      <c r="F22" s="5"/>
+      <c r="G22" s="5"/>
+    </row>
+    <row r="23" spans="4:8" x14ac:dyDescent="0.3">
+      <c r="D23" s="4">
+        <v>3</v>
+      </c>
+      <c r="E23" t="s">
+        <v>9</v>
+      </c>
+      <c r="F23">
+        <v>1</v>
+      </c>
+      <c r="G23">
+        <v>329225.10081099998</v>
+      </c>
+      <c r="H23" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="24" spans="4:8" x14ac:dyDescent="0.3">
+      <c r="D24" s="4"/>
+      <c r="E24" t="s">
+        <v>16</v>
+      </c>
+      <c r="F24">
+        <v>1</v>
+      </c>
+      <c r="G24">
+        <v>323506.65818299999</v>
+      </c>
+    </row>
+    <row r="25" spans="4:8" x14ac:dyDescent="0.3">
+      <c r="D25" s="4"/>
+      <c r="E25" t="s">
+        <v>10</v>
+      </c>
+      <c r="F25">
+        <v>1</v>
+      </c>
+      <c r="G25">
+        <v>323403.41790900001</v>
+      </c>
+    </row>
+    <row r="26" spans="4:8" x14ac:dyDescent="0.3">
+      <c r="D26" s="4"/>
+      <c r="E26" t="s">
+        <v>11</v>
+      </c>
+      <c r="F26">
+        <v>1</v>
+      </c>
+      <c r="G26">
+        <v>319829.36786699999</v>
+      </c>
+    </row>
+    <row r="27" spans="4:8" x14ac:dyDescent="0.3">
+      <c r="D27" s="4"/>
+      <c r="E27" t="s">
+        <v>12</v>
+      </c>
+      <c r="F27">
+        <v>1</v>
+      </c>
+      <c r="G27">
+        <v>327693.045598</v>
+      </c>
+    </row>
+    <row r="28" spans="4:8" x14ac:dyDescent="0.3">
+      <c r="D28" s="4"/>
+      <c r="E28" t="s">
+        <v>13</v>
+      </c>
+      <c r="F28">
+        <v>0.2</v>
+      </c>
+      <c r="G28">
+        <v>12255.272467000001</v>
+      </c>
+    </row>
+    <row r="29" spans="4:8" x14ac:dyDescent="0.3">
+      <c r="D29" s="4"/>
+      <c r="E29" t="s">
+        <v>14</v>
+      </c>
+      <c r="F29">
+        <v>1</v>
+      </c>
+      <c r="G29">
+        <v>321583.63291799999</v>
+      </c>
+    </row>
+    <row r="30" spans="4:8" x14ac:dyDescent="0.3">
+      <c r="D30" s="4"/>
+      <c r="E30" t="s">
+        <v>15</v>
+      </c>
+      <c r="F30">
+        <v>1</v>
+      </c>
+      <c r="G30">
+        <v>344760.60256199999</v>
+      </c>
+    </row>
+    <row r="31" spans="4:8" x14ac:dyDescent="0.3">
+      <c r="D31" s="7"/>
+      <c r="E31" s="7"/>
+      <c r="F31" s="7"/>
+      <c r="G31" s="7"/>
     </row>
   </sheetData>
-  <mergeCells count="4">
+  <mergeCells count="6">
+    <mergeCell ref="D31:G31"/>
     <mergeCell ref="D5:D12"/>
     <mergeCell ref="D13:G13"/>
     <mergeCell ref="D14:D21"/>
     <mergeCell ref="D22:G22"/>
+    <mergeCell ref="D23:D30"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -786,7 +893,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D9F3D6F7-9B83-4803-A2A9-5F6E3F05FBE9}">
-  <dimension ref="D4:G22"/>
+  <dimension ref="D4:G31"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="4" max="4" width="13.21875" customWidth="1"/>
@@ -808,7 +915,7 @@
       </c>
     </row>
     <row r="5" spans="4:7" x14ac:dyDescent="0.3">
-      <c r="D5" s="3">
+      <c r="D5" s="4">
         <v>1</v>
       </c>
       <c r="E5" t="s">
@@ -822,7 +929,7 @@
       </c>
     </row>
     <row r="6" spans="4:7" x14ac:dyDescent="0.3">
-      <c r="D6" s="3"/>
+      <c r="D6" s="4"/>
       <c r="E6" t="s">
         <v>16</v>
       </c>
@@ -834,7 +941,7 @@
       </c>
     </row>
     <row r="7" spans="4:7" x14ac:dyDescent="0.3">
-      <c r="D7" s="3"/>
+      <c r="D7" s="4"/>
       <c r="E7" t="s">
         <v>10</v>
       </c>
@@ -846,7 +953,7 @@
       </c>
     </row>
     <row r="8" spans="4:7" x14ac:dyDescent="0.3">
-      <c r="D8" s="3"/>
+      <c r="D8" s="4"/>
       <c r="E8" t="s">
         <v>11</v>
       </c>
@@ -858,7 +965,7 @@
       </c>
     </row>
     <row r="9" spans="4:7" x14ac:dyDescent="0.3">
-      <c r="D9" s="3"/>
+      <c r="D9" s="4"/>
       <c r="E9" t="s">
         <v>12</v>
       </c>
@@ -870,7 +977,7 @@
       </c>
     </row>
     <row r="10" spans="4:7" x14ac:dyDescent="0.3">
-      <c r="D10" s="3"/>
+      <c r="D10" s="4"/>
       <c r="E10" t="s">
         <v>13</v>
       </c>
@@ -882,7 +989,7 @@
       </c>
     </row>
     <row r="11" spans="4:7" x14ac:dyDescent="0.3">
-      <c r="D11" s="3"/>
+      <c r="D11" s="4"/>
       <c r="E11" t="s">
         <v>14</v>
       </c>
@@ -894,7 +1001,7 @@
       </c>
     </row>
     <row r="12" spans="4:7" x14ac:dyDescent="0.3">
-      <c r="D12" s="3"/>
+      <c r="D12" s="4"/>
       <c r="E12" t="s">
         <v>15</v>
       </c>
@@ -906,13 +1013,13 @@
       </c>
     </row>
     <row r="13" spans="4:7" x14ac:dyDescent="0.3">
-      <c r="D13" s="4"/>
-      <c r="E13" s="4"/>
-      <c r="F13" s="4"/>
-      <c r="G13" s="4"/>
+      <c r="D13" s="5"/>
+      <c r="E13" s="5"/>
+      <c r="F13" s="5"/>
+      <c r="G13" s="5"/>
     </row>
     <row r="14" spans="4:7" x14ac:dyDescent="0.3">
-      <c r="D14" s="3">
+      <c r="D14" s="4">
         <v>2</v>
       </c>
       <c r="E14" t="s">
@@ -926,7 +1033,7 @@
       </c>
     </row>
     <row r="15" spans="4:7" x14ac:dyDescent="0.3">
-      <c r="D15" s="3"/>
+      <c r="D15" s="4"/>
       <c r="E15" t="s">
         <v>16</v>
       </c>
@@ -938,7 +1045,7 @@
       </c>
     </row>
     <row r="16" spans="4:7" x14ac:dyDescent="0.3">
-      <c r="D16" s="3"/>
+      <c r="D16" s="4"/>
       <c r="E16" t="s">
         <v>10</v>
       </c>
@@ -950,7 +1057,7 @@
       </c>
     </row>
     <row r="17" spans="4:7" x14ac:dyDescent="0.3">
-      <c r="D17" s="3"/>
+      <c r="D17" s="4"/>
       <c r="E17" t="s">
         <v>11</v>
       </c>
@@ -962,7 +1069,7 @@
       </c>
     </row>
     <row r="18" spans="4:7" x14ac:dyDescent="0.3">
-      <c r="D18" s="3"/>
+      <c r="D18" s="4"/>
       <c r="E18" t="s">
         <v>12</v>
       </c>
@@ -974,19 +1081,19 @@
       </c>
     </row>
     <row r="19" spans="4:7" x14ac:dyDescent="0.3">
-      <c r="D19" s="3"/>
-      <c r="E19" s="7" t="s">
+      <c r="D19" s="4"/>
+      <c r="E19" s="3" t="s">
         <v>13</v>
       </c>
-      <c r="F19" s="7">
-        <v>1</v>
-      </c>
-      <c r="G19" s="7">
+      <c r="F19" s="3">
+        <v>1</v>
+      </c>
+      <c r="G19" s="3">
         <v>62.336621000000001</v>
       </c>
     </row>
     <row r="20" spans="4:7" x14ac:dyDescent="0.3">
-      <c r="D20" s="3"/>
+      <c r="D20" s="4"/>
       <c r="E20" t="s">
         <v>14</v>
       </c>
@@ -998,7 +1105,7 @@
       </c>
     </row>
     <row r="21" spans="4:7" x14ac:dyDescent="0.3">
-      <c r="D21" s="3"/>
+      <c r="D21" s="4"/>
       <c r="E21" t="s">
         <v>15</v>
       </c>
@@ -1010,17 +1117,123 @@
       </c>
     </row>
     <row r="22" spans="4:7" x14ac:dyDescent="0.3">
-      <c r="D22" s="4"/>
-      <c r="E22" s="4"/>
-      <c r="F22" s="4"/>
-      <c r="G22" s="4"/>
+      <c r="D22" s="5"/>
+      <c r="E22" s="5"/>
+      <c r="F22" s="5"/>
+      <c r="G22" s="5"/>
+    </row>
+    <row r="23" spans="4:7" x14ac:dyDescent="0.3">
+      <c r="D23" s="4">
+        <v>3</v>
+      </c>
+      <c r="E23" t="s">
+        <v>17</v>
+      </c>
+      <c r="F23" s="2">
+        <v>0.95</v>
+      </c>
+      <c r="G23" s="2">
+        <v>3410.9398190000002</v>
+      </c>
+    </row>
+    <row r="24" spans="4:7" x14ac:dyDescent="0.3">
+      <c r="D24" s="4"/>
+      <c r="E24" t="s">
+        <v>16</v>
+      </c>
+      <c r="F24" s="2">
+        <v>0.95</v>
+      </c>
+      <c r="G24" s="2">
+        <v>3401.3317860000002</v>
+      </c>
+    </row>
+    <row r="25" spans="4:7" x14ac:dyDescent="0.3">
+      <c r="D25" s="4"/>
+      <c r="E25" t="s">
+        <v>10</v>
+      </c>
+      <c r="F25" s="2">
+        <v>0.95</v>
+      </c>
+      <c r="G25" s="2">
+        <v>3380.0382789999999</v>
+      </c>
+    </row>
+    <row r="26" spans="4:7" x14ac:dyDescent="0.3">
+      <c r="D26" s="4"/>
+      <c r="E26" t="s">
+        <v>11</v>
+      </c>
+      <c r="F26" s="2">
+        <v>0.95</v>
+      </c>
+      <c r="G26" s="2">
+        <v>3409.493759</v>
+      </c>
+    </row>
+    <row r="27" spans="4:7" x14ac:dyDescent="0.3">
+      <c r="D27" s="4"/>
+      <c r="E27" t="s">
+        <v>12</v>
+      </c>
+      <c r="F27" s="2">
+        <v>0.95</v>
+      </c>
+      <c r="G27" s="2">
+        <v>3362.0034879999998</v>
+      </c>
+    </row>
+    <row r="28" spans="4:7" x14ac:dyDescent="0.3">
+      <c r="D28" s="4"/>
+      <c r="E28" t="s">
+        <v>13</v>
+      </c>
+      <c r="F28" s="2">
+        <v>1</v>
+      </c>
+      <c r="G28" s="2">
+        <v>6467.5310920000002</v>
+      </c>
+    </row>
+    <row r="29" spans="4:7" x14ac:dyDescent="0.3">
+      <c r="D29" s="4"/>
+      <c r="E29" t="s">
+        <v>14</v>
+      </c>
+      <c r="F29" s="2">
+        <v>0.95</v>
+      </c>
+      <c r="G29" s="2">
+        <v>3399.3432069999999</v>
+      </c>
+    </row>
+    <row r="30" spans="4:7" x14ac:dyDescent="0.3">
+      <c r="D30" s="4"/>
+      <c r="E30" t="s">
+        <v>15</v>
+      </c>
+      <c r="F30" s="2">
+        <v>0.95</v>
+      </c>
+      <c r="G30" s="2">
+        <v>3379.5483079999999</v>
+      </c>
+    </row>
+    <row r="31" spans="4:7" x14ac:dyDescent="0.3">
+      <c r="D31" s="5"/>
+      <c r="E31" s="5"/>
+      <c r="F31" s="5"/>
+      <c r="G31" s="5"/>
     </row>
   </sheetData>
-  <mergeCells count="4">
+  <mergeCells count="6">
+    <mergeCell ref="D31:G31"/>
     <mergeCell ref="D5:D12"/>
     <mergeCell ref="D13:G13"/>
     <mergeCell ref="D14:D21"/>
     <mergeCell ref="D22:G22"/>
+    <mergeCell ref="D23:D30"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -1028,7 +1241,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D9B1F934-9143-4061-8956-2969F906ECCB}">
-  <dimension ref="D4:G20"/>
+  <dimension ref="D4:G28"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="4" max="4" width="16.33203125" customWidth="1"/>
@@ -1050,7 +1263,7 @@
       </c>
     </row>
     <row r="5" spans="4:7" x14ac:dyDescent="0.3">
-      <c r="D5" s="3">
+      <c r="D5" s="4">
         <v>1</v>
       </c>
       <c r="E5" t="s">
@@ -1064,7 +1277,7 @@
       </c>
     </row>
     <row r="6" spans="4:7" x14ac:dyDescent="0.3">
-      <c r="D6" s="3"/>
+      <c r="D6" s="4"/>
       <c r="E6" t="s">
         <v>10</v>
       </c>
@@ -1076,7 +1289,7 @@
       </c>
     </row>
     <row r="7" spans="4:7" x14ac:dyDescent="0.3">
-      <c r="D7" s="3"/>
+      <c r="D7" s="4"/>
       <c r="E7" t="s">
         <v>11</v>
       </c>
@@ -1088,7 +1301,7 @@
       </c>
     </row>
     <row r="8" spans="4:7" x14ac:dyDescent="0.3">
-      <c r="D8" s="3"/>
+      <c r="D8" s="4"/>
       <c r="E8" t="s">
         <v>12</v>
       </c>
@@ -1100,7 +1313,7 @@
       </c>
     </row>
     <row r="9" spans="4:7" x14ac:dyDescent="0.3">
-      <c r="D9" s="3"/>
+      <c r="D9" s="4"/>
       <c r="E9" t="s">
         <v>13</v>
       </c>
@@ -1112,7 +1325,7 @@
       </c>
     </row>
     <row r="10" spans="4:7" x14ac:dyDescent="0.3">
-      <c r="D10" s="3"/>
+      <c r="D10" s="4"/>
       <c r="E10" t="s">
         <v>14</v>
       </c>
@@ -1124,7 +1337,7 @@
       </c>
     </row>
     <row r="11" spans="4:7" x14ac:dyDescent="0.3">
-      <c r="D11" s="3"/>
+      <c r="D11" s="4"/>
       <c r="E11" t="s">
         <v>15</v>
       </c>
@@ -1136,13 +1349,13 @@
       </c>
     </row>
     <row r="12" spans="4:7" x14ac:dyDescent="0.3">
-      <c r="D12" s="5"/>
-      <c r="E12" s="5"/>
-      <c r="F12" s="5"/>
-      <c r="G12" s="5"/>
+      <c r="D12" s="6"/>
+      <c r="E12" s="6"/>
+      <c r="F12" s="6"/>
+      <c r="G12" s="6"/>
     </row>
     <row r="13" spans="4:7" x14ac:dyDescent="0.3">
-      <c r="D13" s="3">
+      <c r="D13" s="4">
         <v>2</v>
       </c>
       <c r="E13" t="s">
@@ -1156,7 +1369,7 @@
       </c>
     </row>
     <row r="14" spans="4:7" x14ac:dyDescent="0.3">
-      <c r="D14" s="3"/>
+      <c r="D14" s="4"/>
       <c r="E14" t="s">
         <v>10</v>
       </c>
@@ -1168,7 +1381,7 @@
       </c>
     </row>
     <row r="15" spans="4:7" x14ac:dyDescent="0.3">
-      <c r="D15" s="3"/>
+      <c r="D15" s="4"/>
       <c r="E15" t="s">
         <v>11</v>
       </c>
@@ -1180,7 +1393,7 @@
       </c>
     </row>
     <row r="16" spans="4:7" x14ac:dyDescent="0.3">
-      <c r="D16" s="3"/>
+      <c r="D16" s="4"/>
       <c r="E16" t="s">
         <v>12</v>
       </c>
@@ -1192,7 +1405,7 @@
       </c>
     </row>
     <row r="17" spans="4:7" x14ac:dyDescent="0.3">
-      <c r="D17" s="3"/>
+      <c r="D17" s="4"/>
       <c r="E17" t="s">
         <v>13</v>
       </c>
@@ -1204,7 +1417,7 @@
       </c>
     </row>
     <row r="18" spans="4:7" x14ac:dyDescent="0.3">
-      <c r="D18" s="3"/>
+      <c r="D18" s="4"/>
       <c r="E18" t="s">
         <v>14</v>
       </c>
@@ -1216,7 +1429,7 @@
       </c>
     </row>
     <row r="19" spans="4:7" x14ac:dyDescent="0.3">
-      <c r="D19" s="3"/>
+      <c r="D19" s="4"/>
       <c r="E19" t="s">
         <v>15</v>
       </c>
@@ -1228,17 +1441,111 @@
       </c>
     </row>
     <row r="20" spans="4:7" x14ac:dyDescent="0.3">
-      <c r="D20" s="4"/>
-      <c r="E20" s="4"/>
-      <c r="F20" s="4"/>
-      <c r="G20" s="4"/>
+      <c r="D20" s="5"/>
+      <c r="E20" s="5"/>
+      <c r="F20" s="5"/>
+      <c r="G20" s="5"/>
+    </row>
+    <row r="21" spans="4:7" x14ac:dyDescent="0.3">
+      <c r="D21" s="4">
+        <v>3</v>
+      </c>
+      <c r="E21" t="s">
+        <v>16</v>
+      </c>
+      <c r="F21">
+        <v>0.55000000000000004</v>
+      </c>
+      <c r="G21">
+        <v>1376.209112</v>
+      </c>
+    </row>
+    <row r="22" spans="4:7" x14ac:dyDescent="0.3">
+      <c r="D22" s="4"/>
+      <c r="E22" t="s">
+        <v>10</v>
+      </c>
+      <c r="F22">
+        <v>0.6</v>
+      </c>
+      <c r="G22">
+        <v>1527.4098349999999</v>
+      </c>
+    </row>
+    <row r="23" spans="4:7" x14ac:dyDescent="0.3">
+      <c r="D23" s="4"/>
+      <c r="E23" t="s">
+        <v>11</v>
+      </c>
+      <c r="F23">
+        <v>0.3</v>
+      </c>
+      <c r="G23">
+        <v>509.229738</v>
+      </c>
+    </row>
+    <row r="24" spans="4:7" x14ac:dyDescent="0.3">
+      <c r="D24" s="4"/>
+      <c r="E24" t="s">
+        <v>12</v>
+      </c>
+      <c r="F24">
+        <v>0.25</v>
+      </c>
+      <c r="G24">
+        <v>425.22268600000001</v>
+      </c>
+    </row>
+    <row r="25" spans="4:7" x14ac:dyDescent="0.3">
+      <c r="D25" s="4"/>
+      <c r="E25" t="s">
+        <v>13</v>
+      </c>
+      <c r="F25">
+        <v>0.5</v>
+      </c>
+      <c r="G25">
+        <v>1001.471212</v>
+      </c>
+    </row>
+    <row r="26" spans="4:7" x14ac:dyDescent="0.3">
+      <c r="D26" s="4"/>
+      <c r="E26" t="s">
+        <v>14</v>
+      </c>
+      <c r="F26">
+        <v>0</v>
+      </c>
+      <c r="G26">
+        <v>5.473039</v>
+      </c>
+    </row>
+    <row r="27" spans="4:7" x14ac:dyDescent="0.3">
+      <c r="D27" s="4"/>
+      <c r="E27" t="s">
+        <v>15</v>
+      </c>
+      <c r="F27">
+        <v>0.65</v>
+      </c>
+      <c r="G27">
+        <v>1448.1409249999999</v>
+      </c>
+    </row>
+    <row r="28" spans="4:7" x14ac:dyDescent="0.3">
+      <c r="D28" s="5"/>
+      <c r="E28" s="5"/>
+      <c r="F28" s="5"/>
+      <c r="G28" s="5"/>
     </row>
   </sheetData>
-  <mergeCells count="4">
+  <mergeCells count="6">
+    <mergeCell ref="D28:G28"/>
     <mergeCell ref="D5:D11"/>
     <mergeCell ref="D12:G12"/>
     <mergeCell ref="D13:D19"/>
     <mergeCell ref="D20:G20"/>
+    <mergeCell ref="D21:D27"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -1246,7 +1553,7 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{AA9C7C1F-8E69-4E9D-9311-55B2096F876D}">
-  <dimension ref="D4:G20"/>
+  <dimension ref="D4:G28"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="4" max="4" width="16.33203125" customWidth="1"/>
@@ -1268,7 +1575,7 @@
       </c>
     </row>
     <row r="5" spans="4:7" x14ac:dyDescent="0.3">
-      <c r="D5" s="3">
+      <c r="D5" s="4">
         <v>1</v>
       </c>
       <c r="E5" t="s">
@@ -1282,7 +1589,7 @@
       </c>
     </row>
     <row r="6" spans="4:7" x14ac:dyDescent="0.3">
-      <c r="D6" s="3"/>
+      <c r="D6" s="4"/>
       <c r="E6" t="s">
         <v>10</v>
       </c>
@@ -1294,7 +1601,7 @@
       </c>
     </row>
     <row r="7" spans="4:7" x14ac:dyDescent="0.3">
-      <c r="D7" s="3"/>
+      <c r="D7" s="4"/>
       <c r="E7" t="s">
         <v>11</v>
       </c>
@@ -1306,7 +1613,7 @@
       </c>
     </row>
     <row r="8" spans="4:7" x14ac:dyDescent="0.3">
-      <c r="D8" s="3"/>
+      <c r="D8" s="4"/>
       <c r="E8" t="s">
         <v>12</v>
       </c>
@@ -1318,7 +1625,7 @@
       </c>
     </row>
     <row r="9" spans="4:7" x14ac:dyDescent="0.3">
-      <c r="D9" s="3"/>
+      <c r="D9" s="4"/>
       <c r="E9" t="s">
         <v>13</v>
       </c>
@@ -1330,7 +1637,7 @@
       </c>
     </row>
     <row r="10" spans="4:7" x14ac:dyDescent="0.3">
-      <c r="D10" s="3"/>
+      <c r="D10" s="4"/>
       <c r="E10" t="s">
         <v>14</v>
       </c>
@@ -1342,7 +1649,7 @@
       </c>
     </row>
     <row r="11" spans="4:7" x14ac:dyDescent="0.3">
-      <c r="D11" s="3"/>
+      <c r="D11" s="4"/>
       <c r="E11" t="s">
         <v>15</v>
       </c>
@@ -1354,13 +1661,13 @@
       </c>
     </row>
     <row r="12" spans="4:7" x14ac:dyDescent="0.3">
-      <c r="D12" s="5"/>
-      <c r="E12" s="5"/>
-      <c r="F12" s="5"/>
-      <c r="G12" s="5"/>
+      <c r="D12" s="6"/>
+      <c r="E12" s="6"/>
+      <c r="F12" s="6"/>
+      <c r="G12" s="6"/>
     </row>
     <row r="13" spans="4:7" x14ac:dyDescent="0.3">
-      <c r="D13" s="3">
+      <c r="D13" s="4">
         <v>2</v>
       </c>
       <c r="E13" t="s">
@@ -1374,7 +1681,7 @@
       </c>
     </row>
     <row r="14" spans="4:7" x14ac:dyDescent="0.3">
-      <c r="D14" s="3"/>
+      <c r="D14" s="4"/>
       <c r="E14" t="s">
         <v>10</v>
       </c>
@@ -1386,7 +1693,7 @@
       </c>
     </row>
     <row r="15" spans="4:7" x14ac:dyDescent="0.3">
-      <c r="D15" s="3"/>
+      <c r="D15" s="4"/>
       <c r="E15" t="s">
         <v>11</v>
       </c>
@@ -1398,7 +1705,7 @@
       </c>
     </row>
     <row r="16" spans="4:7" x14ac:dyDescent="0.3">
-      <c r="D16" s="3"/>
+      <c r="D16" s="4"/>
       <c r="E16" t="s">
         <v>12</v>
       </c>
@@ -1410,7 +1717,7 @@
       </c>
     </row>
     <row r="17" spans="4:7" x14ac:dyDescent="0.3">
-      <c r="D17" s="3"/>
+      <c r="D17" s="4"/>
       <c r="E17" t="s">
         <v>13</v>
       </c>
@@ -1422,7 +1729,7 @@
       </c>
     </row>
     <row r="18" spans="4:7" x14ac:dyDescent="0.3">
-      <c r="D18" s="3"/>
+      <c r="D18" s="4"/>
       <c r="E18" t="s">
         <v>14</v>
       </c>
@@ -1434,7 +1741,7 @@
       </c>
     </row>
     <row r="19" spans="4:7" x14ac:dyDescent="0.3">
-      <c r="D19" s="3"/>
+      <c r="D19" s="4"/>
       <c r="E19" t="s">
         <v>15</v>
       </c>
@@ -1446,17 +1753,111 @@
       </c>
     </row>
     <row r="20" spans="4:7" x14ac:dyDescent="0.3">
-      <c r="D20" s="4"/>
-      <c r="E20" s="4"/>
-      <c r="F20" s="4"/>
-      <c r="G20" s="4"/>
+      <c r="D20" s="5"/>
+      <c r="E20" s="5"/>
+      <c r="F20" s="5"/>
+      <c r="G20" s="5"/>
+    </row>
+    <row r="21" spans="4:7" x14ac:dyDescent="0.3">
+      <c r="D21" s="4">
+        <v>3</v>
+      </c>
+      <c r="E21" t="s">
+        <v>16</v>
+      </c>
+      <c r="F21">
+        <v>0.15</v>
+      </c>
+      <c r="G21">
+        <v>446.82893200000001</v>
+      </c>
+    </row>
+    <row r="22" spans="4:7" x14ac:dyDescent="0.3">
+      <c r="D22" s="4"/>
+      <c r="E22" t="s">
+        <v>10</v>
+      </c>
+      <c r="F22">
+        <v>0</v>
+      </c>
+      <c r="G22">
+        <v>263.68174299999998</v>
+      </c>
+    </row>
+    <row r="23" spans="4:7" x14ac:dyDescent="0.3">
+      <c r="D23" s="4"/>
+      <c r="E23" t="s">
+        <v>11</v>
+      </c>
+      <c r="F23">
+        <v>0</v>
+      </c>
+      <c r="G23">
+        <v>205.671415</v>
+      </c>
+    </row>
+    <row r="24" spans="4:7" x14ac:dyDescent="0.3">
+      <c r="D24" s="4"/>
+      <c r="E24" t="s">
+        <v>12</v>
+      </c>
+      <c r="F24">
+        <v>0</v>
+      </c>
+      <c r="G24">
+        <v>229.85868300000001</v>
+      </c>
+    </row>
+    <row r="25" spans="4:7" x14ac:dyDescent="0.3">
+      <c r="D25" s="4"/>
+      <c r="E25" t="s">
+        <v>13</v>
+      </c>
+      <c r="F25">
+        <v>0.05</v>
+      </c>
+      <c r="G25">
+        <v>285.54760499999998</v>
+      </c>
+    </row>
+    <row r="26" spans="4:7" x14ac:dyDescent="0.3">
+      <c r="D26" s="4"/>
+      <c r="E26" t="s">
+        <v>14</v>
+      </c>
+      <c r="F26">
+        <v>0</v>
+      </c>
+      <c r="G26">
+        <v>30.406841</v>
+      </c>
+    </row>
+    <row r="27" spans="4:7" x14ac:dyDescent="0.3">
+      <c r="D27" s="4"/>
+      <c r="E27" t="s">
+        <v>15</v>
+      </c>
+      <c r="F27">
+        <v>0.1</v>
+      </c>
+      <c r="G27">
+        <v>389.80510199999998</v>
+      </c>
+    </row>
+    <row r="28" spans="4:7" x14ac:dyDescent="0.3">
+      <c r="D28" s="5"/>
+      <c r="E28" s="5"/>
+      <c r="F28" s="5"/>
+      <c r="G28" s="5"/>
     </row>
   </sheetData>
-  <mergeCells count="4">
+  <mergeCells count="6">
+    <mergeCell ref="D28:G28"/>
     <mergeCell ref="D5:D11"/>
     <mergeCell ref="D12:G12"/>
     <mergeCell ref="D20:G20"/>
     <mergeCell ref="D13:D19"/>
+    <mergeCell ref="D21:D27"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/shatrov_bootstraps_res.xlsx
+++ b/shatrov_bootstraps_res.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Игорь\Desktop\sem_8\mipt_diplom\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C6D47663-394C-4FCE-AA78-3825534A79C1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{997BDE62-46C6-46C8-83B1-A37809988675}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Информация про ряды" sheetId="1" r:id="rId1"/>
@@ -29,7 +29,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="120" uniqueCount="27">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="153" uniqueCount="30">
   <si>
     <t>Номер</t>
   </si>
@@ -110,6 +110,15 @@
   </si>
   <si>
     <t>Почему-то для этого ряда методы ML сработали лучше, чем ARIMA/SARIMA</t>
+  </si>
+  <si>
+    <t>Monthly Robberies</t>
+  </si>
+  <si>
+    <t>https://raw.githubusercontent.com/jbrownlee/Datasets/master/monthly-robberies.csv</t>
+  </si>
+  <si>
+    <t>Отсутствует сезонность. Похож на сумму тренда и случайного блуждания</t>
   </si>
 </sst>
 </file>
@@ -174,23 +183,20 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="8">
+  <cellXfs count="7">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
   </cellXfs>
@@ -473,7 +479,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="D4:G7"/>
+  <dimension ref="D4:G8"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="6" max="6" width="8.88671875" customWidth="1"/>
@@ -535,6 +541,20 @@
         <v>26</v>
       </c>
     </row>
+    <row r="8" spans="4:7" x14ac:dyDescent="0.3">
+      <c r="D8">
+        <v>4</v>
+      </c>
+      <c r="E8" t="s">
+        <v>27</v>
+      </c>
+      <c r="F8" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="G8" t="s">
+        <v>29</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -542,7 +562,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5432242B-BB45-4574-A5B4-2CF25C9CDCFF}">
-  <dimension ref="D4:H31"/>
+  <dimension ref="D4:H40"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="4" max="4" width="13.21875" customWidth="1"/>
@@ -564,7 +584,7 @@
       </c>
     </row>
     <row r="5" spans="4:7" x14ac:dyDescent="0.3">
-      <c r="D5" s="4">
+      <c r="D5" s="5">
         <v>1</v>
       </c>
       <c r="E5" t="s">
@@ -578,7 +598,7 @@
       </c>
     </row>
     <row r="6" spans="4:7" x14ac:dyDescent="0.3">
-      <c r="D6" s="4"/>
+      <c r="D6" s="5"/>
       <c r="E6" t="s">
         <v>16</v>
       </c>
@@ -590,7 +610,7 @@
       </c>
     </row>
     <row r="7" spans="4:7" x14ac:dyDescent="0.3">
-      <c r="D7" s="4"/>
+      <c r="D7" s="5"/>
       <c r="E7" t="s">
         <v>10</v>
       </c>
@@ -602,7 +622,7 @@
       </c>
     </row>
     <row r="8" spans="4:7" x14ac:dyDescent="0.3">
-      <c r="D8" s="4"/>
+      <c r="D8" s="5"/>
       <c r="E8" t="s">
         <v>11</v>
       </c>
@@ -614,7 +634,7 @@
       </c>
     </row>
     <row r="9" spans="4:7" x14ac:dyDescent="0.3">
-      <c r="D9" s="4"/>
+      <c r="D9" s="5"/>
       <c r="E9" t="s">
         <v>12</v>
       </c>
@@ -626,7 +646,7 @@
       </c>
     </row>
     <row r="10" spans="4:7" x14ac:dyDescent="0.3">
-      <c r="D10" s="4"/>
+      <c r="D10" s="5"/>
       <c r="E10" t="s">
         <v>13</v>
       </c>
@@ -638,7 +658,7 @@
       </c>
     </row>
     <row r="11" spans="4:7" x14ac:dyDescent="0.3">
-      <c r="D11" s="4"/>
+      <c r="D11" s="5"/>
       <c r="E11" t="s">
         <v>14</v>
       </c>
@@ -650,7 +670,7 @@
       </c>
     </row>
     <row r="12" spans="4:7" x14ac:dyDescent="0.3">
-      <c r="D12" s="4"/>
+      <c r="D12" s="5"/>
       <c r="E12" t="s">
         <v>15</v>
       </c>
@@ -662,13 +682,13 @@
       </c>
     </row>
     <row r="13" spans="4:7" x14ac:dyDescent="0.3">
-      <c r="D13" s="5"/>
-      <c r="E13" s="5"/>
-      <c r="F13" s="5"/>
-      <c r="G13" s="5"/>
+      <c r="D13" s="4"/>
+      <c r="E13" s="4"/>
+      <c r="F13" s="4"/>
+      <c r="G13" s="4"/>
     </row>
     <row r="14" spans="4:7" x14ac:dyDescent="0.3">
-      <c r="D14" s="4">
+      <c r="D14" s="5">
         <v>2</v>
       </c>
       <c r="E14" t="s">
@@ -682,7 +702,7 @@
       </c>
     </row>
     <row r="15" spans="4:7" x14ac:dyDescent="0.3">
-      <c r="D15" s="4"/>
+      <c r="D15" s="5"/>
       <c r="E15" t="s">
         <v>16</v>
       </c>
@@ -694,7 +714,7 @@
       </c>
     </row>
     <row r="16" spans="4:7" x14ac:dyDescent="0.3">
-      <c r="D16" s="4"/>
+      <c r="D16" s="5"/>
       <c r="E16" t="s">
         <v>10</v>
       </c>
@@ -706,7 +726,7 @@
       </c>
     </row>
     <row r="17" spans="4:8" x14ac:dyDescent="0.3">
-      <c r="D17" s="4"/>
+      <c r="D17" s="5"/>
       <c r="E17" t="s">
         <v>11</v>
       </c>
@@ -718,7 +738,7 @@
       </c>
     </row>
     <row r="18" spans="4:8" x14ac:dyDescent="0.3">
-      <c r="D18" s="4"/>
+      <c r="D18" s="5"/>
       <c r="E18" t="s">
         <v>12</v>
       </c>
@@ -730,7 +750,7 @@
       </c>
     </row>
     <row r="19" spans="4:8" x14ac:dyDescent="0.3">
-      <c r="D19" s="4"/>
+      <c r="D19" s="5"/>
       <c r="E19" t="s">
         <v>13</v>
       </c>
@@ -742,7 +762,7 @@
       </c>
     </row>
     <row r="20" spans="4:8" x14ac:dyDescent="0.3">
-      <c r="D20" s="4"/>
+      <c r="D20" s="5"/>
       <c r="E20" t="s">
         <v>14</v>
       </c>
@@ -754,7 +774,7 @@
       </c>
     </row>
     <row r="21" spans="4:8" x14ac:dyDescent="0.3">
-      <c r="D21" s="4"/>
+      <c r="D21" s="5"/>
       <c r="E21" t="s">
         <v>15</v>
       </c>
@@ -766,13 +786,13 @@
       </c>
     </row>
     <row r="22" spans="4:8" x14ac:dyDescent="0.3">
-      <c r="D22" s="5"/>
-      <c r="E22" s="5"/>
-      <c r="F22" s="5"/>
-      <c r="G22" s="5"/>
+      <c r="D22" s="4"/>
+      <c r="E22" s="4"/>
+      <c r="F22" s="4"/>
+      <c r="G22" s="4"/>
     </row>
     <row r="23" spans="4:8" x14ac:dyDescent="0.3">
-      <c r="D23" s="4">
+      <c r="D23" s="5">
         <v>3</v>
       </c>
       <c r="E23" t="s">
@@ -789,7 +809,7 @@
       </c>
     </row>
     <row r="24" spans="4:8" x14ac:dyDescent="0.3">
-      <c r="D24" s="4"/>
+      <c r="D24" s="5"/>
       <c r="E24" t="s">
         <v>16</v>
       </c>
@@ -801,7 +821,7 @@
       </c>
     </row>
     <row r="25" spans="4:8" x14ac:dyDescent="0.3">
-      <c r="D25" s="4"/>
+      <c r="D25" s="5"/>
       <c r="E25" t="s">
         <v>10</v>
       </c>
@@ -813,7 +833,7 @@
       </c>
     </row>
     <row r="26" spans="4:8" x14ac:dyDescent="0.3">
-      <c r="D26" s="4"/>
+      <c r="D26" s="5"/>
       <c r="E26" t="s">
         <v>11</v>
       </c>
@@ -825,7 +845,7 @@
       </c>
     </row>
     <row r="27" spans="4:8" x14ac:dyDescent="0.3">
-      <c r="D27" s="4"/>
+      <c r="D27" s="5"/>
       <c r="E27" t="s">
         <v>12</v>
       </c>
@@ -837,7 +857,7 @@
       </c>
     </row>
     <row r="28" spans="4:8" x14ac:dyDescent="0.3">
-      <c r="D28" s="4"/>
+      <c r="D28" s="5"/>
       <c r="E28" t="s">
         <v>13</v>
       </c>
@@ -849,7 +869,7 @@
       </c>
     </row>
     <row r="29" spans="4:8" x14ac:dyDescent="0.3">
-      <c r="D29" s="4"/>
+      <c r="D29" s="5"/>
       <c r="E29" t="s">
         <v>14</v>
       </c>
@@ -861,7 +881,7 @@
       </c>
     </row>
     <row r="30" spans="4:8" x14ac:dyDescent="0.3">
-      <c r="D30" s="4"/>
+      <c r="D30" s="5"/>
       <c r="E30" t="s">
         <v>15</v>
       </c>
@@ -873,13 +893,119 @@
       </c>
     </row>
     <row r="31" spans="4:8" x14ac:dyDescent="0.3">
-      <c r="D31" s="7"/>
-      <c r="E31" s="7"/>
-      <c r="F31" s="7"/>
-      <c r="G31" s="7"/>
+      <c r="D31" s="4"/>
+      <c r="E31" s="4"/>
+      <c r="F31" s="4"/>
+      <c r="G31" s="4"/>
+    </row>
+    <row r="32" spans="4:8" x14ac:dyDescent="0.3">
+      <c r="D32" s="5">
+        <v>4</v>
+      </c>
+      <c r="E32" t="s">
+        <v>9</v>
+      </c>
+      <c r="F32">
+        <v>0.83333299999999999</v>
+      </c>
+      <c r="G32">
+        <v>186.34364600000001</v>
+      </c>
+    </row>
+    <row r="33" spans="4:7" x14ac:dyDescent="0.3">
+      <c r="D33" s="5"/>
+      <c r="E33" t="s">
+        <v>16</v>
+      </c>
+      <c r="F33">
+        <v>0.83333299999999999</v>
+      </c>
+      <c r="G33">
+        <v>184.746667</v>
+      </c>
+    </row>
+    <row r="34" spans="4:7" x14ac:dyDescent="0.3">
+      <c r="D34" s="5"/>
+      <c r="E34" t="s">
+        <v>10</v>
+      </c>
+      <c r="F34">
+        <v>0.83333299999999999</v>
+      </c>
+      <c r="G34">
+        <v>189.48801599999999</v>
+      </c>
+    </row>
+    <row r="35" spans="4:7" x14ac:dyDescent="0.3">
+      <c r="D35" s="5"/>
+      <c r="E35" t="s">
+        <v>11</v>
+      </c>
+      <c r="F35">
+        <v>0.83333299999999999</v>
+      </c>
+      <c r="G35">
+        <v>187.15413699999999</v>
+      </c>
+    </row>
+    <row r="36" spans="4:7" x14ac:dyDescent="0.3">
+      <c r="D36" s="5"/>
+      <c r="E36" t="s">
+        <v>12</v>
+      </c>
+      <c r="F36">
+        <v>0.83333299999999999</v>
+      </c>
+      <c r="G36">
+        <v>183.13261199999999</v>
+      </c>
+    </row>
+    <row r="37" spans="4:7" x14ac:dyDescent="0.3">
+      <c r="D37" s="5"/>
+      <c r="E37" t="s">
+        <v>13</v>
+      </c>
+      <c r="F37">
+        <v>0.58333299999999999</v>
+      </c>
+      <c r="G37">
+        <v>122.946945</v>
+      </c>
+    </row>
+    <row r="38" spans="4:7" x14ac:dyDescent="0.3">
+      <c r="D38" s="5"/>
+      <c r="E38" t="s">
+        <v>14</v>
+      </c>
+      <c r="F38">
+        <v>0.83333299999999999</v>
+      </c>
+      <c r="G38">
+        <v>183.46469400000001</v>
+      </c>
+    </row>
+    <row r="39" spans="4:7" x14ac:dyDescent="0.3">
+      <c r="D39" s="5"/>
+      <c r="E39" t="s">
+        <v>15</v>
+      </c>
+      <c r="F39">
+        <v>0.83333299999999999</v>
+      </c>
+      <c r="G39">
+        <v>186.87345400000001</v>
+      </c>
+    </row>
+    <row r="40" spans="4:7" x14ac:dyDescent="0.3">
+      <c r="D40" s="4"/>
+      <c r="E40" s="4"/>
+      <c r="F40" s="4"/>
+      <c r="G40" s="4"/>
     </row>
   </sheetData>
-  <mergeCells count="6">
+  <mergeCells count="8">
+    <mergeCell ref="D32:D39"/>
+    <mergeCell ref="D40:G40"/>
     <mergeCell ref="D31:G31"/>
     <mergeCell ref="D5:D12"/>
     <mergeCell ref="D13:G13"/>
@@ -893,7 +1019,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D9F3D6F7-9B83-4803-A2A9-5F6E3F05FBE9}">
-  <dimension ref="D4:G31"/>
+  <dimension ref="D4:G40"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="4" max="4" width="13.21875" customWidth="1"/>
@@ -915,7 +1041,7 @@
       </c>
     </row>
     <row r="5" spans="4:7" x14ac:dyDescent="0.3">
-      <c r="D5" s="4">
+      <c r="D5" s="5">
         <v>1</v>
       </c>
       <c r="E5" t="s">
@@ -929,7 +1055,7 @@
       </c>
     </row>
     <row r="6" spans="4:7" x14ac:dyDescent="0.3">
-      <c r="D6" s="4"/>
+      <c r="D6" s="5"/>
       <c r="E6" t="s">
         <v>16</v>
       </c>
@@ -941,7 +1067,7 @@
       </c>
     </row>
     <row r="7" spans="4:7" x14ac:dyDescent="0.3">
-      <c r="D7" s="4"/>
+      <c r="D7" s="5"/>
       <c r="E7" t="s">
         <v>10</v>
       </c>
@@ -953,7 +1079,7 @@
       </c>
     </row>
     <row r="8" spans="4:7" x14ac:dyDescent="0.3">
-      <c r="D8" s="4"/>
+      <c r="D8" s="5"/>
       <c r="E8" t="s">
         <v>11</v>
       </c>
@@ -965,7 +1091,7 @@
       </c>
     </row>
     <row r="9" spans="4:7" x14ac:dyDescent="0.3">
-      <c r="D9" s="4"/>
+      <c r="D9" s="5"/>
       <c r="E9" t="s">
         <v>12</v>
       </c>
@@ -977,7 +1103,7 @@
       </c>
     </row>
     <row r="10" spans="4:7" x14ac:dyDescent="0.3">
-      <c r="D10" s="4"/>
+      <c r="D10" s="5"/>
       <c r="E10" t="s">
         <v>13</v>
       </c>
@@ -989,7 +1115,7 @@
       </c>
     </row>
     <row r="11" spans="4:7" x14ac:dyDescent="0.3">
-      <c r="D11" s="4"/>
+      <c r="D11" s="5"/>
       <c r="E11" t="s">
         <v>14</v>
       </c>
@@ -1001,7 +1127,7 @@
       </c>
     </row>
     <row r="12" spans="4:7" x14ac:dyDescent="0.3">
-      <c r="D12" s="4"/>
+      <c r="D12" s="5"/>
       <c r="E12" t="s">
         <v>15</v>
       </c>
@@ -1013,13 +1139,13 @@
       </c>
     </row>
     <row r="13" spans="4:7" x14ac:dyDescent="0.3">
-      <c r="D13" s="5"/>
-      <c r="E13" s="5"/>
-      <c r="F13" s="5"/>
-      <c r="G13" s="5"/>
+      <c r="D13" s="4"/>
+      <c r="E13" s="4"/>
+      <c r="F13" s="4"/>
+      <c r="G13" s="4"/>
     </row>
     <row r="14" spans="4:7" x14ac:dyDescent="0.3">
-      <c r="D14" s="4">
+      <c r="D14" s="5">
         <v>2</v>
       </c>
       <c r="E14" t="s">
@@ -1033,7 +1159,7 @@
       </c>
     </row>
     <row r="15" spans="4:7" x14ac:dyDescent="0.3">
-      <c r="D15" s="4"/>
+      <c r="D15" s="5"/>
       <c r="E15" t="s">
         <v>16</v>
       </c>
@@ -1045,7 +1171,7 @@
       </c>
     </row>
     <row r="16" spans="4:7" x14ac:dyDescent="0.3">
-      <c r="D16" s="4"/>
+      <c r="D16" s="5"/>
       <c r="E16" t="s">
         <v>10</v>
       </c>
@@ -1057,7 +1183,7 @@
       </c>
     </row>
     <row r="17" spans="4:7" x14ac:dyDescent="0.3">
-      <c r="D17" s="4"/>
+      <c r="D17" s="5"/>
       <c r="E17" t="s">
         <v>11</v>
       </c>
@@ -1069,7 +1195,7 @@
       </c>
     </row>
     <row r="18" spans="4:7" x14ac:dyDescent="0.3">
-      <c r="D18" s="4"/>
+      <c r="D18" s="5"/>
       <c r="E18" t="s">
         <v>12</v>
       </c>
@@ -1081,7 +1207,7 @@
       </c>
     </row>
     <row r="19" spans="4:7" x14ac:dyDescent="0.3">
-      <c r="D19" s="4"/>
+      <c r="D19" s="5"/>
       <c r="E19" s="3" t="s">
         <v>13</v>
       </c>
@@ -1093,7 +1219,7 @@
       </c>
     </row>
     <row r="20" spans="4:7" x14ac:dyDescent="0.3">
-      <c r="D20" s="4"/>
+      <c r="D20" s="5"/>
       <c r="E20" t="s">
         <v>14</v>
       </c>
@@ -1105,7 +1231,7 @@
       </c>
     </row>
     <row r="21" spans="4:7" x14ac:dyDescent="0.3">
-      <c r="D21" s="4"/>
+      <c r="D21" s="5"/>
       <c r="E21" t="s">
         <v>15</v>
       </c>
@@ -1117,13 +1243,13 @@
       </c>
     </row>
     <row r="22" spans="4:7" x14ac:dyDescent="0.3">
-      <c r="D22" s="5"/>
-      <c r="E22" s="5"/>
-      <c r="F22" s="5"/>
-      <c r="G22" s="5"/>
+      <c r="D22" s="4"/>
+      <c r="E22" s="4"/>
+      <c r="F22" s="4"/>
+      <c r="G22" s="4"/>
     </row>
     <row r="23" spans="4:7" x14ac:dyDescent="0.3">
-      <c r="D23" s="4">
+      <c r="D23" s="5">
         <v>3</v>
       </c>
       <c r="E23" t="s">
@@ -1137,7 +1263,7 @@
       </c>
     </row>
     <row r="24" spans="4:7" x14ac:dyDescent="0.3">
-      <c r="D24" s="4"/>
+      <c r="D24" s="5"/>
       <c r="E24" t="s">
         <v>16</v>
       </c>
@@ -1149,7 +1275,7 @@
       </c>
     </row>
     <row r="25" spans="4:7" x14ac:dyDescent="0.3">
-      <c r="D25" s="4"/>
+      <c r="D25" s="5"/>
       <c r="E25" t="s">
         <v>10</v>
       </c>
@@ -1161,7 +1287,7 @@
       </c>
     </row>
     <row r="26" spans="4:7" x14ac:dyDescent="0.3">
-      <c r="D26" s="4"/>
+      <c r="D26" s="5"/>
       <c r="E26" t="s">
         <v>11</v>
       </c>
@@ -1173,7 +1299,7 @@
       </c>
     </row>
     <row r="27" spans="4:7" x14ac:dyDescent="0.3">
-      <c r="D27" s="4"/>
+      <c r="D27" s="5"/>
       <c r="E27" t="s">
         <v>12</v>
       </c>
@@ -1185,7 +1311,7 @@
       </c>
     </row>
     <row r="28" spans="4:7" x14ac:dyDescent="0.3">
-      <c r="D28" s="4"/>
+      <c r="D28" s="5"/>
       <c r="E28" t="s">
         <v>13</v>
       </c>
@@ -1197,7 +1323,7 @@
       </c>
     </row>
     <row r="29" spans="4:7" x14ac:dyDescent="0.3">
-      <c r="D29" s="4"/>
+      <c r="D29" s="5"/>
       <c r="E29" t="s">
         <v>14</v>
       </c>
@@ -1209,7 +1335,7 @@
       </c>
     </row>
     <row r="30" spans="4:7" x14ac:dyDescent="0.3">
-      <c r="D30" s="4"/>
+      <c r="D30" s="5"/>
       <c r="E30" t="s">
         <v>15</v>
       </c>
@@ -1221,13 +1347,119 @@
       </c>
     </row>
     <row r="31" spans="4:7" x14ac:dyDescent="0.3">
-      <c r="D31" s="5"/>
-      <c r="E31" s="5"/>
-      <c r="F31" s="5"/>
-      <c r="G31" s="5"/>
+      <c r="D31" s="4"/>
+      <c r="E31" s="4"/>
+      <c r="F31" s="4"/>
+      <c r="G31" s="4"/>
+    </row>
+    <row r="32" spans="4:7" x14ac:dyDescent="0.3">
+      <c r="D32" s="5">
+        <v>4</v>
+      </c>
+      <c r="E32" t="s">
+        <v>17</v>
+      </c>
+      <c r="F32" s="2">
+        <v>1</v>
+      </c>
+      <c r="G32" s="2">
+        <v>840.34417199999996</v>
+      </c>
+    </row>
+    <row r="33" spans="4:7" x14ac:dyDescent="0.3">
+      <c r="D33" s="5"/>
+      <c r="E33" t="s">
+        <v>16</v>
+      </c>
+      <c r="F33" s="2">
+        <v>1</v>
+      </c>
+      <c r="G33" s="2">
+        <v>812.39180299999998</v>
+      </c>
+    </row>
+    <row r="34" spans="4:7" x14ac:dyDescent="0.3">
+      <c r="D34" s="5"/>
+      <c r="E34" t="s">
+        <v>10</v>
+      </c>
+      <c r="F34" s="2">
+        <v>1</v>
+      </c>
+      <c r="G34" s="2">
+        <v>841.59871699999997</v>
+      </c>
+    </row>
+    <row r="35" spans="4:7" x14ac:dyDescent="0.3">
+      <c r="D35" s="5"/>
+      <c r="E35" t="s">
+        <v>11</v>
+      </c>
+      <c r="F35" s="2">
+        <v>1</v>
+      </c>
+      <c r="G35" s="2">
+        <v>786.86640899999998</v>
+      </c>
+    </row>
+    <row r="36" spans="4:7" x14ac:dyDescent="0.3">
+      <c r="D36" s="5"/>
+      <c r="E36" t="s">
+        <v>12</v>
+      </c>
+      <c r="F36" s="2">
+        <v>1</v>
+      </c>
+      <c r="G36" s="2">
+        <v>852.16210899999999</v>
+      </c>
+    </row>
+    <row r="37" spans="4:7" x14ac:dyDescent="0.3">
+      <c r="D37" s="5"/>
+      <c r="E37" t="s">
+        <v>13</v>
+      </c>
+      <c r="F37" s="2">
+        <v>0.83333299999999999</v>
+      </c>
+      <c r="G37" s="2">
+        <v>171.405417</v>
+      </c>
+    </row>
+    <row r="38" spans="4:7" x14ac:dyDescent="0.3">
+      <c r="D38" s="5"/>
+      <c r="E38" t="s">
+        <v>14</v>
+      </c>
+      <c r="F38" s="2">
+        <v>1</v>
+      </c>
+      <c r="G38" s="2">
+        <v>835.86260600000003</v>
+      </c>
+    </row>
+    <row r="39" spans="4:7" x14ac:dyDescent="0.3">
+      <c r="D39" s="5"/>
+      <c r="E39" t="s">
+        <v>15</v>
+      </c>
+      <c r="F39" s="2">
+        <v>1</v>
+      </c>
+      <c r="G39" s="2">
+        <v>849.79519800000003</v>
+      </c>
+    </row>
+    <row r="40" spans="4:7" x14ac:dyDescent="0.3">
+      <c r="D40" s="4"/>
+      <c r="E40" s="4"/>
+      <c r="F40" s="4"/>
+      <c r="G40" s="4"/>
     </row>
   </sheetData>
-  <mergeCells count="6">
+  <mergeCells count="8">
+    <mergeCell ref="D32:D39"/>
+    <mergeCell ref="D40:G40"/>
     <mergeCell ref="D31:G31"/>
     <mergeCell ref="D5:D12"/>
     <mergeCell ref="D13:G13"/>
@@ -1241,7 +1473,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D9B1F934-9143-4061-8956-2969F906ECCB}">
-  <dimension ref="D4:G28"/>
+  <dimension ref="D4:G36"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="4" max="4" width="16.33203125" customWidth="1"/>
@@ -1263,7 +1495,7 @@
       </c>
     </row>
     <row r="5" spans="4:7" x14ac:dyDescent="0.3">
-      <c r="D5" s="4">
+      <c r="D5" s="5">
         <v>1</v>
       </c>
       <c r="E5" t="s">
@@ -1277,7 +1509,7 @@
       </c>
     </row>
     <row r="6" spans="4:7" x14ac:dyDescent="0.3">
-      <c r="D6" s="4"/>
+      <c r="D6" s="5"/>
       <c r="E6" t="s">
         <v>10</v>
       </c>
@@ -1289,7 +1521,7 @@
       </c>
     </row>
     <row r="7" spans="4:7" x14ac:dyDescent="0.3">
-      <c r="D7" s="4"/>
+      <c r="D7" s="5"/>
       <c r="E7" t="s">
         <v>11</v>
       </c>
@@ -1301,7 +1533,7 @@
       </c>
     </row>
     <row r="8" spans="4:7" x14ac:dyDescent="0.3">
-      <c r="D8" s="4"/>
+      <c r="D8" s="5"/>
       <c r="E8" t="s">
         <v>12</v>
       </c>
@@ -1313,7 +1545,7 @@
       </c>
     </row>
     <row r="9" spans="4:7" x14ac:dyDescent="0.3">
-      <c r="D9" s="4"/>
+      <c r="D9" s="5"/>
       <c r="E9" t="s">
         <v>13</v>
       </c>
@@ -1325,7 +1557,7 @@
       </c>
     </row>
     <row r="10" spans="4:7" x14ac:dyDescent="0.3">
-      <c r="D10" s="4"/>
+      <c r="D10" s="5"/>
       <c r="E10" t="s">
         <v>14</v>
       </c>
@@ -1337,7 +1569,7 @@
       </c>
     </row>
     <row r="11" spans="4:7" x14ac:dyDescent="0.3">
-      <c r="D11" s="4"/>
+      <c r="D11" s="5"/>
       <c r="E11" t="s">
         <v>15</v>
       </c>
@@ -1355,7 +1587,7 @@
       <c r="G12" s="6"/>
     </row>
     <row r="13" spans="4:7" x14ac:dyDescent="0.3">
-      <c r="D13" s="4">
+      <c r="D13" s="5">
         <v>2</v>
       </c>
       <c r="E13" t="s">
@@ -1369,7 +1601,7 @@
       </c>
     </row>
     <row r="14" spans="4:7" x14ac:dyDescent="0.3">
-      <c r="D14" s="4"/>
+      <c r="D14" s="5"/>
       <c r="E14" t="s">
         <v>10</v>
       </c>
@@ -1381,7 +1613,7 @@
       </c>
     </row>
     <row r="15" spans="4:7" x14ac:dyDescent="0.3">
-      <c r="D15" s="4"/>
+      <c r="D15" s="5"/>
       <c r="E15" t="s">
         <v>11</v>
       </c>
@@ -1393,7 +1625,7 @@
       </c>
     </row>
     <row r="16" spans="4:7" x14ac:dyDescent="0.3">
-      <c r="D16" s="4"/>
+      <c r="D16" s="5"/>
       <c r="E16" t="s">
         <v>12</v>
       </c>
@@ -1405,7 +1637,7 @@
       </c>
     </row>
     <row r="17" spans="4:7" x14ac:dyDescent="0.3">
-      <c r="D17" s="4"/>
+      <c r="D17" s="5"/>
       <c r="E17" t="s">
         <v>13</v>
       </c>
@@ -1417,7 +1649,7 @@
       </c>
     </row>
     <row r="18" spans="4:7" x14ac:dyDescent="0.3">
-      <c r="D18" s="4"/>
+      <c r="D18" s="5"/>
       <c r="E18" t="s">
         <v>14</v>
       </c>
@@ -1429,7 +1661,7 @@
       </c>
     </row>
     <row r="19" spans="4:7" x14ac:dyDescent="0.3">
-      <c r="D19" s="4"/>
+      <c r="D19" s="5"/>
       <c r="E19" t="s">
         <v>15</v>
       </c>
@@ -1441,13 +1673,13 @@
       </c>
     </row>
     <row r="20" spans="4:7" x14ac:dyDescent="0.3">
-      <c r="D20" s="5"/>
-      <c r="E20" s="5"/>
-      <c r="F20" s="5"/>
-      <c r="G20" s="5"/>
+      <c r="D20" s="4"/>
+      <c r="E20" s="4"/>
+      <c r="F20" s="4"/>
+      <c r="G20" s="4"/>
     </row>
     <row r="21" spans="4:7" x14ac:dyDescent="0.3">
-      <c r="D21" s="4">
+      <c r="D21" s="5">
         <v>3</v>
       </c>
       <c r="E21" t="s">
@@ -1461,7 +1693,7 @@
       </c>
     </row>
     <row r="22" spans="4:7" x14ac:dyDescent="0.3">
-      <c r="D22" s="4"/>
+      <c r="D22" s="5"/>
       <c r="E22" t="s">
         <v>10</v>
       </c>
@@ -1473,7 +1705,7 @@
       </c>
     </row>
     <row r="23" spans="4:7" x14ac:dyDescent="0.3">
-      <c r="D23" s="4"/>
+      <c r="D23" s="5"/>
       <c r="E23" t="s">
         <v>11</v>
       </c>
@@ -1485,7 +1717,7 @@
       </c>
     </row>
     <row r="24" spans="4:7" x14ac:dyDescent="0.3">
-      <c r="D24" s="4"/>
+      <c r="D24" s="5"/>
       <c r="E24" t="s">
         <v>12</v>
       </c>
@@ -1497,7 +1729,7 @@
       </c>
     </row>
     <row r="25" spans="4:7" x14ac:dyDescent="0.3">
-      <c r="D25" s="4"/>
+      <c r="D25" s="5"/>
       <c r="E25" t="s">
         <v>13</v>
       </c>
@@ -1509,7 +1741,7 @@
       </c>
     </row>
     <row r="26" spans="4:7" x14ac:dyDescent="0.3">
-      <c r="D26" s="4"/>
+      <c r="D26" s="5"/>
       <c r="E26" t="s">
         <v>14</v>
       </c>
@@ -1521,7 +1753,7 @@
       </c>
     </row>
     <row r="27" spans="4:7" x14ac:dyDescent="0.3">
-      <c r="D27" s="4"/>
+      <c r="D27" s="5"/>
       <c r="E27" t="s">
         <v>15</v>
       </c>
@@ -1533,13 +1765,107 @@
       </c>
     </row>
     <row r="28" spans="4:7" x14ac:dyDescent="0.3">
-      <c r="D28" s="5"/>
-      <c r="E28" s="5"/>
-      <c r="F28" s="5"/>
-      <c r="G28" s="5"/>
+      <c r="D28" s="4"/>
+      <c r="E28" s="4"/>
+      <c r="F28" s="4"/>
+      <c r="G28" s="4"/>
+    </row>
+    <row r="29" spans="4:7" x14ac:dyDescent="0.3">
+      <c r="D29" s="5">
+        <v>4</v>
+      </c>
+      <c r="E29" t="s">
+        <v>16</v>
+      </c>
+      <c r="F29">
+        <v>0.25</v>
+      </c>
+      <c r="G29">
+        <v>58.867489999999997</v>
+      </c>
+    </row>
+    <row r="30" spans="4:7" x14ac:dyDescent="0.3">
+      <c r="D30" s="5"/>
+      <c r="E30" t="s">
+        <v>10</v>
+      </c>
+      <c r="F30">
+        <v>0.20833299999999999</v>
+      </c>
+      <c r="G30">
+        <v>46.697495000000004</v>
+      </c>
+    </row>
+    <row r="31" spans="4:7" x14ac:dyDescent="0.3">
+      <c r="D31" s="5"/>
+      <c r="E31" t="s">
+        <v>11</v>
+      </c>
+      <c r="F31">
+        <v>0.16666700000000001</v>
+      </c>
+      <c r="G31">
+        <v>23.463401999999999</v>
+      </c>
+    </row>
+    <row r="32" spans="4:7" x14ac:dyDescent="0.3">
+      <c r="D32" s="5"/>
+      <c r="E32" t="s">
+        <v>12</v>
+      </c>
+      <c r="F32">
+        <v>0.125</v>
+      </c>
+      <c r="G32">
+        <v>20.009763</v>
+      </c>
+    </row>
+    <row r="33" spans="4:7" x14ac:dyDescent="0.3">
+      <c r="D33" s="5"/>
+      <c r="E33" t="s">
+        <v>13</v>
+      </c>
+      <c r="F33">
+        <v>0.25</v>
+      </c>
+      <c r="G33">
+        <v>54.664957999999999</v>
+      </c>
+    </row>
+    <row r="34" spans="4:7" x14ac:dyDescent="0.3">
+      <c r="D34" s="5"/>
+      <c r="E34" t="s">
+        <v>14</v>
+      </c>
+      <c r="F34">
+        <v>0</v>
+      </c>
+      <c r="G34">
+        <v>5.7547449999999998</v>
+      </c>
+    </row>
+    <row r="35" spans="4:7" x14ac:dyDescent="0.3">
+      <c r="D35" s="5"/>
+      <c r="E35" t="s">
+        <v>15</v>
+      </c>
+      <c r="F35">
+        <v>0.20833299999999999</v>
+      </c>
+      <c r="G35">
+        <v>55.995865000000002</v>
+      </c>
+    </row>
+    <row r="36" spans="4:7" x14ac:dyDescent="0.3">
+      <c r="D36" s="4"/>
+      <c r="E36" s="4"/>
+      <c r="F36" s="4"/>
+      <c r="G36" s="4"/>
     </row>
   </sheetData>
-  <mergeCells count="6">
+  <mergeCells count="8">
+    <mergeCell ref="D29:D35"/>
+    <mergeCell ref="D36:G36"/>
     <mergeCell ref="D28:G28"/>
     <mergeCell ref="D5:D11"/>
     <mergeCell ref="D12:G12"/>
@@ -1553,7 +1879,7 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{AA9C7C1F-8E69-4E9D-9311-55B2096F876D}">
-  <dimension ref="D4:G28"/>
+  <dimension ref="D4:G36"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="4" max="4" width="16.33203125" customWidth="1"/>
@@ -1575,7 +1901,7 @@
       </c>
     </row>
     <row r="5" spans="4:7" x14ac:dyDescent="0.3">
-      <c r="D5" s="4">
+      <c r="D5" s="5">
         <v>1</v>
       </c>
       <c r="E5" t="s">
@@ -1589,7 +1915,7 @@
       </c>
     </row>
     <row r="6" spans="4:7" x14ac:dyDescent="0.3">
-      <c r="D6" s="4"/>
+      <c r="D6" s="5"/>
       <c r="E6" t="s">
         <v>10</v>
       </c>
@@ -1601,7 +1927,7 @@
       </c>
     </row>
     <row r="7" spans="4:7" x14ac:dyDescent="0.3">
-      <c r="D7" s="4"/>
+      <c r="D7" s="5"/>
       <c r="E7" t="s">
         <v>11</v>
       </c>
@@ -1613,7 +1939,7 @@
       </c>
     </row>
     <row r="8" spans="4:7" x14ac:dyDescent="0.3">
-      <c r="D8" s="4"/>
+      <c r="D8" s="5"/>
       <c r="E8" t="s">
         <v>12</v>
       </c>
@@ -1625,7 +1951,7 @@
       </c>
     </row>
     <row r="9" spans="4:7" x14ac:dyDescent="0.3">
-      <c r="D9" s="4"/>
+      <c r="D9" s="5"/>
       <c r="E9" t="s">
         <v>13</v>
       </c>
@@ -1637,7 +1963,7 @@
       </c>
     </row>
     <row r="10" spans="4:7" x14ac:dyDescent="0.3">
-      <c r="D10" s="4"/>
+      <c r="D10" s="5"/>
       <c r="E10" t="s">
         <v>14</v>
       </c>
@@ -1649,7 +1975,7 @@
       </c>
     </row>
     <row r="11" spans="4:7" x14ac:dyDescent="0.3">
-      <c r="D11" s="4"/>
+      <c r="D11" s="5"/>
       <c r="E11" t="s">
         <v>15</v>
       </c>
@@ -1667,7 +1993,7 @@
       <c r="G12" s="6"/>
     </row>
     <row r="13" spans="4:7" x14ac:dyDescent="0.3">
-      <c r="D13" s="4">
+      <c r="D13" s="5">
         <v>2</v>
       </c>
       <c r="E13" t="s">
@@ -1681,7 +2007,7 @@
       </c>
     </row>
     <row r="14" spans="4:7" x14ac:dyDescent="0.3">
-      <c r="D14" s="4"/>
+      <c r="D14" s="5"/>
       <c r="E14" t="s">
         <v>10</v>
       </c>
@@ -1693,7 +2019,7 @@
       </c>
     </row>
     <row r="15" spans="4:7" x14ac:dyDescent="0.3">
-      <c r="D15" s="4"/>
+      <c r="D15" s="5"/>
       <c r="E15" t="s">
         <v>11</v>
       </c>
@@ -1705,7 +2031,7 @@
       </c>
     </row>
     <row r="16" spans="4:7" x14ac:dyDescent="0.3">
-      <c r="D16" s="4"/>
+      <c r="D16" s="5"/>
       <c r="E16" t="s">
         <v>12</v>
       </c>
@@ -1717,7 +2043,7 @@
       </c>
     </row>
     <row r="17" spans="4:7" x14ac:dyDescent="0.3">
-      <c r="D17" s="4"/>
+      <c r="D17" s="5"/>
       <c r="E17" t="s">
         <v>13</v>
       </c>
@@ -1729,7 +2055,7 @@
       </c>
     </row>
     <row r="18" spans="4:7" x14ac:dyDescent="0.3">
-      <c r="D18" s="4"/>
+      <c r="D18" s="5"/>
       <c r="E18" t="s">
         <v>14</v>
       </c>
@@ -1741,7 +2067,7 @@
       </c>
     </row>
     <row r="19" spans="4:7" x14ac:dyDescent="0.3">
-      <c r="D19" s="4"/>
+      <c r="D19" s="5"/>
       <c r="E19" t="s">
         <v>15</v>
       </c>
@@ -1753,13 +2079,13 @@
       </c>
     </row>
     <row r="20" spans="4:7" x14ac:dyDescent="0.3">
-      <c r="D20" s="5"/>
-      <c r="E20" s="5"/>
-      <c r="F20" s="5"/>
-      <c r="G20" s="5"/>
+      <c r="D20" s="4"/>
+      <c r="E20" s="4"/>
+      <c r="F20" s="4"/>
+      <c r="G20" s="4"/>
     </row>
     <row r="21" spans="4:7" x14ac:dyDescent="0.3">
-      <c r="D21" s="4">
+      <c r="D21" s="5">
         <v>3</v>
       </c>
       <c r="E21" t="s">
@@ -1773,7 +2099,7 @@
       </c>
     </row>
     <row r="22" spans="4:7" x14ac:dyDescent="0.3">
-      <c r="D22" s="4"/>
+      <c r="D22" s="5"/>
       <c r="E22" t="s">
         <v>10</v>
       </c>
@@ -1785,7 +2111,7 @@
       </c>
     </row>
     <row r="23" spans="4:7" x14ac:dyDescent="0.3">
-      <c r="D23" s="4"/>
+      <c r="D23" s="5"/>
       <c r="E23" t="s">
         <v>11</v>
       </c>
@@ -1797,7 +2123,7 @@
       </c>
     </row>
     <row r="24" spans="4:7" x14ac:dyDescent="0.3">
-      <c r="D24" s="4"/>
+      <c r="D24" s="5"/>
       <c r="E24" t="s">
         <v>12</v>
       </c>
@@ -1809,7 +2135,7 @@
       </c>
     </row>
     <row r="25" spans="4:7" x14ac:dyDescent="0.3">
-      <c r="D25" s="4"/>
+      <c r="D25" s="5"/>
       <c r="E25" t="s">
         <v>13</v>
       </c>
@@ -1821,7 +2147,7 @@
       </c>
     </row>
     <row r="26" spans="4:7" x14ac:dyDescent="0.3">
-      <c r="D26" s="4"/>
+      <c r="D26" s="5"/>
       <c r="E26" t="s">
         <v>14</v>
       </c>
@@ -1833,7 +2159,7 @@
       </c>
     </row>
     <row r="27" spans="4:7" x14ac:dyDescent="0.3">
-      <c r="D27" s="4"/>
+      <c r="D27" s="5"/>
       <c r="E27" t="s">
         <v>15</v>
       </c>
@@ -1845,13 +2171,107 @@
       </c>
     </row>
     <row r="28" spans="4:7" x14ac:dyDescent="0.3">
-      <c r="D28" s="5"/>
-      <c r="E28" s="5"/>
-      <c r="F28" s="5"/>
-      <c r="G28" s="5"/>
+      <c r="D28" s="4"/>
+      <c r="E28" s="4"/>
+      <c r="F28" s="4"/>
+      <c r="G28" s="4"/>
+    </row>
+    <row r="29" spans="4:7" x14ac:dyDescent="0.3">
+      <c r="D29" s="5">
+        <v>4</v>
+      </c>
+      <c r="E29" t="s">
+        <v>16</v>
+      </c>
+      <c r="F29">
+        <v>8.3333000000000004E-2</v>
+      </c>
+      <c r="G29">
+        <v>22.351651</v>
+      </c>
+    </row>
+    <row r="30" spans="4:7" x14ac:dyDescent="0.3">
+      <c r="D30" s="5"/>
+      <c r="E30" t="s">
+        <v>10</v>
+      </c>
+      <c r="F30">
+        <v>8.3333000000000004E-2</v>
+      </c>
+      <c r="G30">
+        <v>18.362424000000001</v>
+      </c>
+    </row>
+    <row r="31" spans="4:7" x14ac:dyDescent="0.3">
+      <c r="D31" s="5"/>
+      <c r="E31" t="s">
+        <v>11</v>
+      </c>
+      <c r="F31">
+        <v>4.1667000000000003E-2</v>
+      </c>
+      <c r="G31">
+        <v>11.536178</v>
+      </c>
+    </row>
+    <row r="32" spans="4:7" x14ac:dyDescent="0.3">
+      <c r="D32" s="5"/>
+      <c r="E32" t="s">
+        <v>12</v>
+      </c>
+      <c r="F32">
+        <v>4.1667000000000003E-2</v>
+      </c>
+      <c r="G32">
+        <v>9.1053379999999997</v>
+      </c>
+    </row>
+    <row r="33" spans="4:7" x14ac:dyDescent="0.3">
+      <c r="D33" s="5"/>
+      <c r="E33" t="s">
+        <v>13</v>
+      </c>
+      <c r="F33">
+        <v>4.1667000000000003E-2</v>
+      </c>
+      <c r="G33">
+        <v>15.940567</v>
+      </c>
+    </row>
+    <row r="34" spans="4:7" x14ac:dyDescent="0.3">
+      <c r="D34" s="5"/>
+      <c r="E34" t="s">
+        <v>14</v>
+      </c>
+      <c r="F34">
+        <v>4.1667000000000003E-2</v>
+      </c>
+      <c r="G34">
+        <v>7.6881339999999998</v>
+      </c>
+    </row>
+    <row r="35" spans="4:7" x14ac:dyDescent="0.3">
+      <c r="D35" s="5"/>
+      <c r="E35" t="s">
+        <v>15</v>
+      </c>
+      <c r="F35">
+        <v>8.3333000000000004E-2</v>
+      </c>
+      <c r="G35">
+        <v>21.509909</v>
+      </c>
+    </row>
+    <row r="36" spans="4:7" x14ac:dyDescent="0.3">
+      <c r="D36" s="4"/>
+      <c r="E36" s="4"/>
+      <c r="F36" s="4"/>
+      <c r="G36" s="4"/>
     </row>
   </sheetData>
-  <mergeCells count="6">
+  <mergeCells count="8">
+    <mergeCell ref="D29:D35"/>
+    <mergeCell ref="D36:G36"/>
     <mergeCell ref="D28:G28"/>
     <mergeCell ref="D5:D11"/>
     <mergeCell ref="D12:G12"/>

--- a/shatrov_bootstraps_res.xlsx
+++ b/shatrov_bootstraps_res.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Игорь\Desktop\sem_8\mipt_diplom\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{997BDE62-46C6-46C8-83B1-A37809988675}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{87B0526A-92FE-4B67-9D1D-F981FFEF7C5B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Информация про ряды" sheetId="1" r:id="rId1"/>
@@ -29,7 +29,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="153" uniqueCount="30">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="186" uniqueCount="32">
   <si>
     <t>Номер</t>
   </si>
@@ -119,6 +119,12 @@
   </si>
   <si>
     <t>Отсутствует сезонность. Похож на сумму тренда и случайного блуждания</t>
+  </si>
+  <si>
+    <t>https://raw.githubusercontent.com/jbrownlee/Datasets/master/monthly-writing-paper-sales.csv</t>
+  </si>
+  <si>
+    <t>Monthly Writing Paper Sales</t>
   </si>
 </sst>
 </file>
@@ -128,7 +134,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="0.000"/>
   </numFmts>
-  <fonts count="3" x14ac:knownFonts="1">
+  <fonts count="4" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -146,6 +152,14 @@
     <font>
       <sz val="11"/>
       <color rgb="FFFF0000"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color theme="10"/>
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
@@ -180,27 +194,32 @@
       <diagonal/>
     </border>
   </borders>
-  <cellStyleXfs count="1">
+  <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="7">
+  <cellXfs count="8">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
   </cellXfs>
-  <cellStyles count="1">
+  <cellStyles count="2">
+    <cellStyle name="Гиперссылка" xfId="1" builtinId="8"/>
     <cellStyle name="Обычный" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
@@ -479,7 +498,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="D4:G8"/>
+  <dimension ref="D4:G9"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="6" max="6" width="8.88671875" customWidth="1"/>
@@ -555,14 +574,31 @@
         <v>29</v>
       </c>
     </row>
+    <row r="9" spans="4:7" x14ac:dyDescent="0.3">
+      <c r="D9">
+        <v>5</v>
+      </c>
+      <c r="E9" t="s">
+        <v>31</v>
+      </c>
+      <c r="F9" s="7" t="s">
+        <v>30</v>
+      </c>
+      <c r="G9" t="s">
+        <v>21</v>
+      </c>
+    </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink ref="F9" r:id="rId1" xr:uid="{9367D316-61C7-4D04-93AD-9FDC62845A8C}"/>
+  </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5432242B-BB45-4574-A5B4-2CF25C9CDCFF}">
-  <dimension ref="D4:H40"/>
+  <dimension ref="D4:H49"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="4" max="4" width="13.21875" customWidth="1"/>
@@ -584,7 +620,7 @@
       </c>
     </row>
     <row r="5" spans="4:7" x14ac:dyDescent="0.3">
-      <c r="D5" s="5">
+      <c r="D5" s="4">
         <v>1</v>
       </c>
       <c r="E5" t="s">
@@ -598,7 +634,7 @@
       </c>
     </row>
     <row r="6" spans="4:7" x14ac:dyDescent="0.3">
-      <c r="D6" s="5"/>
+      <c r="D6" s="4"/>
       <c r="E6" t="s">
         <v>16</v>
       </c>
@@ -610,7 +646,7 @@
       </c>
     </row>
     <row r="7" spans="4:7" x14ac:dyDescent="0.3">
-      <c r="D7" s="5"/>
+      <c r="D7" s="4"/>
       <c r="E7" t="s">
         <v>10</v>
       </c>
@@ -622,7 +658,7 @@
       </c>
     </row>
     <row r="8" spans="4:7" x14ac:dyDescent="0.3">
-      <c r="D8" s="5"/>
+      <c r="D8" s="4"/>
       <c r="E8" t="s">
         <v>11</v>
       </c>
@@ -634,7 +670,7 @@
       </c>
     </row>
     <row r="9" spans="4:7" x14ac:dyDescent="0.3">
-      <c r="D9" s="5"/>
+      <c r="D9" s="4"/>
       <c r="E9" t="s">
         <v>12</v>
       </c>
@@ -646,7 +682,7 @@
       </c>
     </row>
     <row r="10" spans="4:7" x14ac:dyDescent="0.3">
-      <c r="D10" s="5"/>
+      <c r="D10" s="4"/>
       <c r="E10" t="s">
         <v>13</v>
       </c>
@@ -658,7 +694,7 @@
       </c>
     </row>
     <row r="11" spans="4:7" x14ac:dyDescent="0.3">
-      <c r="D11" s="5"/>
+      <c r="D11" s="4"/>
       <c r="E11" t="s">
         <v>14</v>
       </c>
@@ -670,7 +706,7 @@
       </c>
     </row>
     <row r="12" spans="4:7" x14ac:dyDescent="0.3">
-      <c r="D12" s="5"/>
+      <c r="D12" s="4"/>
       <c r="E12" t="s">
         <v>15</v>
       </c>
@@ -682,13 +718,13 @@
       </c>
     </row>
     <row r="13" spans="4:7" x14ac:dyDescent="0.3">
-      <c r="D13" s="4"/>
-      <c r="E13" s="4"/>
-      <c r="F13" s="4"/>
-      <c r="G13" s="4"/>
+      <c r="D13" s="5"/>
+      <c r="E13" s="5"/>
+      <c r="F13" s="5"/>
+      <c r="G13" s="5"/>
     </row>
     <row r="14" spans="4:7" x14ac:dyDescent="0.3">
-      <c r="D14" s="5">
+      <c r="D14" s="4">
         <v>2</v>
       </c>
       <c r="E14" t="s">
@@ -702,7 +738,7 @@
       </c>
     </row>
     <row r="15" spans="4:7" x14ac:dyDescent="0.3">
-      <c r="D15" s="5"/>
+      <c r="D15" s="4"/>
       <c r="E15" t="s">
         <v>16</v>
       </c>
@@ -714,7 +750,7 @@
       </c>
     </row>
     <row r="16" spans="4:7" x14ac:dyDescent="0.3">
-      <c r="D16" s="5"/>
+      <c r="D16" s="4"/>
       <c r="E16" t="s">
         <v>10</v>
       </c>
@@ -726,7 +762,7 @@
       </c>
     </row>
     <row r="17" spans="4:8" x14ac:dyDescent="0.3">
-      <c r="D17" s="5"/>
+      <c r="D17" s="4"/>
       <c r="E17" t="s">
         <v>11</v>
       </c>
@@ -738,7 +774,7 @@
       </c>
     </row>
     <row r="18" spans="4:8" x14ac:dyDescent="0.3">
-      <c r="D18" s="5"/>
+      <c r="D18" s="4"/>
       <c r="E18" t="s">
         <v>12</v>
       </c>
@@ -750,7 +786,7 @@
       </c>
     </row>
     <row r="19" spans="4:8" x14ac:dyDescent="0.3">
-      <c r="D19" s="5"/>
+      <c r="D19" s="4"/>
       <c r="E19" t="s">
         <v>13</v>
       </c>
@@ -762,7 +798,7 @@
       </c>
     </row>
     <row r="20" spans="4:8" x14ac:dyDescent="0.3">
-      <c r="D20" s="5"/>
+      <c r="D20" s="4"/>
       <c r="E20" t="s">
         <v>14</v>
       </c>
@@ -774,7 +810,7 @@
       </c>
     </row>
     <row r="21" spans="4:8" x14ac:dyDescent="0.3">
-      <c r="D21" s="5"/>
+      <c r="D21" s="4"/>
       <c r="E21" t="s">
         <v>15</v>
       </c>
@@ -786,13 +822,13 @@
       </c>
     </row>
     <row r="22" spans="4:8" x14ac:dyDescent="0.3">
-      <c r="D22" s="4"/>
-      <c r="E22" s="4"/>
-      <c r="F22" s="4"/>
-      <c r="G22" s="4"/>
+      <c r="D22" s="5"/>
+      <c r="E22" s="5"/>
+      <c r="F22" s="5"/>
+      <c r="G22" s="5"/>
     </row>
     <row r="23" spans="4:8" x14ac:dyDescent="0.3">
-      <c r="D23" s="5">
+      <c r="D23" s="4">
         <v>3</v>
       </c>
       <c r="E23" t="s">
@@ -809,7 +845,7 @@
       </c>
     </row>
     <row r="24" spans="4:8" x14ac:dyDescent="0.3">
-      <c r="D24" s="5"/>
+      <c r="D24" s="4"/>
       <c r="E24" t="s">
         <v>16</v>
       </c>
@@ -821,7 +857,7 @@
       </c>
     </row>
     <row r="25" spans="4:8" x14ac:dyDescent="0.3">
-      <c r="D25" s="5"/>
+      <c r="D25" s="4"/>
       <c r="E25" t="s">
         <v>10</v>
       </c>
@@ -833,7 +869,7 @@
       </c>
     </row>
     <row r="26" spans="4:8" x14ac:dyDescent="0.3">
-      <c r="D26" s="5"/>
+      <c r="D26" s="4"/>
       <c r="E26" t="s">
         <v>11</v>
       </c>
@@ -845,7 +881,7 @@
       </c>
     </row>
     <row r="27" spans="4:8" x14ac:dyDescent="0.3">
-      <c r="D27" s="5"/>
+      <c r="D27" s="4"/>
       <c r="E27" t="s">
         <v>12</v>
       </c>
@@ -857,7 +893,7 @@
       </c>
     </row>
     <row r="28" spans="4:8" x14ac:dyDescent="0.3">
-      <c r="D28" s="5"/>
+      <c r="D28" s="4"/>
       <c r="E28" t="s">
         <v>13</v>
       </c>
@@ -869,7 +905,7 @@
       </c>
     </row>
     <row r="29" spans="4:8" x14ac:dyDescent="0.3">
-      <c r="D29" s="5"/>
+      <c r="D29" s="4"/>
       <c r="E29" t="s">
         <v>14</v>
       </c>
@@ -881,7 +917,7 @@
       </c>
     </row>
     <row r="30" spans="4:8" x14ac:dyDescent="0.3">
-      <c r="D30" s="5"/>
+      <c r="D30" s="4"/>
       <c r="E30" t="s">
         <v>15</v>
       </c>
@@ -893,13 +929,13 @@
       </c>
     </row>
     <row r="31" spans="4:8" x14ac:dyDescent="0.3">
-      <c r="D31" s="4"/>
-      <c r="E31" s="4"/>
-      <c r="F31" s="4"/>
-      <c r="G31" s="4"/>
+      <c r="D31" s="5"/>
+      <c r="E31" s="5"/>
+      <c r="F31" s="5"/>
+      <c r="G31" s="5"/>
     </row>
     <row r="32" spans="4:8" x14ac:dyDescent="0.3">
-      <c r="D32" s="5">
+      <c r="D32" s="4">
         <v>4</v>
       </c>
       <c r="E32" t="s">
@@ -913,7 +949,7 @@
       </c>
     </row>
     <row r="33" spans="4:7" x14ac:dyDescent="0.3">
-      <c r="D33" s="5"/>
+      <c r="D33" s="4"/>
       <c r="E33" t="s">
         <v>16</v>
       </c>
@@ -925,7 +961,7 @@
       </c>
     </row>
     <row r="34" spans="4:7" x14ac:dyDescent="0.3">
-      <c r="D34" s="5"/>
+      <c r="D34" s="4"/>
       <c r="E34" t="s">
         <v>10</v>
       </c>
@@ -937,7 +973,7 @@
       </c>
     </row>
     <row r="35" spans="4:7" x14ac:dyDescent="0.3">
-      <c r="D35" s="5"/>
+      <c r="D35" s="4"/>
       <c r="E35" t="s">
         <v>11</v>
       </c>
@@ -949,7 +985,7 @@
       </c>
     </row>
     <row r="36" spans="4:7" x14ac:dyDescent="0.3">
-      <c r="D36" s="5"/>
+      <c r="D36" s="4"/>
       <c r="E36" t="s">
         <v>12</v>
       </c>
@@ -961,7 +997,7 @@
       </c>
     </row>
     <row r="37" spans="4:7" x14ac:dyDescent="0.3">
-      <c r="D37" s="5"/>
+      <c r="D37" s="4"/>
       <c r="E37" t="s">
         <v>13</v>
       </c>
@@ -973,7 +1009,7 @@
       </c>
     </row>
     <row r="38" spans="4:7" x14ac:dyDescent="0.3">
-      <c r="D38" s="5"/>
+      <c r="D38" s="4"/>
       <c r="E38" t="s">
         <v>14</v>
       </c>
@@ -985,7 +1021,7 @@
       </c>
     </row>
     <row r="39" spans="4:7" x14ac:dyDescent="0.3">
-      <c r="D39" s="5"/>
+      <c r="D39" s="4"/>
       <c r="E39" t="s">
         <v>15</v>
       </c>
@@ -997,13 +1033,119 @@
       </c>
     </row>
     <row r="40" spans="4:7" x14ac:dyDescent="0.3">
-      <c r="D40" s="4"/>
-      <c r="E40" s="4"/>
-      <c r="F40" s="4"/>
-      <c r="G40" s="4"/>
+      <c r="D40" s="5"/>
+      <c r="E40" s="5"/>
+      <c r="F40" s="5"/>
+      <c r="G40" s="5"/>
+    </row>
+    <row r="41" spans="4:7" x14ac:dyDescent="0.3">
+      <c r="D41" s="4">
+        <v>5</v>
+      </c>
+      <c r="E41" t="s">
+        <v>9</v>
+      </c>
+      <c r="F41">
+        <v>0.54166700000000001</v>
+      </c>
+      <c r="G41">
+        <v>847.86075000000005</v>
+      </c>
+    </row>
+    <row r="42" spans="4:7" x14ac:dyDescent="0.3">
+      <c r="D42" s="4"/>
+      <c r="E42" t="s">
+        <v>16</v>
+      </c>
+      <c r="F42">
+        <v>0.54166700000000001</v>
+      </c>
+      <c r="G42">
+        <v>838.84561099999996</v>
+      </c>
+    </row>
+    <row r="43" spans="4:7" x14ac:dyDescent="0.3">
+      <c r="D43" s="4"/>
+      <c r="E43" t="s">
+        <v>10</v>
+      </c>
+      <c r="F43">
+        <v>0.54166700000000001</v>
+      </c>
+      <c r="G43">
+        <v>853.22697500000004</v>
+      </c>
+    </row>
+    <row r="44" spans="4:7" x14ac:dyDescent="0.3">
+      <c r="D44" s="4"/>
+      <c r="E44" t="s">
+        <v>11</v>
+      </c>
+      <c r="F44">
+        <v>0.54166700000000001</v>
+      </c>
+      <c r="G44">
+        <v>837.32505200000003</v>
+      </c>
+    </row>
+    <row r="45" spans="4:7" x14ac:dyDescent="0.3">
+      <c r="D45" s="4"/>
+      <c r="E45" t="s">
+        <v>12</v>
+      </c>
+      <c r="F45">
+        <v>0.58333299999999999</v>
+      </c>
+      <c r="G45">
+        <v>843.81196799999998</v>
+      </c>
+    </row>
+    <row r="46" spans="4:7" x14ac:dyDescent="0.3">
+      <c r="D46" s="4"/>
+      <c r="E46" t="s">
+        <v>13</v>
+      </c>
+      <c r="F46">
+        <v>0.66666700000000001</v>
+      </c>
+      <c r="G46">
+        <v>1067.962276</v>
+      </c>
+    </row>
+    <row r="47" spans="4:7" x14ac:dyDescent="0.3">
+      <c r="D47" s="4"/>
+      <c r="E47" t="s">
+        <v>14</v>
+      </c>
+      <c r="F47">
+        <v>0.54166700000000001</v>
+      </c>
+      <c r="G47">
+        <v>858.89092200000005</v>
+      </c>
+    </row>
+    <row r="48" spans="4:7" x14ac:dyDescent="0.3">
+      <c r="D48" s="4"/>
+      <c r="E48" t="s">
+        <v>15</v>
+      </c>
+      <c r="F48">
+        <v>0.54166700000000001</v>
+      </c>
+      <c r="G48">
+        <v>855.25156200000004</v>
+      </c>
+    </row>
+    <row r="49" spans="4:7" x14ac:dyDescent="0.3">
+      <c r="D49" s="5"/>
+      <c r="E49" s="5"/>
+      <c r="F49" s="5"/>
+      <c r="G49" s="5"/>
     </row>
   </sheetData>
-  <mergeCells count="8">
+  <mergeCells count="10">
+    <mergeCell ref="D41:D48"/>
+    <mergeCell ref="D49:G49"/>
     <mergeCell ref="D32:D39"/>
     <mergeCell ref="D40:G40"/>
     <mergeCell ref="D31:G31"/>
@@ -1019,7 +1161,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D9F3D6F7-9B83-4803-A2A9-5F6E3F05FBE9}">
-  <dimension ref="D4:G40"/>
+  <dimension ref="D4:G49"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="4" max="4" width="13.21875" customWidth="1"/>
@@ -1041,7 +1183,7 @@
       </c>
     </row>
     <row r="5" spans="4:7" x14ac:dyDescent="0.3">
-      <c r="D5" s="5">
+      <c r="D5" s="4">
         <v>1</v>
       </c>
       <c r="E5" t="s">
@@ -1055,7 +1197,7 @@
       </c>
     </row>
     <row r="6" spans="4:7" x14ac:dyDescent="0.3">
-      <c r="D6" s="5"/>
+      <c r="D6" s="4"/>
       <c r="E6" t="s">
         <v>16</v>
       </c>
@@ -1067,7 +1209,7 @@
       </c>
     </row>
     <row r="7" spans="4:7" x14ac:dyDescent="0.3">
-      <c r="D7" s="5"/>
+      <c r="D7" s="4"/>
       <c r="E7" t="s">
         <v>10</v>
       </c>
@@ -1079,7 +1221,7 @@
       </c>
     </row>
     <row r="8" spans="4:7" x14ac:dyDescent="0.3">
-      <c r="D8" s="5"/>
+      <c r="D8" s="4"/>
       <c r="E8" t="s">
         <v>11</v>
       </c>
@@ -1091,7 +1233,7 @@
       </c>
     </row>
     <row r="9" spans="4:7" x14ac:dyDescent="0.3">
-      <c r="D9" s="5"/>
+      <c r="D9" s="4"/>
       <c r="E9" t="s">
         <v>12</v>
       </c>
@@ -1103,7 +1245,7 @@
       </c>
     </row>
     <row r="10" spans="4:7" x14ac:dyDescent="0.3">
-      <c r="D10" s="5"/>
+      <c r="D10" s="4"/>
       <c r="E10" t="s">
         <v>13</v>
       </c>
@@ -1115,7 +1257,7 @@
       </c>
     </row>
     <row r="11" spans="4:7" x14ac:dyDescent="0.3">
-      <c r="D11" s="5"/>
+      <c r="D11" s="4"/>
       <c r="E11" t="s">
         <v>14</v>
       </c>
@@ -1127,7 +1269,7 @@
       </c>
     </row>
     <row r="12" spans="4:7" x14ac:dyDescent="0.3">
-      <c r="D12" s="5"/>
+      <c r="D12" s="4"/>
       <c r="E12" t="s">
         <v>15</v>
       </c>
@@ -1139,13 +1281,13 @@
       </c>
     </row>
     <row r="13" spans="4:7" x14ac:dyDescent="0.3">
-      <c r="D13" s="4"/>
-      <c r="E13" s="4"/>
-      <c r="F13" s="4"/>
-      <c r="G13" s="4"/>
+      <c r="D13" s="5"/>
+      <c r="E13" s="5"/>
+      <c r="F13" s="5"/>
+      <c r="G13" s="5"/>
     </row>
     <row r="14" spans="4:7" x14ac:dyDescent="0.3">
-      <c r="D14" s="5">
+      <c r="D14" s="4">
         <v>2</v>
       </c>
       <c r="E14" t="s">
@@ -1159,7 +1301,7 @@
       </c>
     </row>
     <row r="15" spans="4:7" x14ac:dyDescent="0.3">
-      <c r="D15" s="5"/>
+      <c r="D15" s="4"/>
       <c r="E15" t="s">
         <v>16</v>
       </c>
@@ -1171,7 +1313,7 @@
       </c>
     </row>
     <row r="16" spans="4:7" x14ac:dyDescent="0.3">
-      <c r="D16" s="5"/>
+      <c r="D16" s="4"/>
       <c r="E16" t="s">
         <v>10</v>
       </c>
@@ -1183,7 +1325,7 @@
       </c>
     </row>
     <row r="17" spans="4:7" x14ac:dyDescent="0.3">
-      <c r="D17" s="5"/>
+      <c r="D17" s="4"/>
       <c r="E17" t="s">
         <v>11</v>
       </c>
@@ -1195,7 +1337,7 @@
       </c>
     </row>
     <row r="18" spans="4:7" x14ac:dyDescent="0.3">
-      <c r="D18" s="5"/>
+      <c r="D18" s="4"/>
       <c r="E18" t="s">
         <v>12</v>
       </c>
@@ -1207,7 +1349,7 @@
       </c>
     </row>
     <row r="19" spans="4:7" x14ac:dyDescent="0.3">
-      <c r="D19" s="5"/>
+      <c r="D19" s="4"/>
       <c r="E19" s="3" t="s">
         <v>13</v>
       </c>
@@ -1219,7 +1361,7 @@
       </c>
     </row>
     <row r="20" spans="4:7" x14ac:dyDescent="0.3">
-      <c r="D20" s="5"/>
+      <c r="D20" s="4"/>
       <c r="E20" t="s">
         <v>14</v>
       </c>
@@ -1231,7 +1373,7 @@
       </c>
     </row>
     <row r="21" spans="4:7" x14ac:dyDescent="0.3">
-      <c r="D21" s="5"/>
+      <c r="D21" s="4"/>
       <c r="E21" t="s">
         <v>15</v>
       </c>
@@ -1243,13 +1385,13 @@
       </c>
     </row>
     <row r="22" spans="4:7" x14ac:dyDescent="0.3">
-      <c r="D22" s="4"/>
-      <c r="E22" s="4"/>
-      <c r="F22" s="4"/>
-      <c r="G22" s="4"/>
+      <c r="D22" s="5"/>
+      <c r="E22" s="5"/>
+      <c r="F22" s="5"/>
+      <c r="G22" s="5"/>
     </row>
     <row r="23" spans="4:7" x14ac:dyDescent="0.3">
-      <c r="D23" s="5">
+      <c r="D23" s="4">
         <v>3</v>
       </c>
       <c r="E23" t="s">
@@ -1263,7 +1405,7 @@
       </c>
     </row>
     <row r="24" spans="4:7" x14ac:dyDescent="0.3">
-      <c r="D24" s="5"/>
+      <c r="D24" s="4"/>
       <c r="E24" t="s">
         <v>16</v>
       </c>
@@ -1275,7 +1417,7 @@
       </c>
     </row>
     <row r="25" spans="4:7" x14ac:dyDescent="0.3">
-      <c r="D25" s="5"/>
+      <c r="D25" s="4"/>
       <c r="E25" t="s">
         <v>10</v>
       </c>
@@ -1287,7 +1429,7 @@
       </c>
     </row>
     <row r="26" spans="4:7" x14ac:dyDescent="0.3">
-      <c r="D26" s="5"/>
+      <c r="D26" s="4"/>
       <c r="E26" t="s">
         <v>11</v>
       </c>
@@ -1299,7 +1441,7 @@
       </c>
     </row>
     <row r="27" spans="4:7" x14ac:dyDescent="0.3">
-      <c r="D27" s="5"/>
+      <c r="D27" s="4"/>
       <c r="E27" t="s">
         <v>12</v>
       </c>
@@ -1311,7 +1453,7 @@
       </c>
     </row>
     <row r="28" spans="4:7" x14ac:dyDescent="0.3">
-      <c r="D28" s="5"/>
+      <c r="D28" s="4"/>
       <c r="E28" t="s">
         <v>13</v>
       </c>
@@ -1323,7 +1465,7 @@
       </c>
     </row>
     <row r="29" spans="4:7" x14ac:dyDescent="0.3">
-      <c r="D29" s="5"/>
+      <c r="D29" s="4"/>
       <c r="E29" t="s">
         <v>14</v>
       </c>
@@ -1335,7 +1477,7 @@
       </c>
     </row>
     <row r="30" spans="4:7" x14ac:dyDescent="0.3">
-      <c r="D30" s="5"/>
+      <c r="D30" s="4"/>
       <c r="E30" t="s">
         <v>15</v>
       </c>
@@ -1347,13 +1489,13 @@
       </c>
     </row>
     <row r="31" spans="4:7" x14ac:dyDescent="0.3">
-      <c r="D31" s="4"/>
-      <c r="E31" s="4"/>
-      <c r="F31" s="4"/>
-      <c r="G31" s="4"/>
+      <c r="D31" s="5"/>
+      <c r="E31" s="5"/>
+      <c r="F31" s="5"/>
+      <c r="G31" s="5"/>
     </row>
     <row r="32" spans="4:7" x14ac:dyDescent="0.3">
-      <c r="D32" s="5">
+      <c r="D32" s="4">
         <v>4</v>
       </c>
       <c r="E32" t="s">
@@ -1367,7 +1509,7 @@
       </c>
     </row>
     <row r="33" spans="4:7" x14ac:dyDescent="0.3">
-      <c r="D33" s="5"/>
+      <c r="D33" s="4"/>
       <c r="E33" t="s">
         <v>16</v>
       </c>
@@ -1379,7 +1521,7 @@
       </c>
     </row>
     <row r="34" spans="4:7" x14ac:dyDescent="0.3">
-      <c r="D34" s="5"/>
+      <c r="D34" s="4"/>
       <c r="E34" t="s">
         <v>10</v>
       </c>
@@ -1391,7 +1533,7 @@
       </c>
     </row>
     <row r="35" spans="4:7" x14ac:dyDescent="0.3">
-      <c r="D35" s="5"/>
+      <c r="D35" s="4"/>
       <c r="E35" t="s">
         <v>11</v>
       </c>
@@ -1403,7 +1545,7 @@
       </c>
     </row>
     <row r="36" spans="4:7" x14ac:dyDescent="0.3">
-      <c r="D36" s="5"/>
+      <c r="D36" s="4"/>
       <c r="E36" t="s">
         <v>12</v>
       </c>
@@ -1415,7 +1557,7 @@
       </c>
     </row>
     <row r="37" spans="4:7" x14ac:dyDescent="0.3">
-      <c r="D37" s="5"/>
+      <c r="D37" s="4"/>
       <c r="E37" t="s">
         <v>13</v>
       </c>
@@ -1427,7 +1569,7 @@
       </c>
     </row>
     <row r="38" spans="4:7" x14ac:dyDescent="0.3">
-      <c r="D38" s="5"/>
+      <c r="D38" s="4"/>
       <c r="E38" t="s">
         <v>14</v>
       </c>
@@ -1439,7 +1581,7 @@
       </c>
     </row>
     <row r="39" spans="4:7" x14ac:dyDescent="0.3">
-      <c r="D39" s="5"/>
+      <c r="D39" s="4"/>
       <c r="E39" t="s">
         <v>15</v>
       </c>
@@ -1451,13 +1593,119 @@
       </c>
     </row>
     <row r="40" spans="4:7" x14ac:dyDescent="0.3">
-      <c r="D40" s="4"/>
-      <c r="E40" s="4"/>
-      <c r="F40" s="4"/>
-      <c r="G40" s="4"/>
+      <c r="D40" s="5"/>
+      <c r="E40" s="5"/>
+      <c r="F40" s="5"/>
+      <c r="G40" s="5"/>
+    </row>
+    <row r="41" spans="4:7" x14ac:dyDescent="0.3">
+      <c r="D41" s="4">
+        <v>5</v>
+      </c>
+      <c r="E41" t="s">
+        <v>17</v>
+      </c>
+      <c r="F41" s="2">
+        <v>0.91666700000000001</v>
+      </c>
+      <c r="G41" s="2">
+        <v>937.70045300000004</v>
+      </c>
+    </row>
+    <row r="42" spans="4:7" x14ac:dyDescent="0.3">
+      <c r="D42" s="4"/>
+      <c r="E42" t="s">
+        <v>16</v>
+      </c>
+      <c r="F42" s="2">
+        <v>0.91666700000000001</v>
+      </c>
+      <c r="G42" s="2">
+        <v>936.699343</v>
+      </c>
+    </row>
+    <row r="43" spans="4:7" x14ac:dyDescent="0.3">
+      <c r="D43" s="4"/>
+      <c r="E43" t="s">
+        <v>10</v>
+      </c>
+      <c r="F43" s="2">
+        <v>0.875</v>
+      </c>
+      <c r="G43" s="2">
+        <v>931.72322299999996</v>
+      </c>
+    </row>
+    <row r="44" spans="4:7" x14ac:dyDescent="0.3">
+      <c r="D44" s="4"/>
+      <c r="E44" t="s">
+        <v>11</v>
+      </c>
+      <c r="F44" s="2">
+        <v>0.875</v>
+      </c>
+      <c r="G44" s="2">
+        <v>907.72775799999999</v>
+      </c>
+    </row>
+    <row r="45" spans="4:7" x14ac:dyDescent="0.3">
+      <c r="D45" s="4"/>
+      <c r="E45" t="s">
+        <v>12</v>
+      </c>
+      <c r="F45" s="2">
+        <v>0.91666700000000001</v>
+      </c>
+      <c r="G45" s="2">
+        <v>936.01575700000001</v>
+      </c>
+    </row>
+    <row r="46" spans="4:7" x14ac:dyDescent="0.3">
+      <c r="D46" s="4"/>
+      <c r="E46" t="s">
+        <v>13</v>
+      </c>
+      <c r="F46" s="2">
+        <v>0.875</v>
+      </c>
+      <c r="G46" s="2">
+        <v>1101.727549</v>
+      </c>
+    </row>
+    <row r="47" spans="4:7" x14ac:dyDescent="0.3">
+      <c r="D47" s="4"/>
+      <c r="E47" t="s">
+        <v>14</v>
+      </c>
+      <c r="F47" s="2">
+        <v>0.91666700000000001</v>
+      </c>
+      <c r="G47" s="2">
+        <v>940.72508100000005</v>
+      </c>
+    </row>
+    <row r="48" spans="4:7" x14ac:dyDescent="0.3">
+      <c r="D48" s="4"/>
+      <c r="E48" t="s">
+        <v>15</v>
+      </c>
+      <c r="F48" s="2">
+        <v>0.91666700000000001</v>
+      </c>
+      <c r="G48" s="2">
+        <v>933.69020699999999</v>
+      </c>
+    </row>
+    <row r="49" spans="4:7" x14ac:dyDescent="0.3">
+      <c r="D49" s="5"/>
+      <c r="E49" s="5"/>
+      <c r="F49" s="5"/>
+      <c r="G49" s="5"/>
     </row>
   </sheetData>
-  <mergeCells count="8">
+  <mergeCells count="10">
+    <mergeCell ref="D41:D48"/>
+    <mergeCell ref="D49:G49"/>
     <mergeCell ref="D32:D39"/>
     <mergeCell ref="D40:G40"/>
     <mergeCell ref="D31:G31"/>
@@ -1473,7 +1721,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D9B1F934-9143-4061-8956-2969F906ECCB}">
-  <dimension ref="D4:G36"/>
+  <dimension ref="D4:G44"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="4" max="4" width="16.33203125" customWidth="1"/>
@@ -1495,7 +1743,7 @@
       </c>
     </row>
     <row r="5" spans="4:7" x14ac:dyDescent="0.3">
-      <c r="D5" s="5">
+      <c r="D5" s="4">
         <v>1</v>
       </c>
       <c r="E5" t="s">
@@ -1509,7 +1757,7 @@
       </c>
     </row>
     <row r="6" spans="4:7" x14ac:dyDescent="0.3">
-      <c r="D6" s="5"/>
+      <c r="D6" s="4"/>
       <c r="E6" t="s">
         <v>10</v>
       </c>
@@ -1521,7 +1769,7 @@
       </c>
     </row>
     <row r="7" spans="4:7" x14ac:dyDescent="0.3">
-      <c r="D7" s="5"/>
+      <c r="D7" s="4"/>
       <c r="E7" t="s">
         <v>11</v>
       </c>
@@ -1533,7 +1781,7 @@
       </c>
     </row>
     <row r="8" spans="4:7" x14ac:dyDescent="0.3">
-      <c r="D8" s="5"/>
+      <c r="D8" s="4"/>
       <c r="E8" t="s">
         <v>12</v>
       </c>
@@ -1545,7 +1793,7 @@
       </c>
     </row>
     <row r="9" spans="4:7" x14ac:dyDescent="0.3">
-      <c r="D9" s="5"/>
+      <c r="D9" s="4"/>
       <c r="E9" t="s">
         <v>13</v>
       </c>
@@ -1557,7 +1805,7 @@
       </c>
     </row>
     <row r="10" spans="4:7" x14ac:dyDescent="0.3">
-      <c r="D10" s="5"/>
+      <c r="D10" s="4"/>
       <c r="E10" t="s">
         <v>14</v>
       </c>
@@ -1569,7 +1817,7 @@
       </c>
     </row>
     <row r="11" spans="4:7" x14ac:dyDescent="0.3">
-      <c r="D11" s="5"/>
+      <c r="D11" s="4"/>
       <c r="E11" t="s">
         <v>15</v>
       </c>
@@ -1587,7 +1835,7 @@
       <c r="G12" s="6"/>
     </row>
     <row r="13" spans="4:7" x14ac:dyDescent="0.3">
-      <c r="D13" s="5">
+      <c r="D13" s="4">
         <v>2</v>
       </c>
       <c r="E13" t="s">
@@ -1601,7 +1849,7 @@
       </c>
     </row>
     <row r="14" spans="4:7" x14ac:dyDescent="0.3">
-      <c r="D14" s="5"/>
+      <c r="D14" s="4"/>
       <c r="E14" t="s">
         <v>10</v>
       </c>
@@ -1613,7 +1861,7 @@
       </c>
     </row>
     <row r="15" spans="4:7" x14ac:dyDescent="0.3">
-      <c r="D15" s="5"/>
+      <c r="D15" s="4"/>
       <c r="E15" t="s">
         <v>11</v>
       </c>
@@ -1625,7 +1873,7 @@
       </c>
     </row>
     <row r="16" spans="4:7" x14ac:dyDescent="0.3">
-      <c r="D16" s="5"/>
+      <c r="D16" s="4"/>
       <c r="E16" t="s">
         <v>12</v>
       </c>
@@ -1637,7 +1885,7 @@
       </c>
     </row>
     <row r="17" spans="4:7" x14ac:dyDescent="0.3">
-      <c r="D17" s="5"/>
+      <c r="D17" s="4"/>
       <c r="E17" t="s">
         <v>13</v>
       </c>
@@ -1649,7 +1897,7 @@
       </c>
     </row>
     <row r="18" spans="4:7" x14ac:dyDescent="0.3">
-      <c r="D18" s="5"/>
+      <c r="D18" s="4"/>
       <c r="E18" t="s">
         <v>14</v>
       </c>
@@ -1661,7 +1909,7 @@
       </c>
     </row>
     <row r="19" spans="4:7" x14ac:dyDescent="0.3">
-      <c r="D19" s="5"/>
+      <c r="D19" s="4"/>
       <c r="E19" t="s">
         <v>15</v>
       </c>
@@ -1673,13 +1921,13 @@
       </c>
     </row>
     <row r="20" spans="4:7" x14ac:dyDescent="0.3">
-      <c r="D20" s="4"/>
-      <c r="E20" s="4"/>
-      <c r="F20" s="4"/>
-      <c r="G20" s="4"/>
+      <c r="D20" s="5"/>
+      <c r="E20" s="5"/>
+      <c r="F20" s="5"/>
+      <c r="G20" s="5"/>
     </row>
     <row r="21" spans="4:7" x14ac:dyDescent="0.3">
-      <c r="D21" s="5">
+      <c r="D21" s="4">
         <v>3</v>
       </c>
       <c r="E21" t="s">
@@ -1693,7 +1941,7 @@
       </c>
     </row>
     <row r="22" spans="4:7" x14ac:dyDescent="0.3">
-      <c r="D22" s="5"/>
+      <c r="D22" s="4"/>
       <c r="E22" t="s">
         <v>10</v>
       </c>
@@ -1705,7 +1953,7 @@
       </c>
     </row>
     <row r="23" spans="4:7" x14ac:dyDescent="0.3">
-      <c r="D23" s="5"/>
+      <c r="D23" s="4"/>
       <c r="E23" t="s">
         <v>11</v>
       </c>
@@ -1717,7 +1965,7 @@
       </c>
     </row>
     <row r="24" spans="4:7" x14ac:dyDescent="0.3">
-      <c r="D24" s="5"/>
+      <c r="D24" s="4"/>
       <c r="E24" t="s">
         <v>12</v>
       </c>
@@ -1729,7 +1977,7 @@
       </c>
     </row>
     <row r="25" spans="4:7" x14ac:dyDescent="0.3">
-      <c r="D25" s="5"/>
+      <c r="D25" s="4"/>
       <c r="E25" t="s">
         <v>13</v>
       </c>
@@ -1741,7 +1989,7 @@
       </c>
     </row>
     <row r="26" spans="4:7" x14ac:dyDescent="0.3">
-      <c r="D26" s="5"/>
+      <c r="D26" s="4"/>
       <c r="E26" t="s">
         <v>14</v>
       </c>
@@ -1753,7 +2001,7 @@
       </c>
     </row>
     <row r="27" spans="4:7" x14ac:dyDescent="0.3">
-      <c r="D27" s="5"/>
+      <c r="D27" s="4"/>
       <c r="E27" t="s">
         <v>15</v>
       </c>
@@ -1765,13 +2013,13 @@
       </c>
     </row>
     <row r="28" spans="4:7" x14ac:dyDescent="0.3">
-      <c r="D28" s="4"/>
-      <c r="E28" s="4"/>
-      <c r="F28" s="4"/>
-      <c r="G28" s="4"/>
+      <c r="D28" s="5"/>
+      <c r="E28" s="5"/>
+      <c r="F28" s="5"/>
+      <c r="G28" s="5"/>
     </row>
     <row r="29" spans="4:7" x14ac:dyDescent="0.3">
-      <c r="D29" s="5">
+      <c r="D29" s="4">
         <v>4</v>
       </c>
       <c r="E29" t="s">
@@ -1785,7 +2033,7 @@
       </c>
     </row>
     <row r="30" spans="4:7" x14ac:dyDescent="0.3">
-      <c r="D30" s="5"/>
+      <c r="D30" s="4"/>
       <c r="E30" t="s">
         <v>10</v>
       </c>
@@ -1797,7 +2045,7 @@
       </c>
     </row>
     <row r="31" spans="4:7" x14ac:dyDescent="0.3">
-      <c r="D31" s="5"/>
+      <c r="D31" s="4"/>
       <c r="E31" t="s">
         <v>11</v>
       </c>
@@ -1809,7 +2057,7 @@
       </c>
     </row>
     <row r="32" spans="4:7" x14ac:dyDescent="0.3">
-      <c r="D32" s="5"/>
+      <c r="D32" s="4"/>
       <c r="E32" t="s">
         <v>12</v>
       </c>
@@ -1821,7 +2069,7 @@
       </c>
     </row>
     <row r="33" spans="4:7" x14ac:dyDescent="0.3">
-      <c r="D33" s="5"/>
+      <c r="D33" s="4"/>
       <c r="E33" t="s">
         <v>13</v>
       </c>
@@ -1833,7 +2081,7 @@
       </c>
     </row>
     <row r="34" spans="4:7" x14ac:dyDescent="0.3">
-      <c r="D34" s="5"/>
+      <c r="D34" s="4"/>
       <c r="E34" t="s">
         <v>14</v>
       </c>
@@ -1845,7 +2093,7 @@
       </c>
     </row>
     <row r="35" spans="4:7" x14ac:dyDescent="0.3">
-      <c r="D35" s="5"/>
+      <c r="D35" s="4"/>
       <c r="E35" t="s">
         <v>15</v>
       </c>
@@ -1857,13 +2105,107 @@
       </c>
     </row>
     <row r="36" spans="4:7" x14ac:dyDescent="0.3">
-      <c r="D36" s="4"/>
-      <c r="E36" s="4"/>
-      <c r="F36" s="4"/>
-      <c r="G36" s="4"/>
+      <c r="D36" s="5"/>
+      <c r="E36" s="5"/>
+      <c r="F36" s="5"/>
+      <c r="G36" s="5"/>
+    </row>
+    <row r="37" spans="4:7" x14ac:dyDescent="0.3">
+      <c r="D37" s="4">
+        <v>5</v>
+      </c>
+      <c r="E37" t="s">
+        <v>16</v>
+      </c>
+      <c r="F37">
+        <v>0.29166700000000001</v>
+      </c>
+      <c r="G37">
+        <v>297.578644</v>
+      </c>
+    </row>
+    <row r="38" spans="4:7" x14ac:dyDescent="0.3">
+      <c r="D38" s="4"/>
+      <c r="E38" t="s">
+        <v>10</v>
+      </c>
+      <c r="F38">
+        <v>0.16666700000000001</v>
+      </c>
+      <c r="G38">
+        <v>196.72213500000001</v>
+      </c>
+    </row>
+    <row r="39" spans="4:7" x14ac:dyDescent="0.3">
+      <c r="D39" s="4"/>
+      <c r="E39" t="s">
+        <v>11</v>
+      </c>
+      <c r="F39">
+        <v>0.125</v>
+      </c>
+      <c r="G39">
+        <v>116.041706</v>
+      </c>
+    </row>
+    <row r="40" spans="4:7" x14ac:dyDescent="0.3">
+      <c r="D40" s="4"/>
+      <c r="E40" t="s">
+        <v>12</v>
+      </c>
+      <c r="F40">
+        <v>0.125</v>
+      </c>
+      <c r="G40">
+        <v>102.865477</v>
+      </c>
+    </row>
+    <row r="41" spans="4:7" x14ac:dyDescent="0.3">
+      <c r="D41" s="4"/>
+      <c r="E41" t="s">
+        <v>13</v>
+      </c>
+      <c r="F41">
+        <v>0.25</v>
+      </c>
+      <c r="G41">
+        <v>275.98971899999998</v>
+      </c>
+    </row>
+    <row r="42" spans="4:7" x14ac:dyDescent="0.3">
+      <c r="D42" s="4"/>
+      <c r="E42" t="s">
+        <v>14</v>
+      </c>
+      <c r="F42">
+        <v>0</v>
+      </c>
+      <c r="G42">
+        <v>6.3266600000000004</v>
+      </c>
+    </row>
+    <row r="43" spans="4:7" x14ac:dyDescent="0.3">
+      <c r="D43" s="4"/>
+      <c r="E43" t="s">
+        <v>15</v>
+      </c>
+      <c r="F43">
+        <v>0.25</v>
+      </c>
+      <c r="G43">
+        <v>292.207177</v>
+      </c>
+    </row>
+    <row r="44" spans="4:7" x14ac:dyDescent="0.3">
+      <c r="D44" s="5"/>
+      <c r="E44" s="5"/>
+      <c r="F44" s="5"/>
+      <c r="G44" s="5"/>
     </row>
   </sheetData>
-  <mergeCells count="8">
+  <mergeCells count="10">
+    <mergeCell ref="D37:D43"/>
+    <mergeCell ref="D44:G44"/>
     <mergeCell ref="D29:D35"/>
     <mergeCell ref="D36:G36"/>
     <mergeCell ref="D28:G28"/>
@@ -1879,7 +2221,7 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{AA9C7C1F-8E69-4E9D-9311-55B2096F876D}">
-  <dimension ref="D4:G36"/>
+  <dimension ref="D4:G44"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="4" max="4" width="16.33203125" customWidth="1"/>
@@ -1901,7 +2243,7 @@
       </c>
     </row>
     <row r="5" spans="4:7" x14ac:dyDescent="0.3">
-      <c r="D5" s="5">
+      <c r="D5" s="4">
         <v>1</v>
       </c>
       <c r="E5" t="s">
@@ -1915,7 +2257,7 @@
       </c>
     </row>
     <row r="6" spans="4:7" x14ac:dyDescent="0.3">
-      <c r="D6" s="5"/>
+      <c r="D6" s="4"/>
       <c r="E6" t="s">
         <v>10</v>
       </c>
@@ -1927,7 +2269,7 @@
       </c>
     </row>
     <row r="7" spans="4:7" x14ac:dyDescent="0.3">
-      <c r="D7" s="5"/>
+      <c r="D7" s="4"/>
       <c r="E7" t="s">
         <v>11</v>
       </c>
@@ -1939,7 +2281,7 @@
       </c>
     </row>
     <row r="8" spans="4:7" x14ac:dyDescent="0.3">
-      <c r="D8" s="5"/>
+      <c r="D8" s="4"/>
       <c r="E8" t="s">
         <v>12</v>
       </c>
@@ -1951,7 +2293,7 @@
       </c>
     </row>
     <row r="9" spans="4:7" x14ac:dyDescent="0.3">
-      <c r="D9" s="5"/>
+      <c r="D9" s="4"/>
       <c r="E9" t="s">
         <v>13</v>
       </c>
@@ -1963,7 +2305,7 @@
       </c>
     </row>
     <row r="10" spans="4:7" x14ac:dyDescent="0.3">
-      <c r="D10" s="5"/>
+      <c r="D10" s="4"/>
       <c r="E10" t="s">
         <v>14</v>
       </c>
@@ -1975,7 +2317,7 @@
       </c>
     </row>
     <row r="11" spans="4:7" x14ac:dyDescent="0.3">
-      <c r="D11" s="5"/>
+      <c r="D11" s="4"/>
       <c r="E11" t="s">
         <v>15</v>
       </c>
@@ -1993,7 +2335,7 @@
       <c r="G12" s="6"/>
     </row>
     <row r="13" spans="4:7" x14ac:dyDescent="0.3">
-      <c r="D13" s="5">
+      <c r="D13" s="4">
         <v>2</v>
       </c>
       <c r="E13" t="s">
@@ -2007,7 +2349,7 @@
       </c>
     </row>
     <row r="14" spans="4:7" x14ac:dyDescent="0.3">
-      <c r="D14" s="5"/>
+      <c r="D14" s="4"/>
       <c r="E14" t="s">
         <v>10</v>
       </c>
@@ -2019,7 +2361,7 @@
       </c>
     </row>
     <row r="15" spans="4:7" x14ac:dyDescent="0.3">
-      <c r="D15" s="5"/>
+      <c r="D15" s="4"/>
       <c r="E15" t="s">
         <v>11</v>
       </c>
@@ -2031,7 +2373,7 @@
       </c>
     </row>
     <row r="16" spans="4:7" x14ac:dyDescent="0.3">
-      <c r="D16" s="5"/>
+      <c r="D16" s="4"/>
       <c r="E16" t="s">
         <v>12</v>
       </c>
@@ -2043,7 +2385,7 @@
       </c>
     </row>
     <row r="17" spans="4:7" x14ac:dyDescent="0.3">
-      <c r="D17" s="5"/>
+      <c r="D17" s="4"/>
       <c r="E17" t="s">
         <v>13</v>
       </c>
@@ -2055,7 +2397,7 @@
       </c>
     </row>
     <row r="18" spans="4:7" x14ac:dyDescent="0.3">
-      <c r="D18" s="5"/>
+      <c r="D18" s="4"/>
       <c r="E18" t="s">
         <v>14</v>
       </c>
@@ -2067,7 +2409,7 @@
       </c>
     </row>
     <row r="19" spans="4:7" x14ac:dyDescent="0.3">
-      <c r="D19" s="5"/>
+      <c r="D19" s="4"/>
       <c r="E19" t="s">
         <v>15</v>
       </c>
@@ -2079,13 +2421,13 @@
       </c>
     </row>
     <row r="20" spans="4:7" x14ac:dyDescent="0.3">
-      <c r="D20" s="4"/>
-      <c r="E20" s="4"/>
-      <c r="F20" s="4"/>
-      <c r="G20" s="4"/>
+      <c r="D20" s="5"/>
+      <c r="E20" s="5"/>
+      <c r="F20" s="5"/>
+      <c r="G20" s="5"/>
     </row>
     <row r="21" spans="4:7" x14ac:dyDescent="0.3">
-      <c r="D21" s="5">
+      <c r="D21" s="4">
         <v>3</v>
       </c>
       <c r="E21" t="s">
@@ -2099,7 +2441,7 @@
       </c>
     </row>
     <row r="22" spans="4:7" x14ac:dyDescent="0.3">
-      <c r="D22" s="5"/>
+      <c r="D22" s="4"/>
       <c r="E22" t="s">
         <v>10</v>
       </c>
@@ -2111,7 +2453,7 @@
       </c>
     </row>
     <row r="23" spans="4:7" x14ac:dyDescent="0.3">
-      <c r="D23" s="5"/>
+      <c r="D23" s="4"/>
       <c r="E23" t="s">
         <v>11</v>
       </c>
@@ -2123,7 +2465,7 @@
       </c>
     </row>
     <row r="24" spans="4:7" x14ac:dyDescent="0.3">
-      <c r="D24" s="5"/>
+      <c r="D24" s="4"/>
       <c r="E24" t="s">
         <v>12</v>
       </c>
@@ -2135,7 +2477,7 @@
       </c>
     </row>
     <row r="25" spans="4:7" x14ac:dyDescent="0.3">
-      <c r="D25" s="5"/>
+      <c r="D25" s="4"/>
       <c r="E25" t="s">
         <v>13</v>
       </c>
@@ -2147,7 +2489,7 @@
       </c>
     </row>
     <row r="26" spans="4:7" x14ac:dyDescent="0.3">
-      <c r="D26" s="5"/>
+      <c r="D26" s="4"/>
       <c r="E26" t="s">
         <v>14</v>
       </c>
@@ -2159,7 +2501,7 @@
       </c>
     </row>
     <row r="27" spans="4:7" x14ac:dyDescent="0.3">
-      <c r="D27" s="5"/>
+      <c r="D27" s="4"/>
       <c r="E27" t="s">
         <v>15</v>
       </c>
@@ -2171,13 +2513,13 @@
       </c>
     </row>
     <row r="28" spans="4:7" x14ac:dyDescent="0.3">
-      <c r="D28" s="4"/>
-      <c r="E28" s="4"/>
-      <c r="F28" s="4"/>
-      <c r="G28" s="4"/>
+      <c r="D28" s="5"/>
+      <c r="E28" s="5"/>
+      <c r="F28" s="5"/>
+      <c r="G28" s="5"/>
     </row>
     <row r="29" spans="4:7" x14ac:dyDescent="0.3">
-      <c r="D29" s="5">
+      <c r="D29" s="4">
         <v>4</v>
       </c>
       <c r="E29" t="s">
@@ -2191,7 +2533,7 @@
       </c>
     </row>
     <row r="30" spans="4:7" x14ac:dyDescent="0.3">
-      <c r="D30" s="5"/>
+      <c r="D30" s="4"/>
       <c r="E30" t="s">
         <v>10</v>
       </c>
@@ -2203,7 +2545,7 @@
       </c>
     </row>
     <row r="31" spans="4:7" x14ac:dyDescent="0.3">
-      <c r="D31" s="5"/>
+      <c r="D31" s="4"/>
       <c r="E31" t="s">
         <v>11</v>
       </c>
@@ -2215,7 +2557,7 @@
       </c>
     </row>
     <row r="32" spans="4:7" x14ac:dyDescent="0.3">
-      <c r="D32" s="5"/>
+      <c r="D32" s="4"/>
       <c r="E32" t="s">
         <v>12</v>
       </c>
@@ -2227,7 +2569,7 @@
       </c>
     </row>
     <row r="33" spans="4:7" x14ac:dyDescent="0.3">
-      <c r="D33" s="5"/>
+      <c r="D33" s="4"/>
       <c r="E33" t="s">
         <v>13</v>
       </c>
@@ -2239,7 +2581,7 @@
       </c>
     </row>
     <row r="34" spans="4:7" x14ac:dyDescent="0.3">
-      <c r="D34" s="5"/>
+      <c r="D34" s="4"/>
       <c r="E34" t="s">
         <v>14</v>
       </c>
@@ -2251,7 +2593,7 @@
       </c>
     </row>
     <row r="35" spans="4:7" x14ac:dyDescent="0.3">
-      <c r="D35" s="5"/>
+      <c r="D35" s="4"/>
       <c r="E35" t="s">
         <v>15</v>
       </c>
@@ -2263,13 +2605,107 @@
       </c>
     </row>
     <row r="36" spans="4:7" x14ac:dyDescent="0.3">
-      <c r="D36" s="4"/>
-      <c r="E36" s="4"/>
-      <c r="F36" s="4"/>
-      <c r="G36" s="4"/>
+      <c r="D36" s="5"/>
+      <c r="E36" s="5"/>
+      <c r="F36" s="5"/>
+      <c r="G36" s="5"/>
+    </row>
+    <row r="37" spans="4:7" x14ac:dyDescent="0.3">
+      <c r="D37" s="4">
+        <v>5</v>
+      </c>
+      <c r="E37" t="s">
+        <v>16</v>
+      </c>
+      <c r="F37">
+        <v>8.3333000000000004E-2</v>
+      </c>
+      <c r="G37">
+        <v>95.155683999999994</v>
+      </c>
+    </row>
+    <row r="38" spans="4:7" x14ac:dyDescent="0.3">
+      <c r="D38" s="4"/>
+      <c r="E38" t="s">
+        <v>10</v>
+      </c>
+      <c r="F38">
+        <v>8.3333000000000004E-2</v>
+      </c>
+      <c r="G38">
+        <v>91.139943000000002</v>
+      </c>
+    </row>
+    <row r="39" spans="4:7" x14ac:dyDescent="0.3">
+      <c r="D39" s="4"/>
+      <c r="E39" t="s">
+        <v>11</v>
+      </c>
+      <c r="F39">
+        <v>8.3333000000000004E-2</v>
+      </c>
+      <c r="G39">
+        <v>50.897694999999999</v>
+      </c>
+    </row>
+    <row r="40" spans="4:7" x14ac:dyDescent="0.3">
+      <c r="D40" s="4"/>
+      <c r="E40" t="s">
+        <v>12</v>
+      </c>
+      <c r="F40">
+        <v>4.1667000000000003E-2</v>
+      </c>
+      <c r="G40">
+        <v>45.668508000000003</v>
+      </c>
+    </row>
+    <row r="41" spans="4:7" x14ac:dyDescent="0.3">
+      <c r="D41" s="4"/>
+      <c r="E41" t="s">
+        <v>13</v>
+      </c>
+      <c r="F41">
+        <v>4.1667000000000003E-2</v>
+      </c>
+      <c r="G41">
+        <v>61.417313999999998</v>
+      </c>
+    </row>
+    <row r="42" spans="4:7" x14ac:dyDescent="0.3">
+      <c r="D42" s="4"/>
+      <c r="E42" t="s">
+        <v>14</v>
+      </c>
+      <c r="F42">
+        <v>4.1667000000000003E-2</v>
+      </c>
+      <c r="G42">
+        <v>8.7120560000000005</v>
+      </c>
+    </row>
+    <row r="43" spans="4:7" x14ac:dyDescent="0.3">
+      <c r="D43" s="4"/>
+      <c r="E43" t="s">
+        <v>15</v>
+      </c>
+      <c r="F43">
+        <v>8.3333000000000004E-2</v>
+      </c>
+      <c r="G43">
+        <v>89.088755000000006</v>
+      </c>
+    </row>
+    <row r="44" spans="4:7" x14ac:dyDescent="0.3">
+      <c r="D44" s="5"/>
+      <c r="E44" s="5"/>
+      <c r="F44" s="5"/>
+      <c r="G44" s="5"/>
     </row>
   </sheetData>
-  <mergeCells count="8">
+  <mergeCells count="10">
+    <mergeCell ref="D37:D43"/>
+    <mergeCell ref="D44:G44"/>
     <mergeCell ref="D29:D35"/>
     <mergeCell ref="D36:G36"/>
     <mergeCell ref="D28:G28"/>

--- a/shatrov_bootstraps_res.xlsx
+++ b/shatrov_bootstraps_res.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Игорь\Desktop\sem_8\mipt_diplom\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{87B0526A-92FE-4B67-9D1D-F981FFEF7C5B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FD6E5DF1-8291-43E0-9B49-6D5022E4162B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Информация про ряды" sheetId="1" r:id="rId1"/>
@@ -29,7 +29,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="186" uniqueCount="32">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="359" uniqueCount="32">
   <si>
     <t>Номер</t>
   </si>
@@ -100,9 +100,6 @@
     <t>Отсутствует тренд</t>
   </si>
   <si>
-    <t>Для этого ряда ARIMA напрогнозировала что-то совсем не то</t>
-  </si>
-  <si>
     <t>https://raw.githubusercontent.com/jbrownlee/Datasets/master/monthly_champagne_sales.csv</t>
   </si>
   <si>
@@ -125,6 +122,9 @@
   </si>
   <si>
     <t>Monthly Writing Paper Sales</t>
+  </si>
+  <si>
+    <t>Winkler</t>
   </si>
 </sst>
 </file>
@@ -205,6 +205,9 @@
     </xf>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -213,9 +216,6 @@
     </xf>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="1" applyAlignment="1">
-      <alignment vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
@@ -501,6 +501,7 @@
   <dimension ref="D4:G9"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
+    <col min="5" max="5" width="17" customWidth="1"/>
     <col min="6" max="6" width="8.88671875" customWidth="1"/>
   </cols>
   <sheetData>
@@ -551,13 +552,13 @@
         <v>3</v>
       </c>
       <c r="E7" t="s">
+        <v>24</v>
+      </c>
+      <c r="F7" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="G7" t="s">
         <v>25</v>
-      </c>
-      <c r="F7" s="1" t="s">
-        <v>24</v>
-      </c>
-      <c r="G7" t="s">
-        <v>26</v>
       </c>
     </row>
     <row r="8" spans="4:7" x14ac:dyDescent="0.3">
@@ -565,13 +566,13 @@
         <v>4</v>
       </c>
       <c r="E8" t="s">
+        <v>26</v>
+      </c>
+      <c r="F8" s="1" t="s">
         <v>27</v>
       </c>
-      <c r="F8" s="1" t="s">
+      <c r="G8" t="s">
         <v>28</v>
-      </c>
-      <c r="G8" t="s">
-        <v>29</v>
       </c>
     </row>
     <row r="9" spans="4:7" x14ac:dyDescent="0.3">
@@ -579,10 +580,10 @@
         <v>5</v>
       </c>
       <c r="E9" t="s">
-        <v>31</v>
-      </c>
-      <c r="F9" s="7" t="s">
         <v>30</v>
+      </c>
+      <c r="F9" s="4" t="s">
+        <v>29</v>
       </c>
       <c r="G9" t="s">
         <v>21</v>
@@ -598,14 +599,22 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5432242B-BB45-4574-A5B4-2CF25C9CDCFF}">
-  <dimension ref="D4:H49"/>
+  <dimension ref="D3:O49"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="4" max="4" width="13.21875" customWidth="1"/>
     <col min="5" max="5" width="30.109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="4" spans="4:7" x14ac:dyDescent="0.3">
+    <row r="3" spans="4:15" x14ac:dyDescent="0.3">
+      <c r="E3">
+        <v>95</v>
+      </c>
+      <c r="L3">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="4" spans="4:15" x14ac:dyDescent="0.3">
       <c r="D4" t="s">
         <v>5</v>
       </c>
@@ -618,9 +627,27 @@
       <c r="G4" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="5" spans="4:7" x14ac:dyDescent="0.3">
-      <c r="D5" s="4">
+      <c r="H4" t="s">
+        <v>31</v>
+      </c>
+      <c r="K4" t="s">
+        <v>5</v>
+      </c>
+      <c r="L4" t="s">
+        <v>6</v>
+      </c>
+      <c r="M4" t="s">
+        <v>7</v>
+      </c>
+      <c r="N4" t="s">
+        <v>8</v>
+      </c>
+      <c r="O4" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="5" spans="4:15" x14ac:dyDescent="0.3">
+      <c r="D5" s="5">
         <v>1</v>
       </c>
       <c r="E5" t="s">
@@ -630,35 +657,85 @@
         <v>0.875</v>
       </c>
       <c r="G5" s="2">
-        <v>118.55475</v>
-      </c>
-    </row>
-    <row r="6" spans="4:7" x14ac:dyDescent="0.3">
-      <c r="D6" s="4"/>
+        <v>118.179372</v>
+      </c>
+      <c r="H5">
+        <v>143.500314</v>
+      </c>
+      <c r="K5" s="5">
+        <v>1</v>
+      </c>
+      <c r="L5" t="s">
+        <v>9</v>
+      </c>
+      <c r="M5" s="2">
+        <v>0.625</v>
+      </c>
+      <c r="N5" s="2">
+        <v>77.273337999999995</v>
+      </c>
+      <c r="O5">
+        <v>118.3819</v>
+      </c>
+    </row>
+    <row r="6" spans="4:15" x14ac:dyDescent="0.3">
+      <c r="D6" s="5"/>
       <c r="E6" t="s">
         <v>16</v>
       </c>
       <c r="F6" s="2">
-        <v>0.91666700000000001</v>
+        <v>0.875</v>
       </c>
       <c r="G6" s="2">
-        <v>118.711969</v>
-      </c>
-    </row>
-    <row r="7" spans="4:7" x14ac:dyDescent="0.3">
-      <c r="D7" s="4"/>
+        <v>115.74259499999999</v>
+      </c>
+      <c r="H6">
+        <v>150.915347</v>
+      </c>
+      <c r="K6" s="5"/>
+      <c r="L6" t="s">
+        <v>16</v>
+      </c>
+      <c r="M6" s="2">
+        <v>0.625</v>
+      </c>
+      <c r="N6" s="2">
+        <v>75.155488000000005</v>
+      </c>
+      <c r="O6">
+        <v>119.759912</v>
+      </c>
+    </row>
+    <row r="7" spans="4:15" x14ac:dyDescent="0.3">
+      <c r="D7" s="5"/>
       <c r="E7" t="s">
         <v>10</v>
       </c>
       <c r="F7" s="2">
-        <v>0.875</v>
+        <v>0.91666700000000001</v>
       </c>
       <c r="G7" s="2">
-        <v>115.279622</v>
-      </c>
-    </row>
-    <row r="8" spans="4:7" x14ac:dyDescent="0.3">
-      <c r="D8" s="4"/>
+        <v>117.083185</v>
+      </c>
+      <c r="H7">
+        <v>148.672079</v>
+      </c>
+      <c r="K7" s="5"/>
+      <c r="L7" t="s">
+        <v>10</v>
+      </c>
+      <c r="M7" s="2">
+        <v>0.625</v>
+      </c>
+      <c r="N7" s="2">
+        <v>74.915011000000007</v>
+      </c>
+      <c r="O7">
+        <v>120.54208800000001</v>
+      </c>
+    </row>
+    <row r="8" spans="4:15" x14ac:dyDescent="0.3">
+      <c r="D8" s="5"/>
       <c r="E8" t="s">
         <v>11</v>
       </c>
@@ -666,35 +743,83 @@
         <v>0.875</v>
       </c>
       <c r="G8" s="2">
-        <v>119.993579</v>
-      </c>
-    </row>
-    <row r="9" spans="4:7" x14ac:dyDescent="0.3">
-      <c r="D9" s="4"/>
+        <v>117.113354</v>
+      </c>
+      <c r="H8">
+        <v>150.813064</v>
+      </c>
+      <c r="K8" s="5"/>
+      <c r="L8" t="s">
+        <v>11</v>
+      </c>
+      <c r="M8" s="2">
+        <v>0.625</v>
+      </c>
+      <c r="N8" s="2">
+        <v>76.965551000000005</v>
+      </c>
+      <c r="O8">
+        <v>123.222641</v>
+      </c>
+    </row>
+    <row r="9" spans="4:15" x14ac:dyDescent="0.3">
+      <c r="D9" s="5"/>
       <c r="E9" t="s">
         <v>12</v>
       </c>
       <c r="F9" s="2">
-        <v>0.91666700000000001</v>
+        <v>0.875</v>
       </c>
       <c r="G9" s="2">
-        <v>121.680055</v>
-      </c>
-    </row>
-    <row r="10" spans="4:7" x14ac:dyDescent="0.3">
-      <c r="D10" s="4"/>
+        <v>116.877878</v>
+      </c>
+      <c r="H9">
+        <v>140.04197600000001</v>
+      </c>
+      <c r="K9" s="5"/>
+      <c r="L9" t="s">
+        <v>12</v>
+      </c>
+      <c r="M9" s="2">
+        <v>0.66666700000000001</v>
+      </c>
+      <c r="N9" s="2">
+        <v>78.088255000000004</v>
+      </c>
+      <c r="O9">
+        <v>115.19004099999999</v>
+      </c>
+    </row>
+    <row r="10" spans="4:15" x14ac:dyDescent="0.3">
+      <c r="D10" s="5"/>
       <c r="E10" t="s">
         <v>13</v>
       </c>
       <c r="F10" s="2">
-        <v>0.54166700000000001</v>
+        <v>0.5</v>
       </c>
       <c r="G10" s="2">
-        <v>53.712603000000001</v>
-      </c>
-    </row>
-    <row r="11" spans="4:7" x14ac:dyDescent="0.3">
-      <c r="D11" s="4"/>
+        <v>53.761783000000001</v>
+      </c>
+      <c r="H10">
+        <v>325.66419200000001</v>
+      </c>
+      <c r="K10" s="5"/>
+      <c r="L10" t="s">
+        <v>13</v>
+      </c>
+      <c r="M10" s="2">
+        <v>0.25</v>
+      </c>
+      <c r="N10" s="2">
+        <v>35.837428000000003</v>
+      </c>
+      <c r="O10">
+        <v>160.04055</v>
+      </c>
+    </row>
+    <row r="11" spans="4:15" x14ac:dyDescent="0.3">
+      <c r="D11" s="5"/>
       <c r="E11" t="s">
         <v>14</v>
       </c>
@@ -702,11 +827,27 @@
         <v>0.91666700000000001</v>
       </c>
       <c r="G11" s="2">
-        <v>116.15567900000001</v>
-      </c>
-    </row>
-    <row r="12" spans="4:7" x14ac:dyDescent="0.3">
-      <c r="D12" s="4"/>
+        <v>119.029605</v>
+      </c>
+      <c r="H11">
+        <v>139.67133799999999</v>
+      </c>
+      <c r="K11" s="5"/>
+      <c r="L11" t="s">
+        <v>14</v>
+      </c>
+      <c r="M11" s="2">
+        <v>0.70833299999999999</v>
+      </c>
+      <c r="N11" s="2">
+        <v>78.283085999999997</v>
+      </c>
+      <c r="O11">
+        <v>120.01003900000001</v>
+      </c>
+    </row>
+    <row r="12" spans="4:15" x14ac:dyDescent="0.3">
+      <c r="D12" s="5"/>
       <c r="E12" t="s">
         <v>15</v>
       </c>
@@ -714,17 +855,39 @@
         <v>0.875</v>
       </c>
       <c r="G12" s="2">
-        <v>115.049564</v>
-      </c>
-    </row>
-    <row r="13" spans="4:7" x14ac:dyDescent="0.3">
-      <c r="D13" s="5"/>
-      <c r="E13" s="5"/>
-      <c r="F13" s="5"/>
-      <c r="G13" s="5"/>
-    </row>
-    <row r="14" spans="4:7" x14ac:dyDescent="0.3">
-      <c r="D14" s="4">
+        <v>119.382682</v>
+      </c>
+      <c r="H12">
+        <v>153.092061</v>
+      </c>
+      <c r="K12" s="5"/>
+      <c r="L12" t="s">
+        <v>15</v>
+      </c>
+      <c r="M12" s="2">
+        <v>0.625</v>
+      </c>
+      <c r="N12" s="2">
+        <v>76.855543999999995</v>
+      </c>
+      <c r="O12">
+        <v>120.149435</v>
+      </c>
+    </row>
+    <row r="13" spans="4:15" x14ac:dyDescent="0.3">
+      <c r="D13" s="6"/>
+      <c r="E13" s="6"/>
+      <c r="F13" s="6"/>
+      <c r="G13" s="6"/>
+      <c r="H13" s="6"/>
+      <c r="K13" s="6"/>
+      <c r="L13" s="6"/>
+      <c r="M13" s="6"/>
+      <c r="N13" s="6"/>
+      <c r="O13" s="6"/>
+    </row>
+    <row r="14" spans="4:15" x14ac:dyDescent="0.3">
+      <c r="D14" s="5">
         <v>2</v>
       </c>
       <c r="E14" t="s">
@@ -734,11 +897,29 @@
         <v>1</v>
       </c>
       <c r="G14">
-        <v>10.445423</v>
-      </c>
-    </row>
-    <row r="15" spans="4:7" x14ac:dyDescent="0.3">
-      <c r="D15" s="4"/>
+        <v>10.485419</v>
+      </c>
+      <c r="H14">
+        <v>10.485419</v>
+      </c>
+      <c r="K14" s="5">
+        <v>2</v>
+      </c>
+      <c r="L14" t="s">
+        <v>9</v>
+      </c>
+      <c r="M14">
+        <v>0.91666700000000001</v>
+      </c>
+      <c r="N14">
+        <v>6.8560470000000002</v>
+      </c>
+      <c r="O14">
+        <v>7.2227560000000004</v>
+      </c>
+    </row>
+    <row r="15" spans="4:15" x14ac:dyDescent="0.3">
+      <c r="D15" s="5"/>
       <c r="E15" t="s">
         <v>16</v>
       </c>
@@ -746,11 +927,27 @@
         <v>1</v>
       </c>
       <c r="G15">
-        <v>10.442648</v>
-      </c>
-    </row>
-    <row r="16" spans="4:7" x14ac:dyDescent="0.3">
-      <c r="D16" s="4"/>
+        <v>10.470326</v>
+      </c>
+      <c r="H15">
+        <v>10.470326</v>
+      </c>
+      <c r="K15" s="5"/>
+      <c r="L15" t="s">
+        <v>16</v>
+      </c>
+      <c r="M15">
+        <v>0.91666700000000001</v>
+      </c>
+      <c r="N15">
+        <v>6.7783509999999998</v>
+      </c>
+      <c r="O15">
+        <v>7.1208200000000001</v>
+      </c>
+    </row>
+    <row r="16" spans="4:15" x14ac:dyDescent="0.3">
+      <c r="D16" s="5"/>
       <c r="E16" t="s">
         <v>10</v>
       </c>
@@ -758,11 +955,27 @@
         <v>1</v>
       </c>
       <c r="G16">
-        <v>10.353051000000001</v>
-      </c>
-    </row>
-    <row r="17" spans="4:8" x14ac:dyDescent="0.3">
-      <c r="D17" s="4"/>
+        <v>10.348589</v>
+      </c>
+      <c r="H16">
+        <v>10.348589</v>
+      </c>
+      <c r="K16" s="5"/>
+      <c r="L16" t="s">
+        <v>10</v>
+      </c>
+      <c r="M16">
+        <v>0.91666700000000001</v>
+      </c>
+      <c r="N16">
+        <v>6.9377240000000002</v>
+      </c>
+      <c r="O16">
+        <v>7.2910029999999999</v>
+      </c>
+    </row>
+    <row r="17" spans="4:15" x14ac:dyDescent="0.3">
+      <c r="D17" s="5"/>
       <c r="E17" t="s">
         <v>11</v>
       </c>
@@ -770,11 +983,27 @@
         <v>1</v>
       </c>
       <c r="G17">
-        <v>10.348001</v>
-      </c>
-    </row>
-    <row r="18" spans="4:8" x14ac:dyDescent="0.3">
-      <c r="D18" s="4"/>
+        <v>10.574653</v>
+      </c>
+      <c r="H17">
+        <v>10.574653</v>
+      </c>
+      <c r="K17" s="5"/>
+      <c r="L17" t="s">
+        <v>11</v>
+      </c>
+      <c r="M17">
+        <v>0.91666700000000001</v>
+      </c>
+      <c r="N17">
+        <v>6.8679759999999996</v>
+      </c>
+      <c r="O17">
+        <v>6.9669049999999997</v>
+      </c>
+    </row>
+    <row r="18" spans="4:15" x14ac:dyDescent="0.3">
+      <c r="D18" s="5"/>
       <c r="E18" t="s">
         <v>12</v>
       </c>
@@ -782,11 +1011,27 @@
         <v>1</v>
       </c>
       <c r="G18">
-        <v>10.370028</v>
-      </c>
-    </row>
-    <row r="19" spans="4:8" x14ac:dyDescent="0.3">
-      <c r="D19" s="4"/>
+        <v>10.536203</v>
+      </c>
+      <c r="H18">
+        <v>10.536203</v>
+      </c>
+      <c r="K18" s="5"/>
+      <c r="L18" t="s">
+        <v>12</v>
+      </c>
+      <c r="M18">
+        <v>0.91666700000000001</v>
+      </c>
+      <c r="N18">
+        <v>6.7783360000000004</v>
+      </c>
+      <c r="O18">
+        <v>7.1565909999999997</v>
+      </c>
+    </row>
+    <row r="19" spans="4:15" x14ac:dyDescent="0.3">
+      <c r="D19" s="5"/>
       <c r="E19" t="s">
         <v>13</v>
       </c>
@@ -794,11 +1039,27 @@
         <v>1</v>
       </c>
       <c r="G19">
-        <v>10.634069999999999</v>
-      </c>
-    </row>
-    <row r="20" spans="4:8" x14ac:dyDescent="0.3">
-      <c r="D20" s="4"/>
+        <v>10.697803</v>
+      </c>
+      <c r="H19">
+        <v>10.697803</v>
+      </c>
+      <c r="K19" s="5"/>
+      <c r="L19" t="s">
+        <v>13</v>
+      </c>
+      <c r="M19">
+        <v>0.83333299999999999</v>
+      </c>
+      <c r="N19">
+        <v>6.1506439999999998</v>
+      </c>
+      <c r="O19">
+        <v>7.005674</v>
+      </c>
+    </row>
+    <row r="20" spans="4:15" x14ac:dyDescent="0.3">
+      <c r="D20" s="5"/>
       <c r="E20" t="s">
         <v>14</v>
       </c>
@@ -806,11 +1067,27 @@
         <v>1</v>
       </c>
       <c r="G20">
-        <v>10.265594999999999</v>
-      </c>
-    </row>
-    <row r="21" spans="4:8" x14ac:dyDescent="0.3">
-      <c r="D21" s="4"/>
+        <v>10.382915000000001</v>
+      </c>
+      <c r="H20">
+        <v>10.382915000000001</v>
+      </c>
+      <c r="K20" s="5"/>
+      <c r="L20" t="s">
+        <v>14</v>
+      </c>
+      <c r="M20">
+        <v>0.91666700000000001</v>
+      </c>
+      <c r="N20">
+        <v>6.8462230000000002</v>
+      </c>
+      <c r="O20">
+        <v>7.1439649999999997</v>
+      </c>
+    </row>
+    <row r="21" spans="4:15" x14ac:dyDescent="0.3">
+      <c r="D21" s="5"/>
       <c r="E21" t="s">
         <v>15</v>
       </c>
@@ -818,17 +1095,39 @@
         <v>1</v>
       </c>
       <c r="G21">
-        <v>10.528846</v>
-      </c>
-    </row>
-    <row r="22" spans="4:8" x14ac:dyDescent="0.3">
-      <c r="D22" s="5"/>
-      <c r="E22" s="5"/>
-      <c r="F22" s="5"/>
-      <c r="G22" s="5"/>
-    </row>
-    <row r="23" spans="4:8" x14ac:dyDescent="0.3">
-      <c r="D23" s="4">
+        <v>10.438907</v>
+      </c>
+      <c r="H21">
+        <v>10.438907</v>
+      </c>
+      <c r="K21" s="5"/>
+      <c r="L21" t="s">
+        <v>15</v>
+      </c>
+      <c r="M21">
+        <v>0.91666700000000001</v>
+      </c>
+      <c r="N21">
+        <v>6.8196139999999996</v>
+      </c>
+      <c r="O21">
+        <v>7.1616650000000002</v>
+      </c>
+    </row>
+    <row r="22" spans="4:15" x14ac:dyDescent="0.3">
+      <c r="D22" s="6"/>
+      <c r="E22" s="6"/>
+      <c r="F22" s="6"/>
+      <c r="G22" s="6"/>
+      <c r="H22" s="6"/>
+      <c r="K22" s="6"/>
+      <c r="L22" s="6"/>
+      <c r="M22" s="6"/>
+      <c r="N22" s="6"/>
+      <c r="O22" s="6"/>
+    </row>
+    <row r="23" spans="4:15" x14ac:dyDescent="0.3">
+      <c r="D23" s="5">
         <v>3</v>
       </c>
       <c r="E23" t="s">
@@ -838,14 +1137,29 @@
         <v>1</v>
       </c>
       <c r="G23">
-        <v>329225.10081099998</v>
-      </c>
-      <c r="H23" t="s">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="24" spans="4:8" x14ac:dyDescent="0.3">
-      <c r="D24" s="4"/>
+        <v>330198.33854000003</v>
+      </c>
+      <c r="H23">
+        <v>330198.33854000003</v>
+      </c>
+      <c r="K23" s="5">
+        <v>3</v>
+      </c>
+      <c r="L23" t="s">
+        <v>9</v>
+      </c>
+      <c r="M23">
+        <v>0.95</v>
+      </c>
+      <c r="N23">
+        <v>215905.08858000001</v>
+      </c>
+      <c r="O23">
+        <v>216085.57585600001</v>
+      </c>
+    </row>
+    <row r="24" spans="4:15" x14ac:dyDescent="0.3">
+      <c r="D24" s="5"/>
       <c r="E24" t="s">
         <v>16</v>
       </c>
@@ -853,11 +1167,27 @@
         <v>1</v>
       </c>
       <c r="G24">
-        <v>323506.65818299999</v>
-      </c>
-    </row>
-    <row r="25" spans="4:8" x14ac:dyDescent="0.3">
-      <c r="D25" s="4"/>
+        <v>325785.91720199998</v>
+      </c>
+      <c r="H24">
+        <v>325785.91720199998</v>
+      </c>
+      <c r="K24" s="5"/>
+      <c r="L24" t="s">
+        <v>16</v>
+      </c>
+      <c r="M24">
+        <v>0.95</v>
+      </c>
+      <c r="N24">
+        <v>220470.85797000001</v>
+      </c>
+      <c r="O24">
+        <v>220667.08983899999</v>
+      </c>
+    </row>
+    <row r="25" spans="4:15" x14ac:dyDescent="0.3">
+      <c r="D25" s="5"/>
       <c r="E25" t="s">
         <v>10</v>
       </c>
@@ -865,11 +1195,27 @@
         <v>1</v>
       </c>
       <c r="G25">
-        <v>323403.41790900001</v>
-      </c>
-    </row>
-    <row r="26" spans="4:8" x14ac:dyDescent="0.3">
-      <c r="D26" s="4"/>
+        <v>346602.01306199998</v>
+      </c>
+      <c r="H25">
+        <v>346602.01306199998</v>
+      </c>
+      <c r="K25" s="5"/>
+      <c r="L25" t="s">
+        <v>10</v>
+      </c>
+      <c r="M25">
+        <v>0.95</v>
+      </c>
+      <c r="N25">
+        <v>218095.634983</v>
+      </c>
+      <c r="O25">
+        <v>218233.176546</v>
+      </c>
+    </row>
+    <row r="26" spans="4:15" x14ac:dyDescent="0.3">
+      <c r="D26" s="5"/>
       <c r="E26" t="s">
         <v>11</v>
       </c>
@@ -877,11 +1223,27 @@
         <v>1</v>
       </c>
       <c r="G26">
-        <v>319829.36786699999</v>
-      </c>
-    </row>
-    <row r="27" spans="4:8" x14ac:dyDescent="0.3">
-      <c r="D27" s="4"/>
+        <v>324640.63021500001</v>
+      </c>
+      <c r="H26">
+        <v>324640.63021500001</v>
+      </c>
+      <c r="K26" s="5"/>
+      <c r="L26" t="s">
+        <v>11</v>
+      </c>
+      <c r="M26">
+        <v>0.95</v>
+      </c>
+      <c r="N26">
+        <v>222161.98621599999</v>
+      </c>
+      <c r="O26">
+        <v>222341.84054199999</v>
+      </c>
+    </row>
+    <row r="27" spans="4:15" x14ac:dyDescent="0.3">
+      <c r="D27" s="5"/>
       <c r="E27" t="s">
         <v>12</v>
       </c>
@@ -889,23 +1251,55 @@
         <v>1</v>
       </c>
       <c r="G27">
-        <v>327693.045598</v>
-      </c>
-    </row>
-    <row r="28" spans="4:8" x14ac:dyDescent="0.3">
-      <c r="D28" s="4"/>
+        <v>330300.32221100002</v>
+      </c>
+      <c r="H27">
+        <v>330300.32221100002</v>
+      </c>
+      <c r="K27" s="5"/>
+      <c r="L27" t="s">
+        <v>12</v>
+      </c>
+      <c r="M27">
+        <v>0.95</v>
+      </c>
+      <c r="N27">
+        <v>208402.429634</v>
+      </c>
+      <c r="O27">
+        <v>208676.04598600001</v>
+      </c>
+    </row>
+    <row r="28" spans="4:15" x14ac:dyDescent="0.3">
+      <c r="D28" s="5"/>
       <c r="E28" t="s">
         <v>13</v>
       </c>
       <c r="F28">
+        <v>0.25</v>
+      </c>
+      <c r="G28">
+        <v>11784.516629</v>
+      </c>
+      <c r="H28">
+        <v>1628735.769816</v>
+      </c>
+      <c r="K28" s="5"/>
+      <c r="L28" t="s">
+        <v>13</v>
+      </c>
+      <c r="M28">
         <v>0.2</v>
       </c>
-      <c r="G28">
-        <v>12255.272467000001</v>
-      </c>
-    </row>
-    <row r="29" spans="4:8" x14ac:dyDescent="0.3">
-      <c r="D29" s="4"/>
+      <c r="N28">
+        <v>4912.1042049999996</v>
+      </c>
+      <c r="O28">
+        <v>416639.59496199997</v>
+      </c>
+    </row>
+    <row r="29" spans="4:15" x14ac:dyDescent="0.3">
+      <c r="D29" s="5"/>
       <c r="E29" t="s">
         <v>14</v>
       </c>
@@ -913,11 +1307,27 @@
         <v>1</v>
       </c>
       <c r="G29">
-        <v>321583.63291799999</v>
-      </c>
-    </row>
-    <row r="30" spans="4:8" x14ac:dyDescent="0.3">
-      <c r="D30" s="4"/>
+        <v>325348.234704</v>
+      </c>
+      <c r="H29">
+        <v>325348.234704</v>
+      </c>
+      <c r="K29" s="5"/>
+      <c r="L29" t="s">
+        <v>14</v>
+      </c>
+      <c r="M29">
+        <v>0.95</v>
+      </c>
+      <c r="N29">
+        <v>210816.71750299999</v>
+      </c>
+      <c r="O29">
+        <v>210985.93087099999</v>
+      </c>
+    </row>
+    <row r="30" spans="4:15" x14ac:dyDescent="0.3">
+      <c r="D30" s="5"/>
       <c r="E30" t="s">
         <v>15</v>
       </c>
@@ -925,17 +1335,39 @@
         <v>1</v>
       </c>
       <c r="G30">
-        <v>344760.60256199999</v>
-      </c>
-    </row>
-    <row r="31" spans="4:8" x14ac:dyDescent="0.3">
-      <c r="D31" s="5"/>
-      <c r="E31" s="5"/>
-      <c r="F31" s="5"/>
-      <c r="G31" s="5"/>
-    </row>
-    <row r="32" spans="4:8" x14ac:dyDescent="0.3">
-      <c r="D32" s="4">
+        <v>327440.46781599999</v>
+      </c>
+      <c r="H30">
+        <v>327440.46781599999</v>
+      </c>
+      <c r="K30" s="5"/>
+      <c r="L30" t="s">
+        <v>15</v>
+      </c>
+      <c r="M30">
+        <v>0.95</v>
+      </c>
+      <c r="N30">
+        <v>219074.26666200001</v>
+      </c>
+      <c r="O30">
+        <v>219268.92628499999</v>
+      </c>
+    </row>
+    <row r="31" spans="4:15" x14ac:dyDescent="0.3">
+      <c r="D31" s="6"/>
+      <c r="E31" s="6"/>
+      <c r="F31" s="6"/>
+      <c r="G31" s="6"/>
+      <c r="H31" s="6"/>
+      <c r="K31" s="6"/>
+      <c r="L31" s="6"/>
+      <c r="M31" s="6"/>
+      <c r="N31" s="6"/>
+      <c r="O31" s="6"/>
+    </row>
+    <row r="32" spans="4:15" x14ac:dyDescent="0.3">
+      <c r="D32" s="5">
         <v>4</v>
       </c>
       <c r="E32" t="s">
@@ -945,11 +1377,29 @@
         <v>0.83333299999999999</v>
       </c>
       <c r="G32">
-        <v>186.34364600000001</v>
-      </c>
-    </row>
-    <row r="33" spans="4:7" x14ac:dyDescent="0.3">
-      <c r="D33" s="4"/>
+        <v>186.34379100000001</v>
+      </c>
+      <c r="H32">
+        <v>411.41243400000002</v>
+      </c>
+      <c r="K32" s="5">
+        <v>4</v>
+      </c>
+      <c r="L32" t="s">
+        <v>9</v>
+      </c>
+      <c r="M32">
+        <v>0.625</v>
+      </c>
+      <c r="N32">
+        <v>121.843656</v>
+      </c>
+      <c r="O32">
+        <v>269.866491</v>
+      </c>
+    </row>
+    <row r="33" spans="4:15" x14ac:dyDescent="0.3">
+      <c r="D33" s="5"/>
       <c r="E33" t="s">
         <v>16</v>
       </c>
@@ -957,11 +1407,27 @@
         <v>0.83333299999999999</v>
       </c>
       <c r="G33">
-        <v>184.746667</v>
-      </c>
-    </row>
-    <row r="34" spans="4:7" x14ac:dyDescent="0.3">
-      <c r="D34" s="4"/>
+        <v>187.270577</v>
+      </c>
+      <c r="H33">
+        <v>406.96381200000002</v>
+      </c>
+      <c r="K33" s="5"/>
+      <c r="L33" t="s">
+        <v>16</v>
+      </c>
+      <c r="M33">
+        <v>0.625</v>
+      </c>
+      <c r="N33">
+        <v>121.33037299999999</v>
+      </c>
+      <c r="O33">
+        <v>264.086682</v>
+      </c>
+    </row>
+    <row r="34" spans="4:15" x14ac:dyDescent="0.3">
+      <c r="D34" s="5"/>
       <c r="E34" t="s">
         <v>10</v>
       </c>
@@ -969,11 +1435,27 @@
         <v>0.83333299999999999</v>
       </c>
       <c r="G34">
-        <v>189.48801599999999</v>
-      </c>
-    </row>
-    <row r="35" spans="4:7" x14ac:dyDescent="0.3">
-      <c r="D35" s="4"/>
+        <v>186.89030700000001</v>
+      </c>
+      <c r="H34">
+        <v>412.83118300000001</v>
+      </c>
+      <c r="K34" s="5"/>
+      <c r="L34" t="s">
+        <v>10</v>
+      </c>
+      <c r="M34">
+        <v>0.625</v>
+      </c>
+      <c r="N34">
+        <v>119.928978</v>
+      </c>
+      <c r="O34">
+        <v>272.91328099999998</v>
+      </c>
+    </row>
+    <row r="35" spans="4:15" x14ac:dyDescent="0.3">
+      <c r="D35" s="5"/>
       <c r="E35" t="s">
         <v>11</v>
       </c>
@@ -981,11 +1463,27 @@
         <v>0.83333299999999999</v>
       </c>
       <c r="G35">
-        <v>187.15413699999999</v>
-      </c>
-    </row>
-    <row r="36" spans="4:7" x14ac:dyDescent="0.3">
-      <c r="D36" s="4"/>
+        <v>191.33027899999999</v>
+      </c>
+      <c r="H35">
+        <v>399.21729900000003</v>
+      </c>
+      <c r="K35" s="5"/>
+      <c r="L35" t="s">
+        <v>11</v>
+      </c>
+      <c r="M35">
+        <v>0.625</v>
+      </c>
+      <c r="N35">
+        <v>121.545548</v>
+      </c>
+      <c r="O35">
+        <v>274.39187600000002</v>
+      </c>
+    </row>
+    <row r="36" spans="4:15" x14ac:dyDescent="0.3">
+      <c r="D36" s="5"/>
       <c r="E36" t="s">
         <v>12</v>
       </c>
@@ -993,23 +1491,55 @@
         <v>0.83333299999999999</v>
       </c>
       <c r="G36">
-        <v>183.13261199999999</v>
-      </c>
-    </row>
-    <row r="37" spans="4:7" x14ac:dyDescent="0.3">
-      <c r="D37" s="4"/>
+        <v>183.56060299999999</v>
+      </c>
+      <c r="H36">
+        <v>429.05745100000001</v>
+      </c>
+      <c r="K36" s="5"/>
+      <c r="L36" t="s">
+        <v>12</v>
+      </c>
+      <c r="M36">
+        <v>0.625</v>
+      </c>
+      <c r="N36">
+        <v>121.522802</v>
+      </c>
+      <c r="O36">
+        <v>270.89478100000002</v>
+      </c>
+    </row>
+    <row r="37" spans="4:15" x14ac:dyDescent="0.3">
+      <c r="D37" s="5"/>
       <c r="E37" t="s">
         <v>13</v>
       </c>
       <c r="F37">
-        <v>0.58333299999999999</v>
+        <v>0.54166700000000001</v>
       </c>
       <c r="G37">
-        <v>122.946945</v>
-      </c>
-    </row>
-    <row r="38" spans="4:7" x14ac:dyDescent="0.3">
-      <c r="D38" s="4"/>
+        <v>125.184408</v>
+      </c>
+      <c r="H37">
+        <v>666.45495700000004</v>
+      </c>
+      <c r="K37" s="5"/>
+      <c r="L37" t="s">
+        <v>13</v>
+      </c>
+      <c r="M37">
+        <v>0.54166700000000001</v>
+      </c>
+      <c r="N37">
+        <v>62.086235000000002</v>
+      </c>
+      <c r="O37">
+        <v>345.44335799999999</v>
+      </c>
+    </row>
+    <row r="38" spans="4:15" x14ac:dyDescent="0.3">
+      <c r="D38" s="5"/>
       <c r="E38" t="s">
         <v>14</v>
       </c>
@@ -1017,11 +1547,27 @@
         <v>0.83333299999999999</v>
       </c>
       <c r="G38">
-        <v>183.46469400000001</v>
-      </c>
-    </row>
-    <row r="39" spans="4:7" x14ac:dyDescent="0.3">
-      <c r="D39" s="4"/>
+        <v>183.55655999999999</v>
+      </c>
+      <c r="H38">
+        <v>407.70602000000002</v>
+      </c>
+      <c r="K38" s="5"/>
+      <c r="L38" t="s">
+        <v>14</v>
+      </c>
+      <c r="M38">
+        <v>0.625</v>
+      </c>
+      <c r="N38">
+        <v>121.451717</v>
+      </c>
+      <c r="O38">
+        <v>268.54494599999998</v>
+      </c>
+    </row>
+    <row r="39" spans="4:15" x14ac:dyDescent="0.3">
+      <c r="D39" s="5"/>
       <c r="E39" t="s">
         <v>15</v>
       </c>
@@ -1029,17 +1575,39 @@
         <v>0.83333299999999999</v>
       </c>
       <c r="G39">
-        <v>186.87345400000001</v>
-      </c>
-    </row>
-    <row r="40" spans="4:7" x14ac:dyDescent="0.3">
-      <c r="D40" s="5"/>
-      <c r="E40" s="5"/>
-      <c r="F40" s="5"/>
-      <c r="G40" s="5"/>
-    </row>
-    <row r="41" spans="4:7" x14ac:dyDescent="0.3">
-      <c r="D41" s="4">
+        <v>186.52072200000001</v>
+      </c>
+      <c r="H39">
+        <v>429.96469500000001</v>
+      </c>
+      <c r="K39" s="5"/>
+      <c r="L39" t="s">
+        <v>15</v>
+      </c>
+      <c r="M39">
+        <v>0.54166700000000001</v>
+      </c>
+      <c r="N39">
+        <v>121.288082</v>
+      </c>
+      <c r="O39">
+        <v>272.89653600000003</v>
+      </c>
+    </row>
+    <row r="40" spans="4:15" x14ac:dyDescent="0.3">
+      <c r="D40" s="6"/>
+      <c r="E40" s="6"/>
+      <c r="F40" s="6"/>
+      <c r="G40" s="6"/>
+      <c r="H40" s="6"/>
+      <c r="K40" s="6"/>
+      <c r="L40" s="6"/>
+      <c r="M40" s="6"/>
+      <c r="N40" s="6"/>
+      <c r="O40" s="6"/>
+    </row>
+    <row r="41" spans="4:15" x14ac:dyDescent="0.3">
+      <c r="D41" s="5">
         <v>5</v>
       </c>
       <c r="E41" t="s">
@@ -1049,11 +1617,29 @@
         <v>0.54166700000000001</v>
       </c>
       <c r="G41">
-        <v>847.86075000000005</v>
-      </c>
-    </row>
-    <row r="42" spans="4:7" x14ac:dyDescent="0.3">
-      <c r="D42" s="4"/>
+        <v>846.54007999999999</v>
+      </c>
+      <c r="H41">
+        <v>5339.2549419999996</v>
+      </c>
+      <c r="K41" s="5">
+        <v>5</v>
+      </c>
+      <c r="L41" t="s">
+        <v>9</v>
+      </c>
+      <c r="M41">
+        <v>0.45833299999999999</v>
+      </c>
+      <c r="N41">
+        <v>553.52280599999995</v>
+      </c>
+      <c r="O41">
+        <v>2377.8256160000001</v>
+      </c>
+    </row>
+    <row r="42" spans="4:15" x14ac:dyDescent="0.3">
+      <c r="D42" s="5"/>
       <c r="E42" t="s">
         <v>16</v>
       </c>
@@ -1061,11 +1647,27 @@
         <v>0.54166700000000001</v>
       </c>
       <c r="G42">
-        <v>838.84561099999996</v>
-      </c>
-    </row>
-    <row r="43" spans="4:7" x14ac:dyDescent="0.3">
-      <c r="D43" s="4"/>
+        <v>845.89146700000003</v>
+      </c>
+      <c r="H42">
+        <v>5284.3149919999996</v>
+      </c>
+      <c r="K42" s="5"/>
+      <c r="L42" t="s">
+        <v>16</v>
+      </c>
+      <c r="M42">
+        <v>0.41666700000000001</v>
+      </c>
+      <c r="N42">
+        <v>548.84105899999997</v>
+      </c>
+      <c r="O42">
+        <v>2399.3531370000001</v>
+      </c>
+    </row>
+    <row r="43" spans="4:15" x14ac:dyDescent="0.3">
+      <c r="D43" s="5"/>
       <c r="E43" t="s">
         <v>10</v>
       </c>
@@ -1073,11 +1675,27 @@
         <v>0.54166700000000001</v>
       </c>
       <c r="G43">
-        <v>853.22697500000004</v>
-      </c>
-    </row>
-    <row r="44" spans="4:7" x14ac:dyDescent="0.3">
-      <c r="D44" s="4"/>
+        <v>844.12120700000003</v>
+      </c>
+      <c r="H43">
+        <v>5452.3993039999996</v>
+      </c>
+      <c r="K43" s="5"/>
+      <c r="L43" t="s">
+        <v>10</v>
+      </c>
+      <c r="M43">
+        <v>0.45833299999999999</v>
+      </c>
+      <c r="N43">
+        <v>549.140942</v>
+      </c>
+      <c r="O43">
+        <v>2391.8057910000002</v>
+      </c>
+    </row>
+    <row r="44" spans="4:15" x14ac:dyDescent="0.3">
+      <c r="D44" s="5"/>
       <c r="E44" t="s">
         <v>11</v>
       </c>
@@ -1085,23 +1703,55 @@
         <v>0.54166700000000001</v>
       </c>
       <c r="G44">
-        <v>837.32505200000003</v>
-      </c>
-    </row>
-    <row r="45" spans="4:7" x14ac:dyDescent="0.3">
-      <c r="D45" s="4"/>
+        <v>840.16767900000002</v>
+      </c>
+      <c r="H44">
+        <v>5324.5379540000004</v>
+      </c>
+      <c r="K44" s="5"/>
+      <c r="L44" t="s">
+        <v>11</v>
+      </c>
+      <c r="M44">
+        <v>0.45833299999999999</v>
+      </c>
+      <c r="N44">
+        <v>550.97883100000001</v>
+      </c>
+      <c r="O44">
+        <v>2364.2043450000001</v>
+      </c>
+    </row>
+    <row r="45" spans="4:15" x14ac:dyDescent="0.3">
+      <c r="D45" s="5"/>
       <c r="E45" t="s">
         <v>12</v>
       </c>
       <c r="F45">
-        <v>0.58333299999999999</v>
+        <v>0.54166700000000001</v>
       </c>
       <c r="G45">
-        <v>843.81196799999998</v>
-      </c>
-    </row>
-    <row r="46" spans="4:7" x14ac:dyDescent="0.3">
-      <c r="D46" s="4"/>
+        <v>839.94743700000004</v>
+      </c>
+      <c r="H45">
+        <v>5318.596106</v>
+      </c>
+      <c r="K45" s="5"/>
+      <c r="L45" t="s">
+        <v>12</v>
+      </c>
+      <c r="M45">
+        <v>0.41666700000000001</v>
+      </c>
+      <c r="N45">
+        <v>555.04141300000003</v>
+      </c>
+      <c r="O45">
+        <v>2388.994729</v>
+      </c>
+    </row>
+    <row r="46" spans="4:15" x14ac:dyDescent="0.3">
+      <c r="D46" s="5"/>
       <c r="E46" t="s">
         <v>13</v>
       </c>
@@ -1109,11 +1759,27 @@
         <v>0.66666700000000001</v>
       </c>
       <c r="G46">
-        <v>1067.962276</v>
-      </c>
-    </row>
-    <row r="47" spans="4:7" x14ac:dyDescent="0.3">
-      <c r="D47" s="4"/>
+        <v>1056.4002820000001</v>
+      </c>
+      <c r="H46">
+        <v>4395.6808650000003</v>
+      </c>
+      <c r="K46" s="5"/>
+      <c r="L46" t="s">
+        <v>13</v>
+      </c>
+      <c r="M46">
+        <v>0.54166700000000001</v>
+      </c>
+      <c r="N46">
+        <v>641.57032800000002</v>
+      </c>
+      <c r="O46">
+        <v>2133.4583259999999</v>
+      </c>
+    </row>
+    <row r="47" spans="4:15" x14ac:dyDescent="0.3">
+      <c r="D47" s="5"/>
       <c r="E47" t="s">
         <v>14</v>
       </c>
@@ -1121,11 +1787,27 @@
         <v>0.54166700000000001</v>
       </c>
       <c r="G47">
-        <v>858.89092200000005</v>
-      </c>
-    </row>
-    <row r="48" spans="4:7" x14ac:dyDescent="0.3">
-      <c r="D48" s="4"/>
+        <v>835.63370999999995</v>
+      </c>
+      <c r="H47">
+        <v>5450.6061710000004</v>
+      </c>
+      <c r="K47" s="5"/>
+      <c r="L47" t="s">
+        <v>14</v>
+      </c>
+      <c r="M47">
+        <v>0.41666700000000001</v>
+      </c>
+      <c r="N47">
+        <v>548.92532600000004</v>
+      </c>
+      <c r="O47">
+        <v>2394.0892909999998</v>
+      </c>
+    </row>
+    <row r="48" spans="4:15" x14ac:dyDescent="0.3">
+      <c r="D48" s="5"/>
       <c r="E48" t="s">
         <v>15</v>
       </c>
@@ -1133,27 +1815,59 @@
         <v>0.54166700000000001</v>
       </c>
       <c r="G48">
-        <v>855.25156200000004</v>
-      </c>
-    </row>
-    <row r="49" spans="4:7" x14ac:dyDescent="0.3">
-      <c r="D49" s="5"/>
-      <c r="E49" s="5"/>
-      <c r="F49" s="5"/>
-      <c r="G49" s="5"/>
+        <v>844.663005</v>
+      </c>
+      <c r="H48">
+        <v>5406.424336</v>
+      </c>
+      <c r="K48" s="5"/>
+      <c r="L48" t="s">
+        <v>15</v>
+      </c>
+      <c r="M48">
+        <v>0.41666700000000001</v>
+      </c>
+      <c r="N48">
+        <v>552.70605599999999</v>
+      </c>
+      <c r="O48">
+        <v>2383.9639569999999</v>
+      </c>
+    </row>
+    <row r="49" spans="4:15" x14ac:dyDescent="0.3">
+      <c r="D49" s="6"/>
+      <c r="E49" s="6"/>
+      <c r="F49" s="6"/>
+      <c r="G49" s="6"/>
+      <c r="H49" s="6"/>
+      <c r="K49" s="6"/>
+      <c r="L49" s="6"/>
+      <c r="M49" s="6"/>
+      <c r="N49" s="6"/>
+      <c r="O49" s="6"/>
     </row>
   </sheetData>
-  <mergeCells count="10">
+  <mergeCells count="20">
+    <mergeCell ref="K32:K39"/>
+    <mergeCell ref="K41:K48"/>
+    <mergeCell ref="K49:O49"/>
+    <mergeCell ref="K40:O40"/>
+    <mergeCell ref="K31:O31"/>
+    <mergeCell ref="K5:K12"/>
+    <mergeCell ref="K14:K21"/>
+    <mergeCell ref="K23:K30"/>
+    <mergeCell ref="K22:O22"/>
+    <mergeCell ref="K13:O13"/>
+    <mergeCell ref="D5:D12"/>
+    <mergeCell ref="D14:D21"/>
+    <mergeCell ref="D23:D30"/>
+    <mergeCell ref="D13:H13"/>
+    <mergeCell ref="D22:H22"/>
     <mergeCell ref="D41:D48"/>
-    <mergeCell ref="D49:G49"/>
     <mergeCell ref="D32:D39"/>
-    <mergeCell ref="D40:G40"/>
-    <mergeCell ref="D31:G31"/>
-    <mergeCell ref="D5:D12"/>
-    <mergeCell ref="D13:G13"/>
-    <mergeCell ref="D14:D21"/>
-    <mergeCell ref="D22:G22"/>
-    <mergeCell ref="D23:D30"/>
+    <mergeCell ref="D31:H31"/>
+    <mergeCell ref="D40:H40"/>
+    <mergeCell ref="D49:H49"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -1161,14 +1875,22 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D9F3D6F7-9B83-4803-A2A9-5F6E3F05FBE9}">
-  <dimension ref="D4:G49"/>
+  <dimension ref="D3:P49"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="4" max="4" width="13.21875" customWidth="1"/>
     <col min="5" max="5" width="30.109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="4" spans="4:7" x14ac:dyDescent="0.3">
+    <row r="3" spans="4:16" x14ac:dyDescent="0.3">
+      <c r="E3">
+        <v>95</v>
+      </c>
+      <c r="M3">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="4" spans="4:16" x14ac:dyDescent="0.3">
       <c r="D4" t="s">
         <v>5</v>
       </c>
@@ -1181,9 +1903,27 @@
       <c r="G4" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="5" spans="4:7" x14ac:dyDescent="0.3">
-      <c r="D5" s="4">
+      <c r="H4" t="s">
+        <v>31</v>
+      </c>
+      <c r="L4" t="s">
+        <v>5</v>
+      </c>
+      <c r="M4" t="s">
+        <v>6</v>
+      </c>
+      <c r="N4" t="s">
+        <v>7</v>
+      </c>
+      <c r="O4" t="s">
+        <v>8</v>
+      </c>
+      <c r="P4" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="5" spans="4:16" x14ac:dyDescent="0.3">
+      <c r="D5" s="5">
         <v>1</v>
       </c>
       <c r="E5" t="s">
@@ -1193,59 +1933,141 @@
         <v>0.95833299999999999</v>
       </c>
       <c r="G5" s="2">
-        <v>80.157983999999999</v>
-      </c>
-    </row>
-    <row r="6" spans="4:7" x14ac:dyDescent="0.3">
-      <c r="D6" s="4"/>
+        <v>80.359790000000004</v>
+      </c>
+      <c r="H5">
+        <v>80.732042000000007</v>
+      </c>
+      <c r="L5" s="5">
+        <v>1</v>
+      </c>
+      <c r="M5" t="s">
+        <v>17</v>
+      </c>
+      <c r="N5" s="2">
+        <v>0.83333299999999999</v>
+      </c>
+      <c r="O5" s="2">
+        <v>52.544441999999997</v>
+      </c>
+      <c r="P5">
+        <v>60.185394000000002</v>
+      </c>
+    </row>
+    <row r="6" spans="4:16" x14ac:dyDescent="0.3">
+      <c r="D6" s="5"/>
       <c r="E6" t="s">
         <v>16</v>
       </c>
       <c r="F6" s="2">
-        <v>0.91666700000000001</v>
+        <v>0.95833299999999999</v>
       </c>
       <c r="G6" s="2">
-        <v>76.899727999999996</v>
-      </c>
-    </row>
-    <row r="7" spans="4:7" x14ac:dyDescent="0.3">
-      <c r="D7" s="4"/>
+        <v>83.028987999999998</v>
+      </c>
+      <c r="H6">
+        <v>83.828395</v>
+      </c>
+      <c r="L6" s="5"/>
+      <c r="M6" t="s">
+        <v>16</v>
+      </c>
+      <c r="N6" s="2">
+        <v>0.875</v>
+      </c>
+      <c r="O6" s="2">
+        <v>53.555809000000004</v>
+      </c>
+      <c r="P6">
+        <v>60.735185000000001</v>
+      </c>
+    </row>
+    <row r="7" spans="4:16" x14ac:dyDescent="0.3">
+      <c r="D7" s="5"/>
       <c r="E7" t="s">
         <v>10</v>
       </c>
       <c r="F7" s="2">
-        <v>0.95833299999999999</v>
+        <v>0.91666700000000001</v>
       </c>
       <c r="G7" s="2">
-        <v>81.510925</v>
-      </c>
-    </row>
-    <row r="8" spans="4:7" x14ac:dyDescent="0.3">
-      <c r="D8" s="4"/>
+        <v>81.697785999999994</v>
+      </c>
+      <c r="H7">
+        <v>83.053454000000002</v>
+      </c>
+      <c r="L7" s="5"/>
+      <c r="M7" t="s">
+        <v>10</v>
+      </c>
+      <c r="N7" s="2">
+        <v>0.875</v>
+      </c>
+      <c r="O7" s="2">
+        <v>53.141699000000003</v>
+      </c>
+      <c r="P7">
+        <v>60.563670999999999</v>
+      </c>
+    </row>
+    <row r="8" spans="4:16" x14ac:dyDescent="0.3">
+      <c r="D8" s="5"/>
       <c r="E8" t="s">
         <v>11</v>
       </c>
       <c r="F8" s="2">
-        <v>0.91666700000000001</v>
+        <v>0.95833299999999999</v>
       </c>
       <c r="G8" s="2">
-        <v>80.274412999999996</v>
-      </c>
-    </row>
-    <row r="9" spans="4:7" x14ac:dyDescent="0.3">
-      <c r="D9" s="4"/>
+        <v>78.006923999999998</v>
+      </c>
+      <c r="H8">
+        <v>78.422810999999996</v>
+      </c>
+      <c r="L8" s="5"/>
+      <c r="M8" t="s">
+        <v>11</v>
+      </c>
+      <c r="N8" s="2">
+        <v>0.83333299999999999</v>
+      </c>
+      <c r="O8" s="2">
+        <v>51.988134000000002</v>
+      </c>
+      <c r="P8">
+        <v>60.030335999999998</v>
+      </c>
+    </row>
+    <row r="9" spans="4:16" x14ac:dyDescent="0.3">
+      <c r="D9" s="5"/>
       <c r="E9" t="s">
         <v>12</v>
       </c>
       <c r="F9" s="2">
-        <v>1</v>
+        <v>0.91666700000000001</v>
       </c>
       <c r="G9" s="2">
-        <v>79.872102999999996</v>
-      </c>
-    </row>
-    <row r="10" spans="4:7" x14ac:dyDescent="0.3">
-      <c r="D10" s="4"/>
+        <v>79.947243999999998</v>
+      </c>
+      <c r="H9">
+        <v>82.707314999999994</v>
+      </c>
+      <c r="L9" s="5"/>
+      <c r="M9" t="s">
+        <v>12</v>
+      </c>
+      <c r="N9" s="2">
+        <v>0.83333299999999999</v>
+      </c>
+      <c r="O9" s="2">
+        <v>52.479407000000002</v>
+      </c>
+      <c r="P9">
+        <v>60.374386999999999</v>
+      </c>
+    </row>
+    <row r="10" spans="4:16" x14ac:dyDescent="0.3">
+      <c r="D10" s="5"/>
       <c r="E10" t="s">
         <v>13</v>
       </c>
@@ -1253,41 +2075,95 @@
         <v>0.83333299999999999</v>
       </c>
       <c r="G10" s="2">
-        <v>42.898245000000003</v>
-      </c>
-    </row>
-    <row r="11" spans="4:7" x14ac:dyDescent="0.3">
-      <c r="D11" s="4"/>
+        <v>43.474319999999999</v>
+      </c>
+      <c r="H10">
+        <v>99.246764999999996</v>
+      </c>
+      <c r="L10" s="5"/>
+      <c r="M10" t="s">
+        <v>13</v>
+      </c>
+      <c r="N10" s="2">
+        <v>0.625</v>
+      </c>
+      <c r="O10" s="2">
+        <v>28.115302</v>
+      </c>
+      <c r="P10">
+        <v>65.774687</v>
+      </c>
+    </row>
+    <row r="11" spans="4:16" x14ac:dyDescent="0.3">
+      <c r="D11" s="5"/>
       <c r="E11" t="s">
         <v>14</v>
       </c>
       <c r="F11" s="2">
-        <v>0.95833299999999999</v>
+        <v>0.91666700000000001</v>
       </c>
       <c r="G11" s="2">
-        <v>78.904285000000002</v>
-      </c>
-    </row>
-    <row r="12" spans="4:7" x14ac:dyDescent="0.3">
-      <c r="D12" s="4"/>
+        <v>81.850363999999999</v>
+      </c>
+      <c r="H11">
+        <v>87.186156999999994</v>
+      </c>
+      <c r="L11" s="5"/>
+      <c r="M11" t="s">
+        <v>14</v>
+      </c>
+      <c r="N11" s="2">
+        <v>0.875</v>
+      </c>
+      <c r="O11" s="2">
+        <v>52.793655000000001</v>
+      </c>
+      <c r="P11">
+        <v>60.949455999999998</v>
+      </c>
+    </row>
+    <row r="12" spans="4:16" x14ac:dyDescent="0.3">
+      <c r="D12" s="5"/>
       <c r="E12" t="s">
         <v>15</v>
       </c>
       <c r="F12" s="2">
-        <v>1</v>
+        <v>0.91666700000000001</v>
       </c>
       <c r="G12" s="2">
-        <v>80.795083000000005</v>
-      </c>
-    </row>
-    <row r="13" spans="4:7" x14ac:dyDescent="0.3">
-      <c r="D13" s="5"/>
-      <c r="E13" s="5"/>
-      <c r="F13" s="5"/>
-      <c r="G13" s="5"/>
-    </row>
-    <row r="14" spans="4:7" x14ac:dyDescent="0.3">
-      <c r="D14" s="4">
+        <v>81.682552999999999</v>
+      </c>
+      <c r="H12">
+        <v>84.918604999999999</v>
+      </c>
+      <c r="L12" s="5"/>
+      <c r="M12" t="s">
+        <v>15</v>
+      </c>
+      <c r="N12" s="2">
+        <v>0.83333299999999999</v>
+      </c>
+      <c r="O12" s="2">
+        <v>52.033369</v>
+      </c>
+      <c r="P12">
+        <v>60.889226999999998</v>
+      </c>
+    </row>
+    <row r="13" spans="4:16" x14ac:dyDescent="0.3">
+      <c r="D13" s="6"/>
+      <c r="E13" s="6"/>
+      <c r="F13" s="6"/>
+      <c r="G13" s="6"/>
+      <c r="H13" s="6"/>
+      <c r="L13" s="6"/>
+      <c r="M13" s="6"/>
+      <c r="N13" s="6"/>
+      <c r="O13" s="6"/>
+      <c r="P13" s="6"/>
+    </row>
+    <row r="14" spans="4:16" x14ac:dyDescent="0.3">
+      <c r="D14" s="5">
         <v>2</v>
       </c>
       <c r="E14" t="s">
@@ -1297,11 +2173,29 @@
         <v>1</v>
       </c>
       <c r="G14">
-        <v>9.9484739999999992</v>
-      </c>
-    </row>
-    <row r="15" spans="4:7" x14ac:dyDescent="0.3">
-      <c r="D15" s="4"/>
+        <v>9.9500309999999992</v>
+      </c>
+      <c r="H14">
+        <v>9.9500309999999992</v>
+      </c>
+      <c r="L14" s="5">
+        <v>2</v>
+      </c>
+      <c r="M14" t="s">
+        <v>17</v>
+      </c>
+      <c r="N14">
+        <v>0.91666700000000001</v>
+      </c>
+      <c r="O14">
+        <v>6.5059760000000004</v>
+      </c>
+      <c r="P14">
+        <v>6.7958660000000002</v>
+      </c>
+    </row>
+    <row r="15" spans="4:16" x14ac:dyDescent="0.3">
+      <c r="D15" s="5"/>
       <c r="E15" t="s">
         <v>16</v>
       </c>
@@ -1309,11 +2203,27 @@
         <v>1</v>
       </c>
       <c r="G15">
-        <v>9.8285889999999991</v>
-      </c>
-    </row>
-    <row r="16" spans="4:7" x14ac:dyDescent="0.3">
-      <c r="D16" s="4"/>
+        <v>9.8199799999999993</v>
+      </c>
+      <c r="H15">
+        <v>9.8199799999999993</v>
+      </c>
+      <c r="L15" s="5"/>
+      <c r="M15" t="s">
+        <v>16</v>
+      </c>
+      <c r="N15">
+        <v>0.95833299999999999</v>
+      </c>
+      <c r="O15">
+        <v>6.5153999999999996</v>
+      </c>
+      <c r="P15">
+        <v>6.6516219999999997</v>
+      </c>
+    </row>
+    <row r="16" spans="4:16" x14ac:dyDescent="0.3">
+      <c r="D16" s="5"/>
       <c r="E16" t="s">
         <v>10</v>
       </c>
@@ -1321,11 +2231,27 @@
         <v>1</v>
       </c>
       <c r="G16">
-        <v>9.9364369999999997</v>
-      </c>
-    </row>
-    <row r="17" spans="4:7" x14ac:dyDescent="0.3">
-      <c r="D17" s="4"/>
+        <v>9.7604059999999997</v>
+      </c>
+      <c r="H16">
+        <v>9.7604059999999997</v>
+      </c>
+      <c r="L16" s="5"/>
+      <c r="M16" t="s">
+        <v>10</v>
+      </c>
+      <c r="N16">
+        <v>0.875</v>
+      </c>
+      <c r="O16">
+        <v>6.4797260000000003</v>
+      </c>
+      <c r="P16">
+        <v>6.8423959999999999</v>
+      </c>
+    </row>
+    <row r="17" spans="4:16" x14ac:dyDescent="0.3">
+      <c r="D17" s="5"/>
       <c r="E17" t="s">
         <v>11</v>
       </c>
@@ -1333,11 +2259,27 @@
         <v>1</v>
       </c>
       <c r="G17">
-        <v>9.9255580000000005</v>
-      </c>
-    </row>
-    <row r="18" spans="4:7" x14ac:dyDescent="0.3">
-      <c r="D18" s="4"/>
+        <v>10.031902000000001</v>
+      </c>
+      <c r="H17">
+        <v>10.031902000000001</v>
+      </c>
+      <c r="L17" s="5"/>
+      <c r="M17" t="s">
+        <v>11</v>
+      </c>
+      <c r="N17">
+        <v>0.875</v>
+      </c>
+      <c r="O17">
+        <v>6.4767429999999999</v>
+      </c>
+      <c r="P17">
+        <v>6.7604559999999996</v>
+      </c>
+    </row>
+    <row r="18" spans="4:16" x14ac:dyDescent="0.3">
+      <c r="D18" s="5"/>
       <c r="E18" t="s">
         <v>12</v>
       </c>
@@ -1345,11 +2287,27 @@
         <v>1</v>
       </c>
       <c r="G18">
-        <v>9.8594209999999993</v>
-      </c>
-    </row>
-    <row r="19" spans="4:7" x14ac:dyDescent="0.3">
-      <c r="D19" s="4"/>
+        <v>9.8997600000000006</v>
+      </c>
+      <c r="H18">
+        <v>9.8997600000000006</v>
+      </c>
+      <c r="L18" s="5"/>
+      <c r="M18" t="s">
+        <v>12</v>
+      </c>
+      <c r="N18">
+        <v>0.875</v>
+      </c>
+      <c r="O18">
+        <v>6.4965999999999999</v>
+      </c>
+      <c r="P18">
+        <v>6.8305920000000002</v>
+      </c>
+    </row>
+    <row r="19" spans="4:16" x14ac:dyDescent="0.3">
+      <c r="D19" s="5"/>
       <c r="E19" s="3" t="s">
         <v>13</v>
       </c>
@@ -1357,11 +2315,27 @@
         <v>1</v>
       </c>
       <c r="G19" s="3">
-        <v>62.336621000000001</v>
-      </c>
-    </row>
-    <row r="20" spans="4:7" x14ac:dyDescent="0.3">
-      <c r="D20" s="4"/>
+        <v>56.893901999999997</v>
+      </c>
+      <c r="H19">
+        <v>56.893901999999997</v>
+      </c>
+      <c r="L19" s="5"/>
+      <c r="M19" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="N19" s="3">
+        <v>1</v>
+      </c>
+      <c r="O19" s="3">
+        <v>9.8484069999999999</v>
+      </c>
+      <c r="P19">
+        <v>9.8484069999999999</v>
+      </c>
+    </row>
+    <row r="20" spans="4:16" x14ac:dyDescent="0.3">
+      <c r="D20" s="5"/>
       <c r="E20" t="s">
         <v>14</v>
       </c>
@@ -1369,11 +2343,27 @@
         <v>1</v>
       </c>
       <c r="G20">
-        <v>9.8234449999999995</v>
-      </c>
-    </row>
-    <row r="21" spans="4:7" x14ac:dyDescent="0.3">
-      <c r="D21" s="4"/>
+        <v>9.8991710000000008</v>
+      </c>
+      <c r="H20">
+        <v>9.8991710000000008</v>
+      </c>
+      <c r="L20" s="5"/>
+      <c r="M20" t="s">
+        <v>14</v>
+      </c>
+      <c r="N20">
+        <v>0.875</v>
+      </c>
+      <c r="O20">
+        <v>6.4870359999999998</v>
+      </c>
+      <c r="P20">
+        <v>6.8070539999999999</v>
+      </c>
+    </row>
+    <row r="21" spans="4:16" x14ac:dyDescent="0.3">
+      <c r="D21" s="5"/>
       <c r="E21" t="s">
         <v>15</v>
       </c>
@@ -1381,17 +2371,39 @@
         <v>1</v>
       </c>
       <c r="G21">
-        <v>9.9187390000000004</v>
-      </c>
-    </row>
-    <row r="22" spans="4:7" x14ac:dyDescent="0.3">
-      <c r="D22" s="5"/>
-      <c r="E22" s="5"/>
-      <c r="F22" s="5"/>
-      <c r="G22" s="5"/>
-    </row>
-    <row r="23" spans="4:7" x14ac:dyDescent="0.3">
-      <c r="D23" s="4">
+        <v>9.7609619999999993</v>
+      </c>
+      <c r="H21">
+        <v>9.7609619999999993</v>
+      </c>
+      <c r="L21" s="5"/>
+      <c r="M21" t="s">
+        <v>15</v>
+      </c>
+      <c r="N21">
+        <v>0.95833299999999999</v>
+      </c>
+      <c r="O21">
+        <v>6.4527409999999996</v>
+      </c>
+      <c r="P21">
+        <v>6.6913369999999999</v>
+      </c>
+    </row>
+    <row r="22" spans="4:16" x14ac:dyDescent="0.3">
+      <c r="D22" s="6"/>
+      <c r="E22" s="6"/>
+      <c r="F22" s="6"/>
+      <c r="G22" s="6"/>
+      <c r="H22" s="6"/>
+      <c r="L22" s="6"/>
+      <c r="M22" s="6"/>
+      <c r="N22" s="6"/>
+      <c r="O22" s="6"/>
+      <c r="P22" s="6"/>
+    </row>
+    <row r="23" spans="4:16" x14ac:dyDescent="0.3">
+      <c r="D23" s="5">
         <v>3</v>
       </c>
       <c r="E23" t="s">
@@ -1401,11 +2413,29 @@
         <v>0.95</v>
       </c>
       <c r="G23" s="2">
-        <v>3410.9398190000002</v>
-      </c>
-    </row>
-    <row r="24" spans="4:7" x14ac:dyDescent="0.3">
-      <c r="D24" s="4"/>
+        <v>3410.9398849999998</v>
+      </c>
+      <c r="H23">
+        <v>4217.0109409999995</v>
+      </c>
+      <c r="L23" s="5">
+        <v>3</v>
+      </c>
+      <c r="M23" t="s">
+        <v>17</v>
+      </c>
+      <c r="N23" s="2">
+        <v>0.75</v>
+      </c>
+      <c r="O23" s="2">
+        <v>2230.2937120000001</v>
+      </c>
+      <c r="P23">
+        <v>3149.6784560000001</v>
+      </c>
+    </row>
+    <row r="24" spans="4:16" x14ac:dyDescent="0.3">
+      <c r="D24" s="5"/>
       <c r="E24" t="s">
         <v>16</v>
       </c>
@@ -1413,11 +2443,27 @@
         <v>0.95</v>
       </c>
       <c r="G24" s="2">
-        <v>3401.3317860000002</v>
-      </c>
-    </row>
-    <row r="25" spans="4:7" x14ac:dyDescent="0.3">
-      <c r="D25" s="4"/>
+        <v>3397.090365</v>
+      </c>
+      <c r="H24">
+        <v>4196.7834730000004</v>
+      </c>
+      <c r="L24" s="5"/>
+      <c r="M24" t="s">
+        <v>16</v>
+      </c>
+      <c r="N24" s="2">
+        <v>0.75</v>
+      </c>
+      <c r="O24" s="2">
+        <v>2233.6216559999998</v>
+      </c>
+      <c r="P24">
+        <v>3077.20109</v>
+      </c>
+    </row>
+    <row r="25" spans="4:16" x14ac:dyDescent="0.3">
+      <c r="D25" s="5"/>
       <c r="E25" t="s">
         <v>10</v>
       </c>
@@ -1425,11 +2471,27 @@
         <v>0.95</v>
       </c>
       <c r="G25" s="2">
-        <v>3380.0382789999999</v>
-      </c>
-    </row>
-    <row r="26" spans="4:7" x14ac:dyDescent="0.3">
-      <c r="D26" s="4"/>
+        <v>3364.6878999999999</v>
+      </c>
+      <c r="H25">
+        <v>4233.8351110000003</v>
+      </c>
+      <c r="L25" s="5"/>
+      <c r="M25" t="s">
+        <v>10</v>
+      </c>
+      <c r="N25" s="2">
+        <v>0.75</v>
+      </c>
+      <c r="O25" s="2">
+        <v>2213.1801639999999</v>
+      </c>
+      <c r="P25">
+        <v>3124.8121959999999</v>
+      </c>
+    </row>
+    <row r="26" spans="4:16" x14ac:dyDescent="0.3">
+      <c r="D26" s="5"/>
       <c r="E26" t="s">
         <v>11</v>
       </c>
@@ -1437,11 +2499,27 @@
         <v>0.95</v>
       </c>
       <c r="G26" s="2">
-        <v>3409.493759</v>
-      </c>
-    </row>
-    <row r="27" spans="4:7" x14ac:dyDescent="0.3">
-      <c r="D27" s="4"/>
+        <v>3382.0778610000002</v>
+      </c>
+      <c r="H26">
+        <v>4346.802036</v>
+      </c>
+      <c r="L26" s="5"/>
+      <c r="M26" t="s">
+        <v>11</v>
+      </c>
+      <c r="N26" s="2">
+        <v>0.75</v>
+      </c>
+      <c r="O26" s="2">
+        <v>2230.2875859999999</v>
+      </c>
+      <c r="P26">
+        <v>3196.7607950000001</v>
+      </c>
+    </row>
+    <row r="27" spans="4:16" x14ac:dyDescent="0.3">
+      <c r="D27" s="5"/>
       <c r="E27" t="s">
         <v>12</v>
       </c>
@@ -1449,11 +2527,27 @@
         <v>0.95</v>
       </c>
       <c r="G27" s="2">
-        <v>3362.0034879999998</v>
-      </c>
-    </row>
-    <row r="28" spans="4:7" x14ac:dyDescent="0.3">
-      <c r="D28" s="4"/>
+        <v>3391.407303</v>
+      </c>
+      <c r="H27">
+        <v>4312.8634199999997</v>
+      </c>
+      <c r="L27" s="5"/>
+      <c r="M27" t="s">
+        <v>12</v>
+      </c>
+      <c r="N27" s="2">
+        <v>0.75</v>
+      </c>
+      <c r="O27" s="2">
+        <v>2229.5284310000002</v>
+      </c>
+      <c r="P27">
+        <v>3170.4379399999998</v>
+      </c>
+    </row>
+    <row r="28" spans="4:16" x14ac:dyDescent="0.3">
+      <c r="D28" s="5"/>
       <c r="E28" t="s">
         <v>13</v>
       </c>
@@ -1461,11 +2555,27 @@
         <v>1</v>
       </c>
       <c r="G28" s="2">
-        <v>6467.5310920000002</v>
-      </c>
-    </row>
-    <row r="29" spans="4:7" x14ac:dyDescent="0.3">
-      <c r="D29" s="4"/>
+        <v>6084.61438</v>
+      </c>
+      <c r="H28">
+        <v>6084.61438</v>
+      </c>
+      <c r="L28" s="5"/>
+      <c r="M28" t="s">
+        <v>13</v>
+      </c>
+      <c r="N28" s="2">
+        <v>1</v>
+      </c>
+      <c r="O28" s="2">
+        <v>2660.8760130000001</v>
+      </c>
+      <c r="P28">
+        <v>2660.8760130000001</v>
+      </c>
+    </row>
+    <row r="29" spans="4:16" x14ac:dyDescent="0.3">
+      <c r="D29" s="5"/>
       <c r="E29" t="s">
         <v>14</v>
       </c>
@@ -1473,11 +2583,27 @@
         <v>0.95</v>
       </c>
       <c r="G29" s="2">
-        <v>3399.3432069999999</v>
-      </c>
-    </row>
-    <row r="30" spans="4:7" x14ac:dyDescent="0.3">
-      <c r="D30" s="4"/>
+        <v>3363.8429860000001</v>
+      </c>
+      <c r="H29">
+        <v>4008.0422549999998</v>
+      </c>
+      <c r="L29" s="5"/>
+      <c r="M29" t="s">
+        <v>14</v>
+      </c>
+      <c r="N29" s="2">
+        <v>0.75</v>
+      </c>
+      <c r="O29" s="2">
+        <v>2206.6708130000002</v>
+      </c>
+      <c r="P29">
+        <v>3157.1300660000002</v>
+      </c>
+    </row>
+    <row r="30" spans="4:16" x14ac:dyDescent="0.3">
+      <c r="D30" s="5"/>
       <c r="E30" t="s">
         <v>15</v>
       </c>
@@ -1485,17 +2611,39 @@
         <v>0.95</v>
       </c>
       <c r="G30" s="2">
-        <v>3379.5483079999999</v>
-      </c>
-    </row>
-    <row r="31" spans="4:7" x14ac:dyDescent="0.3">
-      <c r="D31" s="5"/>
-      <c r="E31" s="5"/>
-      <c r="F31" s="5"/>
-      <c r="G31" s="5"/>
-    </row>
-    <row r="32" spans="4:7" x14ac:dyDescent="0.3">
-      <c r="D32" s="4">
+        <v>3406.0027669999999</v>
+      </c>
+      <c r="H30">
+        <v>4519.6994599999998</v>
+      </c>
+      <c r="L30" s="5"/>
+      <c r="M30" t="s">
+        <v>15</v>
+      </c>
+      <c r="N30" s="2">
+        <v>0.8</v>
+      </c>
+      <c r="O30" s="2">
+        <v>2220.4202959999998</v>
+      </c>
+      <c r="P30">
+        <v>3091.5559640000001</v>
+      </c>
+    </row>
+    <row r="31" spans="4:16" x14ac:dyDescent="0.3">
+      <c r="D31" s="6"/>
+      <c r="E31" s="6"/>
+      <c r="F31" s="6"/>
+      <c r="G31" s="6"/>
+      <c r="H31" s="6"/>
+      <c r="L31" s="6"/>
+      <c r="M31" s="6"/>
+      <c r="N31" s="6"/>
+      <c r="O31" s="6"/>
+      <c r="P31" s="6"/>
+    </row>
+    <row r="32" spans="4:16" x14ac:dyDescent="0.3">
+      <c r="D32" s="5">
         <v>4</v>
       </c>
       <c r="E32" t="s">
@@ -1505,11 +2653,29 @@
         <v>1</v>
       </c>
       <c r="G32" s="2">
-        <v>840.34417199999996</v>
-      </c>
-    </row>
-    <row r="33" spans="4:7" x14ac:dyDescent="0.3">
-      <c r="D33" s="4"/>
+        <v>840.42940199999998</v>
+      </c>
+      <c r="H32">
+        <v>840.42940199999998</v>
+      </c>
+      <c r="L32" s="5">
+        <v>4</v>
+      </c>
+      <c r="M32" t="s">
+        <v>17</v>
+      </c>
+      <c r="N32" s="2">
+        <v>1</v>
+      </c>
+      <c r="O32" s="2">
+        <v>549.52724799999999</v>
+      </c>
+      <c r="P32">
+        <v>549.52724799999999</v>
+      </c>
+    </row>
+    <row r="33" spans="4:16" x14ac:dyDescent="0.3">
+      <c r="D33" s="5"/>
       <c r="E33" t="s">
         <v>16</v>
       </c>
@@ -1517,11 +2683,27 @@
         <v>1</v>
       </c>
       <c r="G33" s="2">
-        <v>812.39180299999998</v>
-      </c>
-    </row>
-    <row r="34" spans="4:7" x14ac:dyDescent="0.3">
-      <c r="D34" s="4"/>
+        <v>836.42193199999997</v>
+      </c>
+      <c r="H33">
+        <v>836.42193199999997</v>
+      </c>
+      <c r="L33" s="5"/>
+      <c r="M33" t="s">
+        <v>16</v>
+      </c>
+      <c r="N33" s="2">
+        <v>1</v>
+      </c>
+      <c r="O33" s="2">
+        <v>547.17173600000001</v>
+      </c>
+      <c r="P33">
+        <v>547.17173600000001</v>
+      </c>
+    </row>
+    <row r="34" spans="4:16" x14ac:dyDescent="0.3">
+      <c r="D34" s="5"/>
       <c r="E34" t="s">
         <v>10</v>
       </c>
@@ -1529,11 +2711,27 @@
         <v>1</v>
       </c>
       <c r="G34" s="2">
-        <v>841.59871699999997</v>
-      </c>
-    </row>
-    <row r="35" spans="4:7" x14ac:dyDescent="0.3">
-      <c r="D35" s="4"/>
+        <v>811.59063700000002</v>
+      </c>
+      <c r="H34">
+        <v>811.59063700000002</v>
+      </c>
+      <c r="L34" s="5"/>
+      <c r="M34" t="s">
+        <v>10</v>
+      </c>
+      <c r="N34" s="2">
+        <v>1</v>
+      </c>
+      <c r="O34" s="2">
+        <v>534.91403200000002</v>
+      </c>
+      <c r="P34">
+        <v>534.91403200000002</v>
+      </c>
+    </row>
+    <row r="35" spans="4:16" x14ac:dyDescent="0.3">
+      <c r="D35" s="5"/>
       <c r="E35" t="s">
         <v>11</v>
       </c>
@@ -1541,11 +2739,27 @@
         <v>1</v>
       </c>
       <c r="G35" s="2">
-        <v>786.86640899999998</v>
-      </c>
-    </row>
-    <row r="36" spans="4:7" x14ac:dyDescent="0.3">
-      <c r="D36" s="4"/>
+        <v>852.19998099999998</v>
+      </c>
+      <c r="H35">
+        <v>852.19998099999998</v>
+      </c>
+      <c r="L35" s="5"/>
+      <c r="M35" t="s">
+        <v>11</v>
+      </c>
+      <c r="N35" s="2">
+        <v>1</v>
+      </c>
+      <c r="O35" s="2">
+        <v>535.09654699999999</v>
+      </c>
+      <c r="P35">
+        <v>535.09654699999999</v>
+      </c>
+    </row>
+    <row r="36" spans="4:16" x14ac:dyDescent="0.3">
+      <c r="D36" s="5"/>
       <c r="E36" t="s">
         <v>12</v>
       </c>
@@ -1553,11 +2767,27 @@
         <v>1</v>
       </c>
       <c r="G36" s="2">
-        <v>852.16210899999999</v>
-      </c>
-    </row>
-    <row r="37" spans="4:7" x14ac:dyDescent="0.3">
-      <c r="D37" s="4"/>
+        <v>808.34737199999995</v>
+      </c>
+      <c r="H36">
+        <v>808.34737199999995</v>
+      </c>
+      <c r="L36" s="5"/>
+      <c r="M36" t="s">
+        <v>12</v>
+      </c>
+      <c r="N36" s="2">
+        <v>1</v>
+      </c>
+      <c r="O36" s="2">
+        <v>547.03996199999995</v>
+      </c>
+      <c r="P36">
+        <v>547.03996199999995</v>
+      </c>
+    </row>
+    <row r="37" spans="4:16" x14ac:dyDescent="0.3">
+      <c r="D37" s="5"/>
       <c r="E37" t="s">
         <v>13</v>
       </c>
@@ -1565,11 +2795,27 @@
         <v>0.83333299999999999</v>
       </c>
       <c r="G37" s="2">
-        <v>171.405417</v>
-      </c>
-    </row>
-    <row r="38" spans="4:7" x14ac:dyDescent="0.3">
-      <c r="D38" s="4"/>
+        <v>174.40398300000001</v>
+      </c>
+      <c r="H37">
+        <v>393.69331299999999</v>
+      </c>
+      <c r="L37" s="5"/>
+      <c r="M37" t="s">
+        <v>13</v>
+      </c>
+      <c r="N37" s="2">
+        <v>0.625</v>
+      </c>
+      <c r="O37" s="2">
+        <v>98.148723000000004</v>
+      </c>
+      <c r="P37">
+        <v>249.705341</v>
+      </c>
+    </row>
+    <row r="38" spans="4:16" x14ac:dyDescent="0.3">
+      <c r="D38" s="5"/>
       <c r="E38" t="s">
         <v>14</v>
       </c>
@@ -1577,11 +2823,27 @@
         <v>1</v>
       </c>
       <c r="G38" s="2">
-        <v>835.86260600000003</v>
-      </c>
-    </row>
-    <row r="39" spans="4:7" x14ac:dyDescent="0.3">
-      <c r="D39" s="4"/>
+        <v>849.14846</v>
+      </c>
+      <c r="H38">
+        <v>849.14846</v>
+      </c>
+      <c r="L38" s="5"/>
+      <c r="M38" t="s">
+        <v>14</v>
+      </c>
+      <c r="N38" s="2">
+        <v>1</v>
+      </c>
+      <c r="O38" s="2">
+        <v>554.34740499999998</v>
+      </c>
+      <c r="P38">
+        <v>554.34740499999998</v>
+      </c>
+    </row>
+    <row r="39" spans="4:16" x14ac:dyDescent="0.3">
+      <c r="D39" s="5"/>
       <c r="E39" t="s">
         <v>15</v>
       </c>
@@ -1589,43 +2851,99 @@
         <v>1</v>
       </c>
       <c r="G39" s="2">
-        <v>849.79519800000003</v>
-      </c>
-    </row>
-    <row r="40" spans="4:7" x14ac:dyDescent="0.3">
-      <c r="D40" s="5"/>
-      <c r="E40" s="5"/>
-      <c r="F40" s="5"/>
-      <c r="G40" s="5"/>
-    </row>
-    <row r="41" spans="4:7" x14ac:dyDescent="0.3">
-      <c r="D41" s="4">
+        <v>817.50268000000005</v>
+      </c>
+      <c r="H39">
+        <v>817.50268000000005</v>
+      </c>
+      <c r="L39" s="5"/>
+      <c r="M39" t="s">
+        <v>15</v>
+      </c>
+      <c r="N39" s="2">
+        <v>1</v>
+      </c>
+      <c r="O39" s="2">
+        <v>538.49544400000002</v>
+      </c>
+      <c r="P39">
+        <v>538.49544400000002</v>
+      </c>
+    </row>
+    <row r="40" spans="4:16" x14ac:dyDescent="0.3">
+      <c r="D40" s="6"/>
+      <c r="E40" s="6"/>
+      <c r="F40" s="6"/>
+      <c r="G40" s="6"/>
+      <c r="H40" s="6"/>
+      <c r="L40" s="6"/>
+      <c r="M40" s="6"/>
+      <c r="N40" s="6"/>
+      <c r="O40" s="6"/>
+      <c r="P40" s="6"/>
+    </row>
+    <row r="41" spans="4:16" x14ac:dyDescent="0.3">
+      <c r="D41" s="5">
         <v>5</v>
       </c>
       <c r="E41" t="s">
         <v>17</v>
       </c>
       <c r="F41" s="2">
-        <v>0.91666700000000001</v>
+        <v>0.875</v>
       </c>
       <c r="G41" s="2">
-        <v>937.70045300000004</v>
-      </c>
-    </row>
-    <row r="42" spans="4:7" x14ac:dyDescent="0.3">
-      <c r="D42" s="4"/>
+        <v>886.70220500000005</v>
+      </c>
+      <c r="H41">
+        <v>1714.5527509999999</v>
+      </c>
+      <c r="L41" s="5">
+        <v>5</v>
+      </c>
+      <c r="M41" t="s">
+        <v>17</v>
+      </c>
+      <c r="N41" s="2">
+        <v>0.79166700000000001</v>
+      </c>
+      <c r="O41" s="2">
+        <v>579.78340800000001</v>
+      </c>
+      <c r="P41">
+        <v>1059.231348</v>
+      </c>
+    </row>
+    <row r="42" spans="4:16" x14ac:dyDescent="0.3">
+      <c r="D42" s="5"/>
       <c r="E42" t="s">
         <v>16</v>
       </c>
       <c r="F42" s="2">
-        <v>0.91666700000000001</v>
+        <v>0.875</v>
       </c>
       <c r="G42" s="2">
-        <v>936.699343</v>
-      </c>
-    </row>
-    <row r="43" spans="4:7" x14ac:dyDescent="0.3">
-      <c r="D43" s="4"/>
+        <v>893.40928499999995</v>
+      </c>
+      <c r="H42">
+        <v>1762.5233740000001</v>
+      </c>
+      <c r="L42" s="5"/>
+      <c r="M42" t="s">
+        <v>16</v>
+      </c>
+      <c r="N42" s="2">
+        <v>0.79166700000000001</v>
+      </c>
+      <c r="O42" s="2">
+        <v>571.62192200000004</v>
+      </c>
+      <c r="P42">
+        <v>1058.3037790000001</v>
+      </c>
+    </row>
+    <row r="43" spans="4:16" x14ac:dyDescent="0.3">
+      <c r="D43" s="5"/>
       <c r="E43" t="s">
         <v>10</v>
       </c>
@@ -1633,11 +2951,27 @@
         <v>0.875</v>
       </c>
       <c r="G43" s="2">
-        <v>931.72322299999996</v>
-      </c>
-    </row>
-    <row r="44" spans="4:7" x14ac:dyDescent="0.3">
-      <c r="D44" s="4"/>
+        <v>897.09858299999996</v>
+      </c>
+      <c r="H43">
+        <v>1713.0995170000001</v>
+      </c>
+      <c r="L43" s="5"/>
+      <c r="M43" t="s">
+        <v>10</v>
+      </c>
+      <c r="N43" s="2">
+        <v>0.79166700000000001</v>
+      </c>
+      <c r="O43" s="2">
+        <v>576.69714999999997</v>
+      </c>
+      <c r="P43">
+        <v>1044.3270339999999</v>
+      </c>
+    </row>
+    <row r="44" spans="4:16" x14ac:dyDescent="0.3">
+      <c r="D44" s="5"/>
       <c r="E44" t="s">
         <v>11</v>
       </c>
@@ -1645,23 +2979,55 @@
         <v>0.875</v>
       </c>
       <c r="G44" s="2">
-        <v>907.72775799999999</v>
-      </c>
-    </row>
-    <row r="45" spans="4:7" x14ac:dyDescent="0.3">
-      <c r="D45" s="4"/>
+        <v>878.80186300000003</v>
+      </c>
+      <c r="H44">
+        <v>1659.321813</v>
+      </c>
+      <c r="L44" s="5"/>
+      <c r="M44" t="s">
+        <v>11</v>
+      </c>
+      <c r="N44" s="2">
+        <v>0.79166700000000001</v>
+      </c>
+      <c r="O44" s="2">
+        <v>573.05174599999998</v>
+      </c>
+      <c r="P44">
+        <v>1052.0655420000001</v>
+      </c>
+    </row>
+    <row r="45" spans="4:16" x14ac:dyDescent="0.3">
+      <c r="D45" s="5"/>
       <c r="E45" t="s">
         <v>12</v>
       </c>
       <c r="F45" s="2">
-        <v>0.91666700000000001</v>
+        <v>0.875</v>
       </c>
       <c r="G45" s="2">
-        <v>936.01575700000001</v>
-      </c>
-    </row>
-    <row r="46" spans="4:7" x14ac:dyDescent="0.3">
-      <c r="D46" s="4"/>
+        <v>865.76613599999996</v>
+      </c>
+      <c r="H45">
+        <v>1742.3928109999999</v>
+      </c>
+      <c r="L45" s="5"/>
+      <c r="M45" t="s">
+        <v>12</v>
+      </c>
+      <c r="N45" s="2">
+        <v>0.75</v>
+      </c>
+      <c r="O45" s="2">
+        <v>571.56380799999999</v>
+      </c>
+      <c r="P45">
+        <v>1071.3569299999999</v>
+      </c>
+    </row>
+    <row r="46" spans="4:16" x14ac:dyDescent="0.3">
+      <c r="D46" s="5"/>
       <c r="E46" t="s">
         <v>13</v>
       </c>
@@ -1669,11 +3035,27 @@
         <v>0.875</v>
       </c>
       <c r="G46" s="2">
-        <v>1101.727549</v>
-      </c>
-    </row>
-    <row r="47" spans="4:7" x14ac:dyDescent="0.3">
-      <c r="D47" s="4"/>
+        <v>1087.8388379999999</v>
+      </c>
+      <c r="H46">
+        <v>1657.811279</v>
+      </c>
+      <c r="L46" s="5"/>
+      <c r="M46" t="s">
+        <v>13</v>
+      </c>
+      <c r="N46" s="2">
+        <v>0.70833299999999999</v>
+      </c>
+      <c r="O46" s="2">
+        <v>612.55559300000004</v>
+      </c>
+      <c r="P46">
+        <v>1107.9777730000001</v>
+      </c>
+    </row>
+    <row r="47" spans="4:16" x14ac:dyDescent="0.3">
+      <c r="D47" s="5"/>
       <c r="E47" t="s">
         <v>14</v>
       </c>
@@ -1681,39 +3063,87 @@
         <v>0.91666700000000001</v>
       </c>
       <c r="G47" s="2">
-        <v>940.72508100000005</v>
-      </c>
-    </row>
-    <row r="48" spans="4:7" x14ac:dyDescent="0.3">
-      <c r="D48" s="4"/>
+        <v>893.13836000000003</v>
+      </c>
+      <c r="H47">
+        <v>1678.5416170000001</v>
+      </c>
+      <c r="L47" s="5"/>
+      <c r="M47" t="s">
+        <v>14</v>
+      </c>
+      <c r="N47" s="2">
+        <v>0.79166700000000001</v>
+      </c>
+      <c r="O47" s="2">
+        <v>575.74486000000002</v>
+      </c>
+      <c r="P47">
+        <v>1045.9838090000001</v>
+      </c>
+    </row>
+    <row r="48" spans="4:16" x14ac:dyDescent="0.3">
+      <c r="D48" s="5"/>
       <c r="E48" t="s">
         <v>15</v>
       </c>
       <c r="F48" s="2">
-        <v>0.91666700000000001</v>
+        <v>0.875</v>
       </c>
       <c r="G48" s="2">
-        <v>933.69020699999999</v>
-      </c>
-    </row>
-    <row r="49" spans="4:7" x14ac:dyDescent="0.3">
-      <c r="D49" s="5"/>
-      <c r="E49" s="5"/>
-      <c r="F49" s="5"/>
-      <c r="G49" s="5"/>
+        <v>889.44131000000004</v>
+      </c>
+      <c r="H48">
+        <v>1731.9311970000001</v>
+      </c>
+      <c r="L48" s="5"/>
+      <c r="M48" t="s">
+        <v>15</v>
+      </c>
+      <c r="N48" s="2">
+        <v>0.75</v>
+      </c>
+      <c r="O48" s="2">
+        <v>568.24586099999999</v>
+      </c>
+      <c r="P48">
+        <v>1087.2026820000001</v>
+      </c>
+    </row>
+    <row r="49" spans="4:16" x14ac:dyDescent="0.3">
+      <c r="D49" s="6"/>
+      <c r="E49" s="6"/>
+      <c r="F49" s="6"/>
+      <c r="G49" s="6"/>
+      <c r="H49" s="6"/>
+      <c r="L49" s="6"/>
+      <c r="M49" s="6"/>
+      <c r="N49" s="6"/>
+      <c r="O49" s="6"/>
+      <c r="P49" s="6"/>
     </row>
   </sheetData>
-  <mergeCells count="10">
+  <mergeCells count="20">
+    <mergeCell ref="L32:L39"/>
+    <mergeCell ref="L41:L48"/>
+    <mergeCell ref="L49:P49"/>
+    <mergeCell ref="L40:P40"/>
+    <mergeCell ref="L31:P31"/>
+    <mergeCell ref="L5:L12"/>
+    <mergeCell ref="L14:L21"/>
+    <mergeCell ref="L23:L30"/>
+    <mergeCell ref="L22:P22"/>
+    <mergeCell ref="L13:P13"/>
+    <mergeCell ref="D5:D12"/>
+    <mergeCell ref="D14:D21"/>
+    <mergeCell ref="D23:D30"/>
+    <mergeCell ref="D13:H13"/>
+    <mergeCell ref="D22:H22"/>
     <mergeCell ref="D41:D48"/>
-    <mergeCell ref="D49:G49"/>
     <mergeCell ref="D32:D39"/>
-    <mergeCell ref="D40:G40"/>
-    <mergeCell ref="D31:G31"/>
-    <mergeCell ref="D5:D12"/>
-    <mergeCell ref="D13:G13"/>
-    <mergeCell ref="D14:D21"/>
-    <mergeCell ref="D22:G22"/>
-    <mergeCell ref="D23:D30"/>
+    <mergeCell ref="D31:H31"/>
+    <mergeCell ref="D40:H40"/>
+    <mergeCell ref="D49:H49"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -1721,14 +3151,22 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D9B1F934-9143-4061-8956-2969F906ECCB}">
-  <dimension ref="D4:G44"/>
+  <dimension ref="D3:P44"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="4" max="4" width="16.33203125" customWidth="1"/>
     <col min="5" max="5" width="26" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="4" spans="4:7" x14ac:dyDescent="0.3">
+    <row r="3" spans="4:16" x14ac:dyDescent="0.3">
+      <c r="E3">
+        <v>95</v>
+      </c>
+      <c r="M3">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="4" spans="4:16" x14ac:dyDescent="0.3">
       <c r="D4" t="s">
         <v>5</v>
       </c>
@@ -1741,9 +3179,27 @@
       <c r="G4" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="5" spans="4:7" x14ac:dyDescent="0.3">
-      <c r="D5" s="4">
+      <c r="H4" t="s">
+        <v>31</v>
+      </c>
+      <c r="L4" t="s">
+        <v>5</v>
+      </c>
+      <c r="M4" t="s">
+        <v>6</v>
+      </c>
+      <c r="N4" t="s">
+        <v>7</v>
+      </c>
+      <c r="O4" t="s">
+        <v>8</v>
+      </c>
+      <c r="P4" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="5" spans="4:16" x14ac:dyDescent="0.3">
+      <c r="D5" s="5">
         <v>1</v>
       </c>
       <c r="E5" t="s">
@@ -1753,11 +3209,29 @@
         <v>0.375</v>
       </c>
       <c r="G5">
-        <v>34.144134999999999</v>
-      </c>
-    </row>
-    <row r="6" spans="4:7" x14ac:dyDescent="0.3">
-      <c r="D6" s="4"/>
+        <v>33.179333</v>
+      </c>
+      <c r="H5">
+        <v>1016.311</v>
+      </c>
+      <c r="L5" s="5">
+        <v>1</v>
+      </c>
+      <c r="M5" t="s">
+        <v>16</v>
+      </c>
+      <c r="N5">
+        <v>0.25</v>
+      </c>
+      <c r="O5">
+        <v>22.921666999999999</v>
+      </c>
+      <c r="P5">
+        <v>304.34625</v>
+      </c>
+    </row>
+    <row r="6" spans="4:16" x14ac:dyDescent="0.3">
+      <c r="D6" s="5"/>
       <c r="E6" t="s">
         <v>10</v>
       </c>
@@ -1765,11 +3239,27 @@
         <v>0.25</v>
       </c>
       <c r="G6">
-        <v>23.945511</v>
-      </c>
-    </row>
-    <row r="7" spans="4:7" x14ac:dyDescent="0.3">
-      <c r="D7" s="4"/>
+        <v>23.798846999999999</v>
+      </c>
+      <c r="H6">
+        <v>1127.309291</v>
+      </c>
+      <c r="L6" s="5"/>
+      <c r="M6" t="s">
+        <v>10</v>
+      </c>
+      <c r="N6">
+        <v>0.20833299999999999</v>
+      </c>
+      <c r="O6">
+        <v>18.439632</v>
+      </c>
+      <c r="P6">
+        <v>320.44422400000002</v>
+      </c>
+    </row>
+    <row r="7" spans="4:16" x14ac:dyDescent="0.3">
+      <c r="D7" s="5"/>
       <c r="E7" t="s">
         <v>11</v>
       </c>
@@ -1777,11 +3267,27 @@
         <v>0.16666700000000001</v>
       </c>
       <c r="G7">
-        <v>12.837243000000001</v>
-      </c>
-    </row>
-    <row r="8" spans="4:7" x14ac:dyDescent="0.3">
-      <c r="D8" s="4"/>
+        <v>12.755409999999999</v>
+      </c>
+      <c r="H7">
+        <v>1364.9563479999999</v>
+      </c>
+      <c r="L7" s="5"/>
+      <c r="M7" t="s">
+        <v>11</v>
+      </c>
+      <c r="N7">
+        <v>8.3333000000000004E-2</v>
+      </c>
+      <c r="O7">
+        <v>7.842746</v>
+      </c>
+      <c r="P7">
+        <v>375.74303400000002</v>
+      </c>
+    </row>
+    <row r="8" spans="4:16" x14ac:dyDescent="0.3">
+      <c r="D8" s="5"/>
       <c r="E8" t="s">
         <v>12</v>
       </c>
@@ -1789,11 +3295,27 @@
         <v>8.3333000000000004E-2</v>
       </c>
       <c r="G8">
-        <v>8.5994060000000001</v>
-      </c>
-    </row>
-    <row r="9" spans="4:7" x14ac:dyDescent="0.3">
-      <c r="D9" s="4"/>
+        <v>8.6620679999999997</v>
+      </c>
+      <c r="H8">
+        <v>1467.130015</v>
+      </c>
+      <c r="L8" s="5"/>
+      <c r="M8" t="s">
+        <v>12</v>
+      </c>
+      <c r="N8">
+        <v>4.1667000000000003E-2</v>
+      </c>
+      <c r="O8">
+        <v>6.1548319999999999</v>
+      </c>
+      <c r="P8">
+        <v>381.94016299999998</v>
+      </c>
+    </row>
+    <row r="9" spans="4:16" x14ac:dyDescent="0.3">
+      <c r="D9" s="5"/>
       <c r="E9" t="s">
         <v>13</v>
       </c>
@@ -1801,11 +3323,27 @@
         <v>0.25</v>
       </c>
       <c r="G9">
-        <v>23.724291999999998</v>
-      </c>
-    </row>
-    <row r="10" spans="4:7" x14ac:dyDescent="0.3">
-      <c r="D10" s="4"/>
+        <v>23.975436999999999</v>
+      </c>
+      <c r="H9">
+        <v>1222.800021</v>
+      </c>
+      <c r="L9" s="5"/>
+      <c r="M9" t="s">
+        <v>13</v>
+      </c>
+      <c r="N9">
+        <v>0.16666700000000001</v>
+      </c>
+      <c r="O9">
+        <v>14.524457999999999</v>
+      </c>
+      <c r="P9">
+        <v>355.09529199999997</v>
+      </c>
+    </row>
+    <row r="10" spans="4:16" x14ac:dyDescent="0.3">
+      <c r="D10" s="5"/>
       <c r="E10" t="s">
         <v>14</v>
       </c>
@@ -1813,11 +3351,27 @@
         <v>4.1667000000000003E-2</v>
       </c>
       <c r="G10">
-        <v>5.9844869999999997</v>
-      </c>
-    </row>
-    <row r="11" spans="4:7" x14ac:dyDescent="0.3">
-      <c r="D11" s="4"/>
+        <v>5.9619470000000003</v>
+      </c>
+      <c r="H10">
+        <v>1527.529902</v>
+      </c>
+      <c r="L10" s="5"/>
+      <c r="M10" t="s">
+        <v>14</v>
+      </c>
+      <c r="N10">
+        <v>4.1667000000000003E-2</v>
+      </c>
+      <c r="O10">
+        <v>4.4795199999999999</v>
+      </c>
+      <c r="P10">
+        <v>392.117009</v>
+      </c>
+    </row>
+    <row r="11" spans="4:16" x14ac:dyDescent="0.3">
+      <c r="D11" s="5"/>
       <c r="E11" t="s">
         <v>15</v>
       </c>
@@ -1827,15 +3381,37 @@
       <c r="G11">
         <v>34.246572999999998</v>
       </c>
-    </row>
-    <row r="12" spans="4:7" x14ac:dyDescent="0.3">
-      <c r="D12" s="6"/>
-      <c r="E12" s="6"/>
-      <c r="F12" s="6"/>
-      <c r="G12" s="6"/>
-    </row>
-    <row r="13" spans="4:7" x14ac:dyDescent="0.3">
-      <c r="D13" s="4">
+      <c r="H11">
+        <v>991.95657300000005</v>
+      </c>
+      <c r="L11" s="5"/>
+      <c r="M11" t="s">
+        <v>15</v>
+      </c>
+      <c r="N11">
+        <v>0.25</v>
+      </c>
+      <c r="O11">
+        <v>24.866667</v>
+      </c>
+      <c r="P11">
+        <v>298.49166300000002</v>
+      </c>
+    </row>
+    <row r="12" spans="4:16" x14ac:dyDescent="0.3">
+      <c r="D12" s="7"/>
+      <c r="E12" s="7"/>
+      <c r="F12" s="7"/>
+      <c r="G12" s="7"/>
+      <c r="H12" s="7"/>
+      <c r="L12" s="7"/>
+      <c r="M12" s="7"/>
+      <c r="N12" s="7"/>
+      <c r="O12" s="7"/>
+      <c r="P12" s="7"/>
+    </row>
+    <row r="13" spans="4:16" x14ac:dyDescent="0.3">
+      <c r="D13" s="5">
         <v>2</v>
       </c>
       <c r="E13" t="s">
@@ -1845,11 +3421,29 @@
         <v>0.79166700000000001</v>
       </c>
       <c r="G13">
-        <v>4.8847680000000002</v>
-      </c>
-    </row>
-    <row r="14" spans="4:7" x14ac:dyDescent="0.3">
-      <c r="D14" s="4"/>
+        <v>4.8286910000000001</v>
+      </c>
+      <c r="H13">
+        <v>11.453649</v>
+      </c>
+      <c r="L13" s="5">
+        <v>2</v>
+      </c>
+      <c r="M13" t="s">
+        <v>16</v>
+      </c>
+      <c r="N13">
+        <v>0.79166700000000001</v>
+      </c>
+      <c r="O13">
+        <v>4.8286910000000001</v>
+      </c>
+      <c r="P13">
+        <v>11.453649</v>
+      </c>
+    </row>
+    <row r="14" spans="4:16" x14ac:dyDescent="0.3">
+      <c r="D14" s="5"/>
       <c r="E14" t="s">
         <v>10</v>
       </c>
@@ -1857,11 +3451,27 @@
         <v>0.79166700000000001</v>
       </c>
       <c r="G14">
-        <v>4.2140019999999998</v>
-      </c>
-    </row>
-    <row r="15" spans="4:7" x14ac:dyDescent="0.3">
-      <c r="D15" s="4"/>
+        <v>4.2649290000000004</v>
+      </c>
+      <c r="H14">
+        <v>12.97362</v>
+      </c>
+      <c r="L14" s="5"/>
+      <c r="M14" t="s">
+        <v>10</v>
+      </c>
+      <c r="N14">
+        <v>0.79166700000000001</v>
+      </c>
+      <c r="O14">
+        <v>4.2649290000000004</v>
+      </c>
+      <c r="P14">
+        <v>12.97362</v>
+      </c>
+    </row>
+    <row r="15" spans="4:16" x14ac:dyDescent="0.3">
+      <c r="D15" s="5"/>
       <c r="E15" t="s">
         <v>11</v>
       </c>
@@ -1869,23 +3479,55 @@
         <v>0.45833299999999999</v>
       </c>
       <c r="G15">
-        <v>2.0839439999999998</v>
-      </c>
-    </row>
-    <row r="16" spans="4:7" x14ac:dyDescent="0.3">
-      <c r="D16" s="4"/>
+        <v>2.1004209999999999</v>
+      </c>
+      <c r="H15">
+        <v>27.946280000000002</v>
+      </c>
+      <c r="L15" s="5"/>
+      <c r="M15" t="s">
+        <v>11</v>
+      </c>
+      <c r="N15">
+        <v>0.45833299999999999</v>
+      </c>
+      <c r="O15">
+        <v>2.1004209999999999</v>
+      </c>
+      <c r="P15">
+        <v>27.946280000000002</v>
+      </c>
+    </row>
+    <row r="16" spans="4:16" x14ac:dyDescent="0.3">
+      <c r="D16" s="5"/>
       <c r="E16" t="s">
         <v>12</v>
       </c>
       <c r="F16">
-        <v>0.375</v>
+        <v>0.29166700000000001</v>
       </c>
       <c r="G16">
-        <v>1.7597320000000001</v>
-      </c>
-    </row>
-    <row r="17" spans="4:7" x14ac:dyDescent="0.3">
-      <c r="D17" s="4"/>
+        <v>1.7770539999999999</v>
+      </c>
+      <c r="H16">
+        <v>31.718164999999999</v>
+      </c>
+      <c r="L16" s="5"/>
+      <c r="M16" t="s">
+        <v>12</v>
+      </c>
+      <c r="N16">
+        <v>0.29166700000000001</v>
+      </c>
+      <c r="O16">
+        <v>1.7770539999999999</v>
+      </c>
+      <c r="P16">
+        <v>31.718164999999999</v>
+      </c>
+    </row>
+    <row r="17" spans="4:16" x14ac:dyDescent="0.3">
+      <c r="D17" s="5"/>
       <c r="E17" t="s">
         <v>13</v>
       </c>
@@ -1893,23 +3535,55 @@
         <v>0.70833299999999999</v>
       </c>
       <c r="G17">
-        <v>4.2938049999999999</v>
-      </c>
-    </row>
-    <row r="18" spans="4:7" x14ac:dyDescent="0.3">
-      <c r="D18" s="4"/>
+        <v>4.3024690000000003</v>
+      </c>
+      <c r="H17">
+        <v>14.289676999999999</v>
+      </c>
+      <c r="L17" s="5"/>
+      <c r="M17" t="s">
+        <v>13</v>
+      </c>
+      <c r="N17">
+        <v>0.70833299999999999</v>
+      </c>
+      <c r="O17">
+        <v>4.3024690000000003</v>
+      </c>
+      <c r="P17">
+        <v>14.289676999999999</v>
+      </c>
+    </row>
+    <row r="18" spans="4:16" x14ac:dyDescent="0.3">
+      <c r="D18" s="5"/>
       <c r="E18" t="s">
         <v>14</v>
       </c>
       <c r="F18">
-        <v>0.75</v>
+        <v>0.79166700000000001</v>
       </c>
       <c r="G18">
-        <v>4.2911840000000003</v>
-      </c>
-    </row>
-    <row r="19" spans="4:7" x14ac:dyDescent="0.3">
-      <c r="D19" s="4"/>
+        <v>4.3276519999999996</v>
+      </c>
+      <c r="H18">
+        <v>17.57959</v>
+      </c>
+      <c r="L18" s="5"/>
+      <c r="M18" t="s">
+        <v>14</v>
+      </c>
+      <c r="N18">
+        <v>0.79166700000000001</v>
+      </c>
+      <c r="O18">
+        <v>4.3276519999999996</v>
+      </c>
+      <c r="P18">
+        <v>17.57959</v>
+      </c>
+    </row>
+    <row r="19" spans="4:16" x14ac:dyDescent="0.3">
+      <c r="D19" s="5"/>
       <c r="E19" t="s">
         <v>15</v>
       </c>
@@ -1919,29 +3593,69 @@
       <c r="G19">
         <v>5.2630650000000001</v>
       </c>
-    </row>
-    <row r="20" spans="4:7" x14ac:dyDescent="0.3">
-      <c r="D20" s="5"/>
-      <c r="E20" s="5"/>
-      <c r="F20" s="5"/>
-      <c r="G20" s="5"/>
-    </row>
-    <row r="21" spans="4:7" x14ac:dyDescent="0.3">
-      <c r="D21" s="4">
+      <c r="H19">
+        <v>10.579065</v>
+      </c>
+      <c r="L19" s="5"/>
+      <c r="M19" t="s">
+        <v>15</v>
+      </c>
+      <c r="N19">
+        <v>0.83333299999999999</v>
+      </c>
+      <c r="O19">
+        <v>5.2630650000000001</v>
+      </c>
+      <c r="P19">
+        <v>10.579065</v>
+      </c>
+    </row>
+    <row r="20" spans="4:16" x14ac:dyDescent="0.3">
+      <c r="D20" s="6"/>
+      <c r="E20" s="6"/>
+      <c r="F20" s="6"/>
+      <c r="G20" s="6"/>
+      <c r="H20" s="6"/>
+      <c r="L20" s="6"/>
+      <c r="M20" s="6"/>
+      <c r="N20" s="6"/>
+      <c r="O20" s="6"/>
+      <c r="P20" s="6"/>
+    </row>
+    <row r="21" spans="4:16" x14ac:dyDescent="0.3">
+      <c r="D21" s="5">
         <v>3</v>
       </c>
       <c r="E21" t="s">
         <v>16</v>
       </c>
       <c r="F21">
-        <v>0.55000000000000004</v>
+        <v>0.6</v>
       </c>
       <c r="G21">
-        <v>1376.209112</v>
-      </c>
-    </row>
-    <row r="22" spans="4:7" x14ac:dyDescent="0.3">
-      <c r="D22" s="4"/>
+        <v>1389.1378500000001</v>
+      </c>
+      <c r="H21">
+        <v>5409.9988499999999</v>
+      </c>
+      <c r="L21" s="5">
+        <v>3</v>
+      </c>
+      <c r="M21" t="s">
+        <v>16</v>
+      </c>
+      <c r="N21">
+        <v>0.3</v>
+      </c>
+      <c r="O21">
+        <v>691.68484999999998</v>
+      </c>
+      <c r="P21">
+        <v>3315.09285</v>
+      </c>
+    </row>
+    <row r="22" spans="4:16" x14ac:dyDescent="0.3">
+      <c r="D22" s="5"/>
       <c r="E22" t="s">
         <v>10</v>
       </c>
@@ -1949,23 +3663,55 @@
         <v>0.6</v>
       </c>
       <c r="G22">
-        <v>1527.4098349999999</v>
-      </c>
-    </row>
-    <row r="23" spans="4:7" x14ac:dyDescent="0.3">
-      <c r="D23" s="4"/>
+        <v>1526.43832</v>
+      </c>
+      <c r="H22">
+        <v>4547.0122499999998</v>
+      </c>
+      <c r="L22" s="5"/>
+      <c r="M22" t="s">
+        <v>10</v>
+      </c>
+      <c r="N22">
+        <v>0.5</v>
+      </c>
+      <c r="O22">
+        <v>1183.301404</v>
+      </c>
+      <c r="P22">
+        <v>2497.1533009999998</v>
+      </c>
+    </row>
+    <row r="23" spans="4:16" x14ac:dyDescent="0.3">
+      <c r="D23" s="5"/>
       <c r="E23" t="s">
         <v>11</v>
       </c>
       <c r="F23">
-        <v>0.3</v>
+        <v>0.25</v>
       </c>
       <c r="G23">
-        <v>509.229738</v>
-      </c>
-    </row>
-    <row r="24" spans="4:7" x14ac:dyDescent="0.3">
-      <c r="D24" s="4"/>
+        <v>497.92233700000003</v>
+      </c>
+      <c r="H23">
+        <v>12709.289934</v>
+      </c>
+      <c r="L23" s="5"/>
+      <c r="M23" t="s">
+        <v>11</v>
+      </c>
+      <c r="N23">
+        <v>0.15</v>
+      </c>
+      <c r="O23">
+        <v>336.346092</v>
+      </c>
+      <c r="P23">
+        <v>4045.667668</v>
+      </c>
+    </row>
+    <row r="24" spans="4:16" x14ac:dyDescent="0.3">
+      <c r="D24" s="5"/>
       <c r="E24" t="s">
         <v>12</v>
       </c>
@@ -1973,11 +3719,27 @@
         <v>0.25</v>
       </c>
       <c r="G24">
-        <v>425.22268600000001</v>
-      </c>
-    </row>
-    <row r="25" spans="4:7" x14ac:dyDescent="0.3">
-      <c r="D25" s="4"/>
+        <v>432.04848299999998</v>
+      </c>
+      <c r="H24">
+        <v>13692.071889000001</v>
+      </c>
+      <c r="L24" s="5"/>
+      <c r="M24" t="s">
+        <v>12</v>
+      </c>
+      <c r="N24">
+        <v>0.15</v>
+      </c>
+      <c r="O24">
+        <v>289.65741500000001</v>
+      </c>
+      <c r="P24">
+        <v>4194.2469170000004</v>
+      </c>
+    </row>
+    <row r="25" spans="4:16" x14ac:dyDescent="0.3">
+      <c r="D25" s="5"/>
       <c r="E25" t="s">
         <v>13</v>
       </c>
@@ -1985,11 +3747,27 @@
         <v>0.5</v>
       </c>
       <c r="G25">
-        <v>1001.471212</v>
-      </c>
-    </row>
-    <row r="26" spans="4:7" x14ac:dyDescent="0.3">
-      <c r="D26" s="4"/>
+        <v>1004.955737</v>
+      </c>
+      <c r="H25">
+        <v>5908.7757380000003</v>
+      </c>
+      <c r="L25" s="5"/>
+      <c r="M25" t="s">
+        <v>13</v>
+      </c>
+      <c r="N25">
+        <v>0.3</v>
+      </c>
+      <c r="O25">
+        <v>543.57005000000004</v>
+      </c>
+      <c r="P25">
+        <v>3269.03505</v>
+      </c>
+    </row>
+    <row r="26" spans="4:16" x14ac:dyDescent="0.3">
+      <c r="D26" s="5"/>
       <c r="E26" t="s">
         <v>14</v>
       </c>
@@ -1997,11 +3775,27 @@
         <v>0</v>
       </c>
       <c r="G26">
-        <v>5.473039</v>
-      </c>
-    </row>
-    <row r="27" spans="4:7" x14ac:dyDescent="0.3">
-      <c r="D27" s="4"/>
+        <v>5.5405129999999998</v>
+      </c>
+      <c r="H26">
+        <v>21523.656132</v>
+      </c>
+      <c r="L26" s="5"/>
+      <c r="M26" t="s">
+        <v>14</v>
+      </c>
+      <c r="N26">
+        <v>0</v>
+      </c>
+      <c r="O26">
+        <v>3.9715479999999999</v>
+      </c>
+      <c r="P26">
+        <v>5391.4525190000004</v>
+      </c>
+    </row>
+    <row r="27" spans="4:16" x14ac:dyDescent="0.3">
+      <c r="D27" s="5"/>
       <c r="E27" t="s">
         <v>15</v>
       </c>
@@ -2011,15 +3805,37 @@
       <c r="G27">
         <v>1448.1409249999999</v>
       </c>
-    </row>
-    <row r="28" spans="4:7" x14ac:dyDescent="0.3">
-      <c r="D28" s="5"/>
-      <c r="E28" s="5"/>
-      <c r="F28" s="5"/>
-      <c r="G28" s="5"/>
-    </row>
-    <row r="29" spans="4:7" x14ac:dyDescent="0.3">
-      <c r="D29" s="4">
+      <c r="H27">
+        <v>3277.8984249999999</v>
+      </c>
+      <c r="L27" s="5"/>
+      <c r="M27" t="s">
+        <v>15</v>
+      </c>
+      <c r="N27">
+        <v>0.4</v>
+      </c>
+      <c r="O27">
+        <v>801.19489999999996</v>
+      </c>
+      <c r="P27">
+        <v>2734.74415</v>
+      </c>
+    </row>
+    <row r="28" spans="4:16" x14ac:dyDescent="0.3">
+      <c r="D28" s="6"/>
+      <c r="E28" s="6"/>
+      <c r="F28" s="6"/>
+      <c r="G28" s="6"/>
+      <c r="H28" s="6"/>
+      <c r="L28" s="6"/>
+      <c r="M28" s="6"/>
+      <c r="N28" s="6"/>
+      <c r="O28" s="6"/>
+      <c r="P28" s="6"/>
+    </row>
+    <row r="29" spans="4:16" x14ac:dyDescent="0.3">
+      <c r="D29" s="5">
         <v>4</v>
       </c>
       <c r="E29" t="s">
@@ -2029,11 +3845,29 @@
         <v>0.25</v>
       </c>
       <c r="G29">
-        <v>58.867489999999997</v>
-      </c>
-    </row>
-    <row r="30" spans="4:7" x14ac:dyDescent="0.3">
-      <c r="D30" s="4"/>
+        <v>57.49624</v>
+      </c>
+      <c r="H29">
+        <v>1869.603323</v>
+      </c>
+      <c r="L29" s="5">
+        <v>4</v>
+      </c>
+      <c r="M29" t="s">
+        <v>16</v>
+      </c>
+      <c r="N29">
+        <v>0.16666700000000001</v>
+      </c>
+      <c r="O29">
+        <v>33.385832999999998</v>
+      </c>
+      <c r="P29">
+        <v>603.29583300000002</v>
+      </c>
+    </row>
+    <row r="30" spans="4:16" x14ac:dyDescent="0.3">
+      <c r="D30" s="5"/>
       <c r="E30" t="s">
         <v>10</v>
       </c>
@@ -2041,11 +3875,27 @@
         <v>0.20833299999999999</v>
       </c>
       <c r="G30">
-        <v>46.697495000000004</v>
-      </c>
-    </row>
-    <row r="31" spans="4:7" x14ac:dyDescent="0.3">
-      <c r="D31" s="4"/>
+        <v>46.850878999999999</v>
+      </c>
+      <c r="H30">
+        <v>2070.9472340000002</v>
+      </c>
+      <c r="L30" s="5"/>
+      <c r="M30" t="s">
+        <v>10</v>
+      </c>
+      <c r="N30">
+        <v>0.16666700000000001</v>
+      </c>
+      <c r="O30">
+        <v>34.900326</v>
+      </c>
+      <c r="P30">
+        <v>596.01668099999995</v>
+      </c>
+    </row>
+    <row r="31" spans="4:16" x14ac:dyDescent="0.3">
+      <c r="D31" s="5"/>
       <c r="E31" t="s">
         <v>11</v>
       </c>
@@ -2053,11 +3903,27 @@
         <v>0.16666700000000001</v>
       </c>
       <c r="G31">
-        <v>23.463401999999999</v>
-      </c>
-    </row>
-    <row r="32" spans="4:7" x14ac:dyDescent="0.3">
-      <c r="D32" s="4"/>
+        <v>23.302811999999999</v>
+      </c>
+      <c r="H31">
+        <v>2436.5750630000002</v>
+      </c>
+      <c r="L31" s="5"/>
+      <c r="M31" t="s">
+        <v>11</v>
+      </c>
+      <c r="N31">
+        <v>0.125</v>
+      </c>
+      <c r="O31">
+        <v>15.380013</v>
+      </c>
+      <c r="P31">
+        <v>655.13962500000002</v>
+      </c>
+    </row>
+    <row r="32" spans="4:16" x14ac:dyDescent="0.3">
+      <c r="D32" s="5"/>
       <c r="E32" t="s">
         <v>12</v>
       </c>
@@ -2065,23 +3931,55 @@
         <v>0.125</v>
       </c>
       <c r="G32">
-        <v>20.009763</v>
-      </c>
-    </row>
-    <row r="33" spans="4:7" x14ac:dyDescent="0.3">
-      <c r="D33" s="4"/>
+        <v>20.259840000000001</v>
+      </c>
+      <c r="H32">
+        <v>2482.136321</v>
+      </c>
+      <c r="L32" s="5"/>
+      <c r="M32" t="s">
+        <v>12</v>
+      </c>
+      <c r="N32">
+        <v>0.125</v>
+      </c>
+      <c r="O32">
+        <v>13.20524</v>
+      </c>
+      <c r="P32">
+        <v>661.83774900000003</v>
+      </c>
+    </row>
+    <row r="33" spans="4:16" x14ac:dyDescent="0.3">
+      <c r="D33" s="5"/>
       <c r="E33" t="s">
         <v>13</v>
       </c>
       <c r="F33">
-        <v>0.25</v>
+        <v>0.20833299999999999</v>
       </c>
       <c r="G33">
-        <v>54.664957999999999</v>
-      </c>
-    </row>
-    <row r="34" spans="4:7" x14ac:dyDescent="0.3">
-      <c r="D34" s="4"/>
+        <v>56.088562000000003</v>
+      </c>
+      <c r="H33">
+        <v>1844.566896</v>
+      </c>
+      <c r="L33" s="5"/>
+      <c r="M33" t="s">
+        <v>13</v>
+      </c>
+      <c r="N33">
+        <v>0.16666700000000001</v>
+      </c>
+      <c r="O33">
+        <v>29.143249999999998</v>
+      </c>
+      <c r="P33">
+        <v>624.92200000000003</v>
+      </c>
+    </row>
+    <row r="34" spans="4:16" x14ac:dyDescent="0.3">
+      <c r="D34" s="5"/>
       <c r="E34" t="s">
         <v>14</v>
       </c>
@@ -2089,11 +3987,27 @@
         <v>0</v>
       </c>
       <c r="G34">
-        <v>5.7547449999999998</v>
-      </c>
-    </row>
-    <row r="35" spans="4:7" x14ac:dyDescent="0.3">
-      <c r="D35" s="4"/>
+        <v>5.6864980000000003</v>
+      </c>
+      <c r="H34">
+        <v>2759.2560140000001</v>
+      </c>
+      <c r="L34" s="5"/>
+      <c r="M34" t="s">
+        <v>14</v>
+      </c>
+      <c r="N34">
+        <v>0</v>
+      </c>
+      <c r="O34">
+        <v>3.810073</v>
+      </c>
+      <c r="P34">
+        <v>702.811779</v>
+      </c>
+    </row>
+    <row r="35" spans="4:16" x14ac:dyDescent="0.3">
+      <c r="D35" s="5"/>
       <c r="E35" t="s">
         <v>15</v>
       </c>
@@ -2103,15 +4017,37 @@
       <c r="G35">
         <v>55.995865000000002</v>
       </c>
-    </row>
-    <row r="36" spans="4:7" x14ac:dyDescent="0.3">
-      <c r="D36" s="5"/>
-      <c r="E36" s="5"/>
-      <c r="F36" s="5"/>
-      <c r="G36" s="5"/>
-    </row>
-    <row r="37" spans="4:7" x14ac:dyDescent="0.3">
-      <c r="D37" s="4">
+      <c r="H35">
+        <v>1925.0547670000001</v>
+      </c>
+      <c r="L35" s="5"/>
+      <c r="M35" t="s">
+        <v>15</v>
+      </c>
+      <c r="N35">
+        <v>0.16666700000000001</v>
+      </c>
+      <c r="O35">
+        <v>35.8795</v>
+      </c>
+      <c r="P35">
+        <v>596.09552599999995</v>
+      </c>
+    </row>
+    <row r="36" spans="4:16" x14ac:dyDescent="0.3">
+      <c r="D36" s="6"/>
+      <c r="E36" s="6"/>
+      <c r="F36" s="6"/>
+      <c r="G36" s="6"/>
+      <c r="H36" s="6"/>
+      <c r="L36" s="6"/>
+      <c r="M36" s="6"/>
+      <c r="N36" s="6"/>
+      <c r="O36" s="6"/>
+      <c r="P36" s="6"/>
+    </row>
+    <row r="37" spans="4:16" x14ac:dyDescent="0.3">
+      <c r="D37" s="5">
         <v>5</v>
       </c>
       <c r="E37" t="s">
@@ -2121,11 +4057,29 @@
         <v>0.29166700000000001</v>
       </c>
       <c r="G37">
-        <v>297.578644</v>
-      </c>
-    </row>
-    <row r="38" spans="4:7" x14ac:dyDescent="0.3">
-      <c r="D38" s="4"/>
+        <v>298.28983799999997</v>
+      </c>
+      <c r="H37">
+        <v>7340.3404710000004</v>
+      </c>
+      <c r="L37" s="5">
+        <v>5</v>
+      </c>
+      <c r="M37" t="s">
+        <v>16</v>
+      </c>
+      <c r="N37">
+        <v>0.125</v>
+      </c>
+      <c r="O37">
+        <v>185.21620999999999</v>
+      </c>
+      <c r="P37">
+        <v>2388.9993330000002</v>
+      </c>
+    </row>
+    <row r="38" spans="4:16" x14ac:dyDescent="0.3">
+      <c r="D38" s="5"/>
       <c r="E38" t="s">
         <v>10</v>
       </c>
@@ -2133,11 +4087,27 @@
         <v>0.16666700000000001</v>
       </c>
       <c r="G38">
-        <v>196.72213500000001</v>
-      </c>
-    </row>
-    <row r="39" spans="4:7" x14ac:dyDescent="0.3">
-      <c r="D39" s="4"/>
+        <v>198.10220200000001</v>
+      </c>
+      <c r="H38">
+        <v>8747.9054219999998</v>
+      </c>
+      <c r="L38" s="5"/>
+      <c r="M38" t="s">
+        <v>10</v>
+      </c>
+      <c r="N38">
+        <v>0.125</v>
+      </c>
+      <c r="O38">
+        <v>147.758499</v>
+      </c>
+      <c r="P38">
+        <v>2503.7735010000001</v>
+      </c>
+    </row>
+    <row r="39" spans="4:16" x14ac:dyDescent="0.3">
+      <c r="D39" s="5"/>
       <c r="E39" t="s">
         <v>11</v>
       </c>
@@ -2145,11 +4115,27 @@
         <v>0.125</v>
       </c>
       <c r="G39">
-        <v>116.041706</v>
-      </c>
-    </row>
-    <row r="40" spans="4:7" x14ac:dyDescent="0.3">
-      <c r="D40" s="4"/>
+        <v>116.65461999999999</v>
+      </c>
+      <c r="H39">
+        <v>9935.6293879999994</v>
+      </c>
+      <c r="L39" s="5"/>
+      <c r="M39" t="s">
+        <v>11</v>
+      </c>
+      <c r="N39">
+        <v>0.125</v>
+      </c>
+      <c r="O39">
+        <v>75.973654999999994</v>
+      </c>
+      <c r="P39">
+        <v>2702.8498330000002</v>
+      </c>
+    </row>
+    <row r="40" spans="4:16" x14ac:dyDescent="0.3">
+      <c r="D40" s="5"/>
       <c r="E40" t="s">
         <v>12</v>
       </c>
@@ -2157,11 +4143,27 @@
         <v>0.125</v>
       </c>
       <c r="G40">
-        <v>102.865477</v>
-      </c>
-    </row>
-    <row r="41" spans="4:7" x14ac:dyDescent="0.3">
-      <c r="D41" s="4"/>
+        <v>102.88864100000001</v>
+      </c>
+      <c r="H40">
+        <v>10109.198096</v>
+      </c>
+      <c r="L40" s="5"/>
+      <c r="M40" t="s">
+        <v>12</v>
+      </c>
+      <c r="N40">
+        <v>8.3333000000000004E-2</v>
+      </c>
+      <c r="O40">
+        <v>67.251092</v>
+      </c>
+      <c r="P40">
+        <v>2731.3995949999999</v>
+      </c>
+    </row>
+    <row r="41" spans="4:16" x14ac:dyDescent="0.3">
+      <c r="D41" s="5"/>
       <c r="E41" t="s">
         <v>13</v>
       </c>
@@ -2169,11 +4171,27 @@
         <v>0.25</v>
       </c>
       <c r="G41">
-        <v>275.98971899999998</v>
-      </c>
-    </row>
-    <row r="42" spans="4:7" x14ac:dyDescent="0.3">
-      <c r="D42" s="4"/>
+        <v>274.095325</v>
+      </c>
+      <c r="H41">
+        <v>7689.6643979999999</v>
+      </c>
+      <c r="L41" s="5"/>
+      <c r="M41" t="s">
+        <v>13</v>
+      </c>
+      <c r="N41">
+        <v>0.125</v>
+      </c>
+      <c r="O41">
+        <v>157.94366400000001</v>
+      </c>
+      <c r="P41">
+        <v>2440.7142039999999</v>
+      </c>
+    </row>
+    <row r="42" spans="4:16" x14ac:dyDescent="0.3">
+      <c r="D42" s="5"/>
       <c r="E42" t="s">
         <v>14</v>
       </c>
@@ -2181,11 +4199,27 @@
         <v>0</v>
       </c>
       <c r="G42">
-        <v>6.3266600000000004</v>
-      </c>
-    </row>
-    <row r="43" spans="4:7" x14ac:dyDescent="0.3">
-      <c r="D43" s="4"/>
+        <v>6.2155889999999996</v>
+      </c>
+      <c r="H42">
+        <v>11786.761043</v>
+      </c>
+      <c r="L42" s="5"/>
+      <c r="M42" t="s">
+        <v>14</v>
+      </c>
+      <c r="N42">
+        <v>0</v>
+      </c>
+      <c r="O42">
+        <v>4.0214299999999996</v>
+      </c>
+      <c r="P42">
+        <v>2958.7487820000001</v>
+      </c>
+    </row>
+    <row r="43" spans="4:16" x14ac:dyDescent="0.3">
+      <c r="D43" s="5"/>
       <c r="E43" t="s">
         <v>15</v>
       </c>
@@ -2195,25 +4229,57 @@
       <c r="G43">
         <v>292.207177</v>
       </c>
-    </row>
-    <row r="44" spans="4:7" x14ac:dyDescent="0.3">
-      <c r="D44" s="5"/>
-      <c r="E44" s="5"/>
-      <c r="F44" s="5"/>
-      <c r="G44" s="5"/>
+      <c r="H43">
+        <v>7355.1954500000002</v>
+      </c>
+      <c r="L43" s="5"/>
+      <c r="M43" t="s">
+        <v>15</v>
+      </c>
+      <c r="N43">
+        <v>0.125</v>
+      </c>
+      <c r="O43">
+        <v>199.488564</v>
+      </c>
+      <c r="P43">
+        <v>2342.201047</v>
+      </c>
+    </row>
+    <row r="44" spans="4:16" x14ac:dyDescent="0.3">
+      <c r="D44" s="6"/>
+      <c r="E44" s="6"/>
+      <c r="F44" s="6"/>
+      <c r="G44" s="6"/>
+      <c r="H44" s="6"/>
+      <c r="L44" s="6"/>
+      <c r="M44" s="6"/>
+      <c r="N44" s="6"/>
+      <c r="O44" s="6"/>
+      <c r="P44" s="6"/>
     </row>
   </sheetData>
-  <mergeCells count="10">
+  <mergeCells count="20">
+    <mergeCell ref="L29:L35"/>
+    <mergeCell ref="L37:L43"/>
+    <mergeCell ref="L28:P28"/>
+    <mergeCell ref="L36:P36"/>
+    <mergeCell ref="L44:P44"/>
+    <mergeCell ref="L5:L11"/>
+    <mergeCell ref="L13:L19"/>
+    <mergeCell ref="L21:L27"/>
+    <mergeCell ref="L12:P12"/>
+    <mergeCell ref="L20:P20"/>
+    <mergeCell ref="D5:D11"/>
+    <mergeCell ref="D13:D19"/>
+    <mergeCell ref="D21:D27"/>
+    <mergeCell ref="D12:H12"/>
+    <mergeCell ref="D20:H20"/>
     <mergeCell ref="D37:D43"/>
-    <mergeCell ref="D44:G44"/>
     <mergeCell ref="D29:D35"/>
-    <mergeCell ref="D36:G36"/>
-    <mergeCell ref="D28:G28"/>
-    <mergeCell ref="D5:D11"/>
-    <mergeCell ref="D12:G12"/>
-    <mergeCell ref="D13:D19"/>
-    <mergeCell ref="D20:G20"/>
-    <mergeCell ref="D21:D27"/>
+    <mergeCell ref="D28:H28"/>
+    <mergeCell ref="D36:H36"/>
+    <mergeCell ref="D44:H44"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -2221,14 +4287,22 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{AA9C7C1F-8E69-4E9D-9311-55B2096F876D}">
-  <dimension ref="D4:G44"/>
+  <dimension ref="D3:P44"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="4" max="4" width="16.33203125" customWidth="1"/>
     <col min="5" max="5" width="26" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="4" spans="4:7" x14ac:dyDescent="0.3">
+    <row r="3" spans="4:16" x14ac:dyDescent="0.3">
+      <c r="E3">
+        <v>95</v>
+      </c>
+      <c r="M3">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="4" spans="4:16" x14ac:dyDescent="0.3">
       <c r="D4" t="s">
         <v>5</v>
       </c>
@@ -2241,9 +4315,27 @@
       <c r="G4" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="5" spans="4:7" x14ac:dyDescent="0.3">
-      <c r="D5" s="4">
+      <c r="H4" t="s">
+        <v>31</v>
+      </c>
+      <c r="L4" t="s">
+        <v>5</v>
+      </c>
+      <c r="M4" t="s">
+        <v>6</v>
+      </c>
+      <c r="N4" t="s">
+        <v>7</v>
+      </c>
+      <c r="O4" t="s">
+        <v>8</v>
+      </c>
+      <c r="P4" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="5" spans="4:16" x14ac:dyDescent="0.3">
+      <c r="D5" s="5">
         <v>1</v>
       </c>
       <c r="E5" t="s">
@@ -2253,11 +4345,29 @@
         <v>0.16666700000000001</v>
       </c>
       <c r="G5">
-        <v>17.689375999999999</v>
-      </c>
-    </row>
-    <row r="6" spans="4:7" x14ac:dyDescent="0.3">
-      <c r="D6" s="4"/>
+        <v>17.793444000000001</v>
+      </c>
+      <c r="H5">
+        <v>1728.848467</v>
+      </c>
+      <c r="L5" s="5">
+        <v>1</v>
+      </c>
+      <c r="M5" t="s">
+        <v>16</v>
+      </c>
+      <c r="N5">
+        <v>0.125</v>
+      </c>
+      <c r="O5">
+        <v>11.741493</v>
+      </c>
+      <c r="P5">
+        <v>467.25515799999999</v>
+      </c>
+    </row>
+    <row r="6" spans="4:16" x14ac:dyDescent="0.3">
+      <c r="D6" s="5"/>
       <c r="E6" t="s">
         <v>10</v>
       </c>
@@ -2265,23 +4375,55 @@
         <v>0.125</v>
       </c>
       <c r="G6">
-        <v>13.845589</v>
-      </c>
-    </row>
-    <row r="7" spans="4:7" x14ac:dyDescent="0.3">
-      <c r="D7" s="4"/>
+        <v>13.727124</v>
+      </c>
+      <c r="H6">
+        <v>1806.212231</v>
+      </c>
+      <c r="L6" s="5"/>
+      <c r="M6" t="s">
+        <v>10</v>
+      </c>
+      <c r="N6">
+        <v>0.125</v>
+      </c>
+      <c r="O6">
+        <v>10.106154</v>
+      </c>
+      <c r="P6">
+        <v>474.86247300000002</v>
+      </c>
+    </row>
+    <row r="7" spans="4:16" x14ac:dyDescent="0.3">
+      <c r="D7" s="5"/>
       <c r="E7" t="s">
         <v>11</v>
       </c>
       <c r="F7">
-        <v>0.125</v>
+        <v>8.3333000000000004E-2</v>
       </c>
       <c r="G7">
-        <v>9.2604380000000006</v>
-      </c>
-    </row>
-    <row r="8" spans="4:7" x14ac:dyDescent="0.3">
-      <c r="D8" s="4"/>
+        <v>8.8489059999999995</v>
+      </c>
+      <c r="H7">
+        <v>1889.586409</v>
+      </c>
+      <c r="L7" s="5"/>
+      <c r="M7" t="s">
+        <v>11</v>
+      </c>
+      <c r="N7">
+        <v>8.3333000000000004E-2</v>
+      </c>
+      <c r="O7">
+        <v>6.3085740000000001</v>
+      </c>
+      <c r="P7">
+        <v>486.151747</v>
+      </c>
+    </row>
+    <row r="8" spans="4:16" x14ac:dyDescent="0.3">
+      <c r="D8" s="5"/>
       <c r="E8" t="s">
         <v>12</v>
       </c>
@@ -2289,11 +4431,27 @@
         <v>8.3333000000000004E-2</v>
       </c>
       <c r="G8">
-        <v>8.0394089999999991</v>
-      </c>
-    </row>
-    <row r="9" spans="4:7" x14ac:dyDescent="0.3">
-      <c r="D9" s="4"/>
+        <v>7.997401</v>
+      </c>
+      <c r="H8">
+        <v>1901.4728700000001</v>
+      </c>
+      <c r="L8" s="5"/>
+      <c r="M8" t="s">
+        <v>12</v>
+      </c>
+      <c r="N8">
+        <v>8.3333000000000004E-2</v>
+      </c>
+      <c r="O8">
+        <v>5.8250200000000003</v>
+      </c>
+      <c r="P8">
+        <v>487.35775799999999</v>
+      </c>
+    </row>
+    <row r="9" spans="4:16" x14ac:dyDescent="0.3">
+      <c r="D9" s="5"/>
       <c r="E9" t="s">
         <v>13</v>
       </c>
@@ -2301,11 +4459,27 @@
         <v>8.3333000000000004E-2</v>
       </c>
       <c r="G9">
-        <v>11.330069999999999</v>
-      </c>
-    </row>
-    <row r="10" spans="4:7" x14ac:dyDescent="0.3">
-      <c r="D10" s="4"/>
+        <v>11.409751</v>
+      </c>
+      <c r="H9">
+        <v>1830.920386</v>
+      </c>
+      <c r="L9" s="5"/>
+      <c r="M9" t="s">
+        <v>13</v>
+      </c>
+      <c r="N9">
+        <v>0</v>
+      </c>
+      <c r="O9">
+        <v>6.2409489999999996</v>
+      </c>
+      <c r="P9">
+        <v>482.56103999999999</v>
+      </c>
+    </row>
+    <row r="10" spans="4:16" x14ac:dyDescent="0.3">
+      <c r="D10" s="5"/>
       <c r="E10" t="s">
         <v>14</v>
       </c>
@@ -2313,11 +4487,27 @@
         <v>0.125</v>
       </c>
       <c r="G10">
-        <v>9.9600950000000008</v>
-      </c>
-    </row>
-    <row r="11" spans="4:7" x14ac:dyDescent="0.3">
-      <c r="D11" s="4"/>
+        <v>10.028267</v>
+      </c>
+      <c r="H10">
+        <v>1876.7238179999999</v>
+      </c>
+      <c r="L10" s="5"/>
+      <c r="M10" t="s">
+        <v>14</v>
+      </c>
+      <c r="N10">
+        <v>8.3333000000000004E-2</v>
+      </c>
+      <c r="O10">
+        <v>6.9244690000000002</v>
+      </c>
+      <c r="P10">
+        <v>486.72825799999998</v>
+      </c>
+    </row>
+    <row r="11" spans="4:16" x14ac:dyDescent="0.3">
+      <c r="D11" s="5"/>
       <c r="E11" t="s">
         <v>15</v>
       </c>
@@ -2327,41 +4517,97 @@
       <c r="G11">
         <v>17.470189000000001</v>
       </c>
-    </row>
-    <row r="12" spans="4:7" x14ac:dyDescent="0.3">
-      <c r="D12" s="6"/>
-      <c r="E12" s="6"/>
-      <c r="F12" s="6"/>
-      <c r="G12" s="6"/>
-    </row>
-    <row r="13" spans="4:7" x14ac:dyDescent="0.3">
-      <c r="D13" s="4">
+      <c r="H11">
+        <v>1747.8217030000001</v>
+      </c>
+      <c r="L11" s="5"/>
+      <c r="M11" t="s">
+        <v>15</v>
+      </c>
+      <c r="N11">
+        <v>0.125</v>
+      </c>
+      <c r="O11">
+        <v>11.820055999999999</v>
+      </c>
+      <c r="P11">
+        <v>468.505292</v>
+      </c>
+    </row>
+    <row r="12" spans="4:16" x14ac:dyDescent="0.3">
+      <c r="D12" s="7"/>
+      <c r="E12" s="7"/>
+      <c r="F12" s="7"/>
+      <c r="G12" s="7"/>
+      <c r="H12" s="7"/>
+      <c r="L12" s="7"/>
+      <c r="M12" s="7"/>
+      <c r="N12" s="7"/>
+      <c r="O12" s="7"/>
+      <c r="P12" s="7"/>
+    </row>
+    <row r="13" spans="4:16" x14ac:dyDescent="0.3">
+      <c r="D13" s="5">
         <v>2</v>
       </c>
       <c r="E13" t="s">
         <v>16</v>
       </c>
       <c r="F13">
-        <v>0.75</v>
+        <v>0.79166700000000001</v>
       </c>
       <c r="G13">
-        <v>3.302511</v>
-      </c>
-    </row>
-    <row r="14" spans="4:7" x14ac:dyDescent="0.3">
-      <c r="D14" s="4"/>
+        <v>3.3525689999999999</v>
+      </c>
+      <c r="H13">
+        <v>16.465423999999999</v>
+      </c>
+      <c r="L13" s="5">
+        <v>2</v>
+      </c>
+      <c r="M13" t="s">
+        <v>16</v>
+      </c>
+      <c r="N13">
+        <v>0.54166700000000001</v>
+      </c>
+      <c r="O13">
+        <v>2.1682260000000002</v>
+      </c>
+      <c r="P13">
+        <v>7.553121</v>
+      </c>
+    </row>
+    <row r="14" spans="4:16" x14ac:dyDescent="0.3">
+      <c r="D14" s="5"/>
       <c r="E14" t="s">
         <v>10</v>
       </c>
       <c r="F14">
-        <v>0.70833299999999999</v>
+        <v>0.75</v>
       </c>
       <c r="G14">
-        <v>2.826975</v>
-      </c>
-    </row>
-    <row r="15" spans="4:7" x14ac:dyDescent="0.3">
-      <c r="D15" s="4"/>
+        <v>2.8606259999999999</v>
+      </c>
+      <c r="H14">
+        <v>20.018080999999999</v>
+      </c>
+      <c r="L14" s="5"/>
+      <c r="M14" t="s">
+        <v>10</v>
+      </c>
+      <c r="N14">
+        <v>0.5</v>
+      </c>
+      <c r="O14">
+        <v>1.9800800000000001</v>
+      </c>
+      <c r="P14">
+        <v>7.8127930000000001</v>
+      </c>
+    </row>
+    <row r="15" spans="4:16" x14ac:dyDescent="0.3">
+      <c r="D15" s="5"/>
       <c r="E15" t="s">
         <v>11</v>
       </c>
@@ -2369,11 +4615,27 @@
         <v>0.45833299999999999</v>
       </c>
       <c r="G15">
-        <v>1.7640830000000001</v>
-      </c>
-    </row>
-    <row r="16" spans="4:7" x14ac:dyDescent="0.3">
-      <c r="D16" s="4"/>
+        <v>1.754359</v>
+      </c>
+      <c r="H15">
+        <v>30.918436</v>
+      </c>
+      <c r="L15" s="5"/>
+      <c r="M15" t="s">
+        <v>11</v>
+      </c>
+      <c r="N15">
+        <v>0.29166700000000001</v>
+      </c>
+      <c r="O15">
+        <v>1.190536</v>
+      </c>
+      <c r="P15">
+        <v>9.9469019999999997</v>
+      </c>
+    </row>
+    <row r="16" spans="4:16" x14ac:dyDescent="0.3">
+      <c r="D16" s="5"/>
       <c r="E16" t="s">
         <v>12</v>
       </c>
@@ -2381,11 +4643,27 @@
         <v>0.41666700000000001</v>
       </c>
       <c r="G16">
-        <v>1.5894790000000001</v>
-      </c>
-    </row>
-    <row r="17" spans="4:7" x14ac:dyDescent="0.3">
-      <c r="D17" s="4"/>
+        <v>1.585296</v>
+      </c>
+      <c r="H16">
+        <v>32.605384000000001</v>
+      </c>
+      <c r="L16" s="5"/>
+      <c r="M16" t="s">
+        <v>12</v>
+      </c>
+      <c r="N16">
+        <v>0.25</v>
+      </c>
+      <c r="O16">
+        <v>1.0562959999999999</v>
+      </c>
+      <c r="P16">
+        <v>10.41732</v>
+      </c>
+    </row>
+    <row r="17" spans="4:16" x14ac:dyDescent="0.3">
+      <c r="D17" s="5"/>
       <c r="E17" t="s">
         <v>13</v>
       </c>
@@ -2393,11 +4671,27 @@
         <v>0.54166700000000001</v>
       </c>
       <c r="G17">
-        <v>2.2582849999999999</v>
-      </c>
-    </row>
-    <row r="18" spans="4:7" x14ac:dyDescent="0.3">
-      <c r="D18" s="4"/>
+        <v>2.3020510000000001</v>
+      </c>
+      <c r="H17">
+        <v>27.925259</v>
+      </c>
+      <c r="L17" s="5"/>
+      <c r="M17" t="s">
+        <v>13</v>
+      </c>
+      <c r="N17">
+        <v>0.33333299999999999</v>
+      </c>
+      <c r="O17">
+        <v>1.5140469999999999</v>
+      </c>
+      <c r="P17">
+        <v>9.754937</v>
+      </c>
+    </row>
+    <row r="18" spans="4:16" x14ac:dyDescent="0.3">
+      <c r="D18" s="5"/>
       <c r="E18" t="s">
         <v>14</v>
       </c>
@@ -2405,11 +4699,27 @@
         <v>0.75</v>
       </c>
       <c r="G18">
-        <v>4.5597669999999999</v>
-      </c>
-    </row>
-    <row r="19" spans="4:7" x14ac:dyDescent="0.3">
-      <c r="D19" s="4"/>
+        <v>4.5613979999999996</v>
+      </c>
+      <c r="H18">
+        <v>18.597137</v>
+      </c>
+      <c r="L18" s="5"/>
+      <c r="M18" t="s">
+        <v>14</v>
+      </c>
+      <c r="N18">
+        <v>0.70833299999999999</v>
+      </c>
+      <c r="O18">
+        <v>2.9497930000000001</v>
+      </c>
+      <c r="P18">
+        <v>8.0710390000000007</v>
+      </c>
+    </row>
+    <row r="19" spans="4:16" x14ac:dyDescent="0.3">
+      <c r="D19" s="5"/>
       <c r="E19" t="s">
         <v>15</v>
       </c>
@@ -2419,15 +4729,37 @@
       <c r="G19">
         <v>3.3573539999999999</v>
       </c>
-    </row>
-    <row r="20" spans="4:7" x14ac:dyDescent="0.3">
-      <c r="D20" s="5"/>
-      <c r="E20" s="5"/>
-      <c r="F20" s="5"/>
-      <c r="G20" s="5"/>
-    </row>
-    <row r="21" spans="4:7" x14ac:dyDescent="0.3">
-      <c r="D21" s="4">
+      <c r="H19">
+        <v>18.770641000000001</v>
+      </c>
+      <c r="L19" s="5"/>
+      <c r="M19" t="s">
+        <v>15</v>
+      </c>
+      <c r="N19">
+        <v>0.54166700000000001</v>
+      </c>
+      <c r="O19">
+        <v>2.2004009999999998</v>
+      </c>
+      <c r="P19">
+        <v>7.8692399999999996</v>
+      </c>
+    </row>
+    <row r="20" spans="4:16" x14ac:dyDescent="0.3">
+      <c r="D20" s="6"/>
+      <c r="E20" s="6"/>
+      <c r="F20" s="6"/>
+      <c r="G20" s="6"/>
+      <c r="H20" s="6"/>
+      <c r="L20" s="6"/>
+      <c r="M20" s="6"/>
+      <c r="N20" s="6"/>
+      <c r="O20" s="6"/>
+      <c r="P20" s="6"/>
+    </row>
+    <row r="21" spans="4:16" x14ac:dyDescent="0.3">
+      <c r="D21" s="5">
         <v>3</v>
       </c>
       <c r="E21" t="s">
@@ -2437,11 +4769,29 @@
         <v>0.15</v>
       </c>
       <c r="G21">
-        <v>446.82893200000001</v>
-      </c>
-    </row>
-    <row r="22" spans="4:7" x14ac:dyDescent="0.3">
-      <c r="D22" s="4"/>
+        <v>438.99705399999999</v>
+      </c>
+      <c r="H21">
+        <v>18190.681049999999</v>
+      </c>
+      <c r="L21" s="5">
+        <v>3</v>
+      </c>
+      <c r="M21" t="s">
+        <v>16</v>
+      </c>
+      <c r="N21">
+        <v>0</v>
+      </c>
+      <c r="O21">
+        <v>305.05923200000001</v>
+      </c>
+      <c r="P21">
+        <v>5460.7693929999996</v>
+      </c>
+    </row>
+    <row r="22" spans="4:16" x14ac:dyDescent="0.3">
+      <c r="D22" s="5"/>
       <c r="E22" t="s">
         <v>10</v>
       </c>
@@ -2449,11 +4799,27 @@
         <v>0</v>
       </c>
       <c r="G22">
-        <v>263.68174299999998</v>
-      </c>
-    </row>
-    <row r="23" spans="4:7" x14ac:dyDescent="0.3">
-      <c r="D23" s="4"/>
+        <v>269.865252</v>
+      </c>
+      <c r="H22">
+        <v>21880.526777999999</v>
+      </c>
+      <c r="L22" s="5"/>
+      <c r="M22" t="s">
+        <v>10</v>
+      </c>
+      <c r="N22">
+        <v>0</v>
+      </c>
+      <c r="O22">
+        <v>181.786903</v>
+      </c>
+      <c r="P22">
+        <v>6033.5829030000004</v>
+      </c>
+    </row>
+    <row r="23" spans="4:16" x14ac:dyDescent="0.3">
+      <c r="D23" s="5"/>
       <c r="E23" t="s">
         <v>11</v>
       </c>
@@ -2461,11 +4827,27 @@
         <v>0</v>
       </c>
       <c r="G23">
-        <v>205.671415</v>
-      </c>
-    </row>
-    <row r="24" spans="4:7" x14ac:dyDescent="0.3">
-      <c r="D24" s="4"/>
+        <v>208.24779000000001</v>
+      </c>
+      <c r="H23">
+        <v>23006.512046</v>
+      </c>
+      <c r="L23" s="5"/>
+      <c r="M23" t="s">
+        <v>11</v>
+      </c>
+      <c r="N23">
+        <v>0</v>
+      </c>
+      <c r="O23">
+        <v>132.39876599999999</v>
+      </c>
+      <c r="P23">
+        <v>6217.654963</v>
+      </c>
+    </row>
+    <row r="24" spans="4:16" x14ac:dyDescent="0.3">
+      <c r="D24" s="5"/>
       <c r="E24" t="s">
         <v>12</v>
       </c>
@@ -2473,11 +4855,27 @@
         <v>0</v>
       </c>
       <c r="G24">
-        <v>229.85868300000001</v>
-      </c>
-    </row>
-    <row r="25" spans="4:7" x14ac:dyDescent="0.3">
-      <c r="D25" s="4"/>
+        <v>227.70563300000001</v>
+      </c>
+      <c r="H24">
+        <v>22768.191392000001</v>
+      </c>
+      <c r="L24" s="5"/>
+      <c r="M24" t="s">
+        <v>12</v>
+      </c>
+      <c r="N24">
+        <v>0</v>
+      </c>
+      <c r="O24">
+        <v>144.45309900000001</v>
+      </c>
+      <c r="P24">
+        <v>6161.0641159999996</v>
+      </c>
+    </row>
+    <row r="25" spans="4:16" x14ac:dyDescent="0.3">
+      <c r="D25" s="5"/>
       <c r="E25" t="s">
         <v>13</v>
       </c>
@@ -2485,11 +4883,27 @@
         <v>0.05</v>
       </c>
       <c r="G25">
-        <v>285.54760499999998</v>
-      </c>
-    </row>
-    <row r="26" spans="4:7" x14ac:dyDescent="0.3">
-      <c r="D26" s="4"/>
+        <v>285.05472600000002</v>
+      </c>
+      <c r="H25">
+        <v>21019.475958999999</v>
+      </c>
+      <c r="L25" s="5"/>
+      <c r="M25" t="s">
+        <v>13</v>
+      </c>
+      <c r="N25">
+        <v>0</v>
+      </c>
+      <c r="O25">
+        <v>221.74178800000001</v>
+      </c>
+      <c r="P25">
+        <v>5764.4069229999996</v>
+      </c>
+    </row>
+    <row r="26" spans="4:16" x14ac:dyDescent="0.3">
+      <c r="D26" s="5"/>
       <c r="E26" t="s">
         <v>14</v>
       </c>
@@ -2497,11 +4911,27 @@
         <v>0</v>
       </c>
       <c r="G26">
-        <v>30.406841</v>
-      </c>
-    </row>
-    <row r="27" spans="4:7" x14ac:dyDescent="0.3">
-      <c r="D27" s="4"/>
+        <v>30.32591</v>
+      </c>
+      <c r="H26">
+        <v>27242.281451999999</v>
+      </c>
+      <c r="L26" s="5"/>
+      <c r="M26" t="s">
+        <v>14</v>
+      </c>
+      <c r="N26">
+        <v>0</v>
+      </c>
+      <c r="O26">
+        <v>8.1647540000000003</v>
+      </c>
+      <c r="P26">
+        <v>7001.5684449999999</v>
+      </c>
+    </row>
+    <row r="27" spans="4:16" x14ac:dyDescent="0.3">
+      <c r="D27" s="5"/>
       <c r="E27" t="s">
         <v>15</v>
       </c>
@@ -2511,15 +4941,37 @@
       <c r="G27">
         <v>389.80510199999998</v>
       </c>
-    </row>
-    <row r="28" spans="4:7" x14ac:dyDescent="0.3">
-      <c r="D28" s="5"/>
-      <c r="E28" s="5"/>
-      <c r="F28" s="5"/>
-      <c r="G28" s="5"/>
-    </row>
-    <row r="29" spans="4:7" x14ac:dyDescent="0.3">
-      <c r="D29" s="4">
+      <c r="H27">
+        <v>19048.814703</v>
+      </c>
+      <c r="L27" s="5"/>
+      <c r="M27" t="s">
+        <v>15</v>
+      </c>
+      <c r="N27">
+        <v>0</v>
+      </c>
+      <c r="O27">
+        <v>277.34696700000001</v>
+      </c>
+      <c r="P27">
+        <v>5535.6923299999999</v>
+      </c>
+    </row>
+    <row r="28" spans="4:16" x14ac:dyDescent="0.3">
+      <c r="D28" s="6"/>
+      <c r="E28" s="6"/>
+      <c r="F28" s="6"/>
+      <c r="G28" s="6"/>
+      <c r="H28" s="6"/>
+      <c r="L28" s="6"/>
+      <c r="M28" s="6"/>
+      <c r="N28" s="6"/>
+      <c r="O28" s="6"/>
+      <c r="P28" s="6"/>
+    </row>
+    <row r="29" spans="4:16" x14ac:dyDescent="0.3">
+      <c r="D29" s="5">
         <v>4</v>
       </c>
       <c r="E29" t="s">
@@ -2529,11 +4981,29 @@
         <v>8.3333000000000004E-2</v>
       </c>
       <c r="G29">
-        <v>22.351651</v>
-      </c>
-    </row>
-    <row r="30" spans="4:7" x14ac:dyDescent="0.3">
-      <c r="D30" s="4"/>
+        <v>22.236863</v>
+      </c>
+      <c r="H29">
+        <v>2533.7548160000001</v>
+      </c>
+      <c r="L29" s="5">
+        <v>4</v>
+      </c>
+      <c r="M29" t="s">
+        <v>16</v>
+      </c>
+      <c r="N29">
+        <v>4.1667000000000003E-2</v>
+      </c>
+      <c r="O29">
+        <v>15.2743</v>
+      </c>
+      <c r="P29">
+        <v>677.74556500000006</v>
+      </c>
+    </row>
+    <row r="30" spans="4:16" x14ac:dyDescent="0.3">
+      <c r="D30" s="5"/>
       <c r="E30" t="s">
         <v>10</v>
       </c>
@@ -2541,11 +5011,27 @@
         <v>8.3333000000000004E-2</v>
       </c>
       <c r="G30">
-        <v>18.362424000000001</v>
-      </c>
-    </row>
-    <row r="31" spans="4:7" x14ac:dyDescent="0.3">
-      <c r="D31" s="4"/>
+        <v>18.334624999999999</v>
+      </c>
+      <c r="H30">
+        <v>2613.4271250000002</v>
+      </c>
+      <c r="L30" s="5"/>
+      <c r="M30" t="s">
+        <v>10</v>
+      </c>
+      <c r="N30">
+        <v>4.1667000000000003E-2</v>
+      </c>
+      <c r="O30">
+        <v>13.813682999999999</v>
+      </c>
+      <c r="P30">
+        <v>683.24497099999996</v>
+      </c>
+    </row>
+    <row r="31" spans="4:16" x14ac:dyDescent="0.3">
+      <c r="D31" s="5"/>
       <c r="E31" t="s">
         <v>11</v>
       </c>
@@ -2553,11 +5039,27 @@
         <v>4.1667000000000003E-2</v>
       </c>
       <c r="G31">
-        <v>11.536178</v>
-      </c>
-    </row>
-    <row r="32" spans="4:7" x14ac:dyDescent="0.3">
-      <c r="D32" s="4"/>
+        <v>10.866497000000001</v>
+      </c>
+      <c r="H31">
+        <v>2731.0749860000001</v>
+      </c>
+      <c r="L31" s="5"/>
+      <c r="M31" t="s">
+        <v>11</v>
+      </c>
+      <c r="N31">
+        <v>4.1667000000000003E-2</v>
+      </c>
+      <c r="O31">
+        <v>7.7136069999999997</v>
+      </c>
+      <c r="P31">
+        <v>705.10328100000004</v>
+      </c>
+    </row>
+    <row r="32" spans="4:16" x14ac:dyDescent="0.3">
+      <c r="D32" s="5"/>
       <c r="E32" t="s">
         <v>12</v>
       </c>
@@ -2565,11 +5067,27 @@
         <v>4.1667000000000003E-2</v>
       </c>
       <c r="G32">
-        <v>9.1053379999999997</v>
-      </c>
-    </row>
-    <row r="33" spans="4:7" x14ac:dyDescent="0.3">
-      <c r="D33" s="4"/>
+        <v>9.0411870000000008</v>
+      </c>
+      <c r="H32">
+        <v>2768.4342550000001</v>
+      </c>
+      <c r="L32" s="5"/>
+      <c r="M32" t="s">
+        <v>12</v>
+      </c>
+      <c r="N32">
+        <v>4.1667000000000003E-2</v>
+      </c>
+      <c r="O32">
+        <v>5.8704010000000002</v>
+      </c>
+      <c r="P32">
+        <v>713.01744799999994</v>
+      </c>
+    </row>
+    <row r="33" spans="4:16" x14ac:dyDescent="0.3">
+      <c r="D33" s="5"/>
       <c r="E33" t="s">
         <v>13</v>
       </c>
@@ -2577,11 +5095,27 @@
         <v>4.1667000000000003E-2</v>
       </c>
       <c r="G33">
-        <v>15.940567</v>
-      </c>
-    </row>
-    <row r="34" spans="4:7" x14ac:dyDescent="0.3">
-      <c r="D34" s="4"/>
+        <v>16.091439999999999</v>
+      </c>
+      <c r="H33">
+        <v>2636.196739</v>
+      </c>
+      <c r="L33" s="5"/>
+      <c r="M33" t="s">
+        <v>13</v>
+      </c>
+      <c r="N33">
+        <v>0</v>
+      </c>
+      <c r="O33">
+        <v>10.079178000000001</v>
+      </c>
+      <c r="P33">
+        <v>694.76316899999995</v>
+      </c>
+    </row>
+    <row r="34" spans="4:16" x14ac:dyDescent="0.3">
+      <c r="D34" s="5"/>
       <c r="E34" t="s">
         <v>14</v>
       </c>
@@ -2589,11 +5123,27 @@
         <v>4.1667000000000003E-2</v>
       </c>
       <c r="G34">
-        <v>7.6881339999999998</v>
-      </c>
-    </row>
-    <row r="35" spans="4:7" x14ac:dyDescent="0.3">
-      <c r="D35" s="4"/>
+        <v>7.6344159999999999</v>
+      </c>
+      <c r="H34">
+        <v>2811.0372480000001</v>
+      </c>
+      <c r="L34" s="5"/>
+      <c r="M34" t="s">
+        <v>14</v>
+      </c>
+      <c r="N34">
+        <v>0</v>
+      </c>
+      <c r="O34">
+        <v>4.8746869999999998</v>
+      </c>
+      <c r="P34">
+        <v>719.39956099999995</v>
+      </c>
+    </row>
+    <row r="35" spans="4:16" x14ac:dyDescent="0.3">
+      <c r="D35" s="5"/>
       <c r="E35" t="s">
         <v>15</v>
       </c>
@@ -2603,15 +5153,37 @@
       <c r="G35">
         <v>21.509909</v>
       </c>
-    </row>
-    <row r="36" spans="4:7" x14ac:dyDescent="0.3">
-      <c r="D36" s="5"/>
-      <c r="E36" s="5"/>
-      <c r="F36" s="5"/>
-      <c r="G36" s="5"/>
-    </row>
-    <row r="37" spans="4:7" x14ac:dyDescent="0.3">
-      <c r="D37" s="4">
+      <c r="H35">
+        <v>2552.888301</v>
+      </c>
+      <c r="L35" s="5"/>
+      <c r="M35" t="s">
+        <v>15</v>
+      </c>
+      <c r="N35">
+        <v>8.3333000000000004E-2</v>
+      </c>
+      <c r="O35">
+        <v>14.323302</v>
+      </c>
+      <c r="P35">
+        <v>683.353025</v>
+      </c>
+    </row>
+    <row r="36" spans="4:16" x14ac:dyDescent="0.3">
+      <c r="D36" s="6"/>
+      <c r="E36" s="6"/>
+      <c r="F36" s="6"/>
+      <c r="G36" s="6"/>
+      <c r="H36" s="6"/>
+      <c r="L36" s="6"/>
+      <c r="M36" s="6"/>
+      <c r="N36" s="6"/>
+      <c r="O36" s="6"/>
+      <c r="P36" s="6"/>
+    </row>
+    <row r="37" spans="4:16" x14ac:dyDescent="0.3">
+      <c r="D37" s="5">
         <v>5</v>
       </c>
       <c r="E37" t="s">
@@ -2621,11 +5193,29 @@
         <v>8.3333000000000004E-2</v>
       </c>
       <c r="G37">
-        <v>95.155683999999994</v>
-      </c>
-    </row>
-    <row r="38" spans="4:7" x14ac:dyDescent="0.3">
-      <c r="D38" s="4"/>
+        <v>94.419690000000003</v>
+      </c>
+      <c r="H37">
+        <v>12254.753266</v>
+      </c>
+      <c r="L37" s="5">
+        <v>5</v>
+      </c>
+      <c r="M37" t="s">
+        <v>16</v>
+      </c>
+      <c r="N37">
+        <v>8.3333000000000004E-2</v>
+      </c>
+      <c r="O37">
+        <v>64.348022999999998</v>
+      </c>
+      <c r="P37">
+        <v>3246.3235970000001</v>
+      </c>
+    </row>
+    <row r="38" spans="4:16" x14ac:dyDescent="0.3">
+      <c r="D38" s="5"/>
       <c r="E38" t="s">
         <v>10</v>
       </c>
@@ -2633,11 +5223,27 @@
         <v>8.3333000000000004E-2</v>
       </c>
       <c r="G38">
-        <v>91.139943000000002</v>
-      </c>
-    </row>
-    <row r="39" spans="4:7" x14ac:dyDescent="0.3">
-      <c r="D39" s="4"/>
+        <v>90.063563000000002</v>
+      </c>
+      <c r="H38">
+        <v>12308.422896</v>
+      </c>
+      <c r="L38" s="5"/>
+      <c r="M38" t="s">
+        <v>10</v>
+      </c>
+      <c r="N38">
+        <v>8.3333000000000004E-2</v>
+      </c>
+      <c r="O38">
+        <v>64.312647999999996</v>
+      </c>
+      <c r="P38">
+        <v>3247.3815020000002</v>
+      </c>
+    </row>
+    <row r="39" spans="4:16" x14ac:dyDescent="0.3">
+      <c r="D39" s="5"/>
       <c r="E39" t="s">
         <v>11</v>
       </c>
@@ -2645,11 +5251,27 @@
         <v>8.3333000000000004E-2</v>
       </c>
       <c r="G39">
-        <v>50.897694999999999</v>
-      </c>
-    </row>
-    <row r="40" spans="4:7" x14ac:dyDescent="0.3">
-      <c r="D40" s="4"/>
+        <v>50.382824999999997</v>
+      </c>
+      <c r="H39">
+        <v>13067.171042</v>
+      </c>
+      <c r="L39" s="5"/>
+      <c r="M39" t="s">
+        <v>11</v>
+      </c>
+      <c r="N39">
+        <v>4.1667000000000003E-2</v>
+      </c>
+      <c r="O39">
+        <v>35.309193999999998</v>
+      </c>
+      <c r="P39">
+        <v>3365.6178340000001</v>
+      </c>
+    </row>
+    <row r="40" spans="4:16" x14ac:dyDescent="0.3">
+      <c r="D40" s="5"/>
       <c r="E40" t="s">
         <v>12</v>
       </c>
@@ -2657,11 +5279,27 @@
         <v>4.1667000000000003E-2</v>
       </c>
       <c r="G40">
-        <v>45.668508000000003</v>
-      </c>
-    </row>
-    <row r="41" spans="4:7" x14ac:dyDescent="0.3">
-      <c r="D41" s="4"/>
+        <v>45.472577000000001</v>
+      </c>
+      <c r="H40">
+        <v>13156.249231</v>
+      </c>
+      <c r="L40" s="5"/>
+      <c r="M40" t="s">
+        <v>12</v>
+      </c>
+      <c r="N40">
+        <v>4.1667000000000003E-2</v>
+      </c>
+      <c r="O40">
+        <v>32.310135000000002</v>
+      </c>
+      <c r="P40">
+        <v>3378.2534190000001</v>
+      </c>
+    </row>
+    <row r="41" spans="4:16" x14ac:dyDescent="0.3">
+      <c r="D41" s="5"/>
       <c r="E41" t="s">
         <v>13</v>
       </c>
@@ -2669,11 +5307,27 @@
         <v>4.1667000000000003E-2</v>
       </c>
       <c r="G41">
-        <v>61.417313999999998</v>
-      </c>
-    </row>
-    <row r="42" spans="4:7" x14ac:dyDescent="0.3">
-      <c r="D42" s="4"/>
+        <v>61.110380999999997</v>
+      </c>
+      <c r="H41">
+        <v>13053.510526</v>
+      </c>
+      <c r="L41" s="5"/>
+      <c r="M41" t="s">
+        <v>13</v>
+      </c>
+      <c r="N41">
+        <v>4.1667000000000003E-2</v>
+      </c>
+      <c r="O41">
+        <v>43.691521000000002</v>
+      </c>
+      <c r="P41">
+        <v>3347.8150310000001</v>
+      </c>
+    </row>
+    <row r="42" spans="4:16" x14ac:dyDescent="0.3">
+      <c r="D42" s="5"/>
       <c r="E42" t="s">
         <v>14</v>
       </c>
@@ -2681,11 +5335,27 @@
         <v>4.1667000000000003E-2</v>
       </c>
       <c r="G42">
-        <v>8.7120560000000005</v>
-      </c>
-    </row>
-    <row r="43" spans="4:7" x14ac:dyDescent="0.3">
-      <c r="D43" s="4"/>
+        <v>6.6388410000000002</v>
+      </c>
+      <c r="H42">
+        <v>13997.711687000001</v>
+      </c>
+      <c r="L42" s="5"/>
+      <c r="M42" t="s">
+        <v>14</v>
+      </c>
+      <c r="N42">
+        <v>0</v>
+      </c>
+      <c r="O42">
+        <v>4.0367249999999997</v>
+      </c>
+      <c r="P42">
+        <v>3517.9947179999999</v>
+      </c>
+    </row>
+    <row r="43" spans="4:16" x14ac:dyDescent="0.3">
+      <c r="D43" s="5"/>
       <c r="E43" t="s">
         <v>15</v>
       </c>
@@ -2695,25 +5365,57 @@
       <c r="G43">
         <v>89.088755000000006</v>
       </c>
-    </row>
-    <row r="44" spans="4:7" x14ac:dyDescent="0.3">
-      <c r="D44" s="5"/>
-      <c r="E44" s="5"/>
-      <c r="F44" s="5"/>
-      <c r="G44" s="5"/>
+      <c r="H43">
+        <v>12347.478488999999</v>
+      </c>
+      <c r="L43" s="5"/>
+      <c r="M43" t="s">
+        <v>15</v>
+      </c>
+      <c r="N43">
+        <v>8.3333000000000004E-2</v>
+      </c>
+      <c r="O43">
+        <v>56.295561999999997</v>
+      </c>
+      <c r="P43">
+        <v>3292.1715800000002</v>
+      </c>
+    </row>
+    <row r="44" spans="4:16" x14ac:dyDescent="0.3">
+      <c r="D44" s="6"/>
+      <c r="E44" s="6"/>
+      <c r="F44" s="6"/>
+      <c r="G44" s="6"/>
+      <c r="H44" s="6"/>
+      <c r="L44" s="6"/>
+      <c r="M44" s="6"/>
+      <c r="N44" s="6"/>
+      <c r="O44" s="6"/>
+      <c r="P44" s="6"/>
     </row>
   </sheetData>
-  <mergeCells count="10">
-    <mergeCell ref="D37:D43"/>
-    <mergeCell ref="D44:G44"/>
-    <mergeCell ref="D29:D35"/>
-    <mergeCell ref="D36:G36"/>
-    <mergeCell ref="D28:G28"/>
+  <mergeCells count="20">
+    <mergeCell ref="L28:P28"/>
+    <mergeCell ref="L29:L35"/>
+    <mergeCell ref="L36:P36"/>
+    <mergeCell ref="L37:L43"/>
+    <mergeCell ref="L44:P44"/>
+    <mergeCell ref="L5:L11"/>
+    <mergeCell ref="L12:P12"/>
+    <mergeCell ref="L13:L19"/>
+    <mergeCell ref="L20:P20"/>
+    <mergeCell ref="L21:L27"/>
     <mergeCell ref="D5:D11"/>
-    <mergeCell ref="D12:G12"/>
-    <mergeCell ref="D20:G20"/>
     <mergeCell ref="D13:D19"/>
     <mergeCell ref="D21:D27"/>
+    <mergeCell ref="D12:H12"/>
+    <mergeCell ref="D20:H20"/>
+    <mergeCell ref="D37:D43"/>
+    <mergeCell ref="D29:D35"/>
+    <mergeCell ref="D28:H28"/>
+    <mergeCell ref="D36:H36"/>
+    <mergeCell ref="D44:H44"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
